--- a/gcam/output/SSP2/iamc_template_gcam_other.xlsx
+++ b/gcam/output/SSP2/iamc_template_gcam_other.xlsx
@@ -684,70 +684,70 @@
         <v>66</v>
       </c>
       <c r="F2">
-        <v>98409</v>
+        <v>98.40900000000001</v>
       </c>
       <c r="G2">
-        <v>151062</v>
+        <v>151.062</v>
       </c>
       <c r="H2">
-        <v>230484</v>
+        <v>230.484</v>
       </c>
       <c r="I2">
-        <v>266642</v>
+        <v>266.642</v>
       </c>
       <c r="J2">
-        <v>304443</v>
+        <v>304.443</v>
       </c>
       <c r="K2">
-        <v>355355</v>
+        <v>355.355</v>
       </c>
       <c r="L2">
-        <v>391100</v>
+        <v>391.1</v>
       </c>
       <c r="M2">
-        <v>438024</v>
+        <v>438.024</v>
       </c>
       <c r="N2">
-        <v>485635</v>
+        <v>485.635</v>
       </c>
       <c r="O2">
-        <v>532794</v>
+        <v>532.794</v>
       </c>
       <c r="P2">
-        <v>578897</v>
+        <v>578.897</v>
       </c>
       <c r="Q2">
-        <v>623428</v>
+        <v>623.428</v>
       </c>
       <c r="R2">
-        <v>665230</v>
+        <v>665.23</v>
       </c>
       <c r="S2">
-        <v>704017</v>
+        <v>704.0170000000001</v>
       </c>
       <c r="T2">
-        <v>738606</v>
+        <v>738.606</v>
       </c>
       <c r="U2">
-        <v>768862</v>
+        <v>768.862</v>
       </c>
       <c r="V2">
-        <v>793943</v>
+        <v>793.943</v>
       </c>
       <c r="W2">
-        <v>814205</v>
+        <v>814.205</v>
       </c>
       <c r="X2">
-        <v>830143</v>
+        <v>830.143</v>
       </c>
       <c r="Y2">
-        <v>842266</v>
+        <v>842.266</v>
       </c>
       <c r="Z2">
-        <v>850642</v>
+        <v>850.6420000000001</v>
       </c>
       <c r="AA2">
-        <v>855535</v>
+        <v>855.535</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -767,70 +767,70 @@
         <v>66</v>
       </c>
       <c r="F3">
-        <v>79953</v>
+        <v>79.953</v>
       </c>
       <c r="G3">
-        <v>120159</v>
+        <v>120.159</v>
       </c>
       <c r="H3">
-        <v>159029</v>
+        <v>159.029</v>
       </c>
       <c r="I3">
-        <v>173374</v>
+        <v>173.374</v>
       </c>
       <c r="J3">
-        <v>190189</v>
+        <v>190.189</v>
       </c>
       <c r="K3">
-        <v>210081</v>
+        <v>210.081</v>
       </c>
       <c r="L3">
-        <v>222993</v>
+        <v>222.993</v>
       </c>
       <c r="M3">
-        <v>238346</v>
+        <v>238.346</v>
       </c>
       <c r="N3">
-        <v>253020</v>
+        <v>253.02</v>
       </c>
       <c r="O3">
-        <v>267277</v>
+        <v>267.277</v>
       </c>
       <c r="P3">
-        <v>280708</v>
+        <v>280.708</v>
       </c>
       <c r="Q3">
-        <v>292805</v>
+        <v>292.805</v>
       </c>
       <c r="R3">
-        <v>303162</v>
+        <v>303.162</v>
       </c>
       <c r="S3">
-        <v>311731</v>
+        <v>311.731</v>
       </c>
       <c r="T3">
-        <v>318383</v>
+        <v>318.383</v>
       </c>
       <c r="U3">
-        <v>323405</v>
+        <v>323.405</v>
       </c>
       <c r="V3">
-        <v>327298</v>
+        <v>327.298</v>
       </c>
       <c r="W3">
-        <v>330277</v>
+        <v>330.277</v>
       </c>
       <c r="X3">
-        <v>332354</v>
+        <v>332.354</v>
       </c>
       <c r="Y3">
-        <v>333628</v>
+        <v>333.628</v>
       </c>
       <c r="Z3">
-        <v>333848</v>
+        <v>333.848</v>
       </c>
       <c r="AA3">
-        <v>332951</v>
+        <v>332.951</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -850,70 +850,70 @@
         <v>66</v>
       </c>
       <c r="F4">
-        <v>52620</v>
+        <v>52.62</v>
       </c>
       <c r="G4">
-        <v>84042</v>
+        <v>84.042</v>
       </c>
       <c r="H4">
-        <v>122552</v>
+        <v>122.552</v>
       </c>
       <c r="I4">
-        <v>140212</v>
+        <v>140.212</v>
       </c>
       <c r="J4">
-        <v>162696</v>
+        <v>162.696</v>
       </c>
       <c r="K4">
-        <v>194118</v>
+        <v>194.118</v>
       </c>
       <c r="L4">
-        <v>215688</v>
+        <v>215.688</v>
       </c>
       <c r="M4">
-        <v>244055</v>
+        <v>244.055</v>
       </c>
       <c r="N4">
-        <v>273381</v>
+        <v>273.381</v>
       </c>
       <c r="O4">
-        <v>303131</v>
+        <v>303.131</v>
       </c>
       <c r="P4">
-        <v>332760</v>
+        <v>332.76</v>
       </c>
       <c r="Q4">
-        <v>361618</v>
+        <v>361.618</v>
       </c>
       <c r="R4">
-        <v>388966</v>
+        <v>388.966</v>
       </c>
       <c r="S4">
-        <v>414621</v>
+        <v>414.621</v>
       </c>
       <c r="T4">
-        <v>438016</v>
+        <v>438.016</v>
       </c>
       <c r="U4">
-        <v>458830</v>
+        <v>458.83</v>
       </c>
       <c r="V4">
-        <v>476989</v>
+        <v>476.989</v>
       </c>
       <c r="W4">
-        <v>491948</v>
+        <v>491.948</v>
       </c>
       <c r="X4">
-        <v>503434</v>
+        <v>503.434</v>
       </c>
       <c r="Y4">
-        <v>511665</v>
+        <v>511.665</v>
       </c>
       <c r="Z4">
-        <v>517324</v>
+        <v>517.324</v>
       </c>
       <c r="AA4">
-        <v>520771</v>
+        <v>520.771</v>
       </c>
     </row>
     <row r="5" spans="1:27">
@@ -933,70 +933,70 @@
         <v>66</v>
       </c>
       <c r="F5">
-        <v>160687</v>
+        <v>160.687</v>
       </c>
       <c r="G5">
-        <v>242847</v>
+        <v>242.847</v>
       </c>
       <c r="H5">
-        <v>366537</v>
+        <v>366.537</v>
       </c>
       <c r="I5">
-        <v>422911</v>
+        <v>422.911</v>
       </c>
       <c r="J5">
-        <v>487548</v>
+        <v>487.548</v>
       </c>
       <c r="K5">
-        <v>574303</v>
+        <v>574.303</v>
       </c>
       <c r="L5">
-        <v>637591</v>
+        <v>637.591</v>
       </c>
       <c r="M5">
-        <v>723488</v>
+        <v>723.4880000000001</v>
       </c>
       <c r="N5">
-        <v>815076</v>
+        <v>815.076</v>
       </c>
       <c r="O5">
-        <v>911381</v>
+        <v>911.381</v>
       </c>
       <c r="P5">
-        <v>1010580</v>
+        <v>1010.58</v>
       </c>
       <c r="Q5">
-        <v>1110720</v>
+        <v>1110.72</v>
       </c>
       <c r="R5">
-        <v>1209160</v>
+        <v>1209.16</v>
       </c>
       <c r="S5">
-        <v>1304450</v>
+        <v>1304.45</v>
       </c>
       <c r="T5">
-        <v>1395550</v>
+        <v>1395.55</v>
       </c>
       <c r="U5">
-        <v>1481360</v>
+        <v>1481.36</v>
       </c>
       <c r="V5">
-        <v>1560780</v>
+        <v>1560.78</v>
       </c>
       <c r="W5">
-        <v>1632350</v>
+        <v>1632.35</v>
       </c>
       <c r="X5">
-        <v>1695070</v>
+        <v>1695.07</v>
       </c>
       <c r="Y5">
-        <v>1748160</v>
+        <v>1748.16</v>
       </c>
       <c r="Z5">
-        <v>1790820</v>
+        <v>1790.82</v>
       </c>
       <c r="AA5">
-        <v>1823070</v>
+        <v>1823.07</v>
       </c>
     </row>
     <row r="6" spans="1:27">
@@ -1016,70 +1016,70 @@
         <v>66</v>
       </c>
       <c r="F6">
-        <v>25876</v>
+        <v>25.876</v>
       </c>
       <c r="G6">
-        <v>32638</v>
+        <v>32.638</v>
       </c>
       <c r="H6">
-        <v>39071</v>
+        <v>39.071</v>
       </c>
       <c r="I6">
-        <v>41100</v>
+        <v>41.1</v>
       </c>
       <c r="J6">
-        <v>43257</v>
+        <v>43.257</v>
       </c>
       <c r="K6">
-        <v>45277</v>
+        <v>45.277</v>
       </c>
       <c r="L6">
-        <v>46190</v>
+        <v>46.19</v>
       </c>
       <c r="M6">
-        <v>47373</v>
+        <v>47.373</v>
       </c>
       <c r="N6">
-        <v>48471</v>
+        <v>48.471</v>
       </c>
       <c r="O6">
-        <v>49452</v>
+        <v>49.452</v>
       </c>
       <c r="P6">
-        <v>50276</v>
+        <v>50.276</v>
       </c>
       <c r="Q6">
-        <v>50923</v>
+        <v>50.923</v>
       </c>
       <c r="R6">
-        <v>51384</v>
+        <v>51.384</v>
       </c>
       <c r="S6">
-        <v>51617</v>
+        <v>51.617</v>
       </c>
       <c r="T6">
-        <v>51654</v>
+        <v>51.654</v>
       </c>
       <c r="U6">
-        <v>51525</v>
+        <v>51.525</v>
       </c>
       <c r="V6">
-        <v>51242</v>
+        <v>51.242</v>
       </c>
       <c r="W6">
-        <v>50814</v>
+        <v>50.814</v>
       </c>
       <c r="X6">
-        <v>50249</v>
+        <v>50.249</v>
       </c>
       <c r="Y6">
-        <v>49567</v>
+        <v>49.567</v>
       </c>
       <c r="Z6">
-        <v>48790</v>
+        <v>48.79</v>
       </c>
       <c r="AA6">
-        <v>47947</v>
+        <v>47.947</v>
       </c>
     </row>
     <row r="7" spans="1:27">
@@ -1099,70 +1099,70 @@
         <v>66</v>
       </c>
       <c r="F7">
-        <v>16982</v>
+        <v>16.982</v>
       </c>
       <c r="G7">
-        <v>20445</v>
+        <v>20.445</v>
       </c>
       <c r="H7">
-        <v>24305</v>
+        <v>24.305</v>
       </c>
       <c r="I7">
-        <v>26366</v>
+        <v>26.366</v>
       </c>
       <c r="J7">
-        <v>28411</v>
+        <v>28.411</v>
       </c>
       <c r="K7">
-        <v>31051</v>
+        <v>31.051</v>
       </c>
       <c r="L7">
-        <v>31999</v>
+        <v>31.999</v>
       </c>
       <c r="M7">
-        <v>33135</v>
+        <v>33.135</v>
       </c>
       <c r="N7">
-        <v>34189</v>
+        <v>34.189</v>
       </c>
       <c r="O7">
-        <v>35181</v>
+        <v>35.181</v>
       </c>
       <c r="P7">
-        <v>36154</v>
+        <v>36.154</v>
       </c>
       <c r="Q7">
-        <v>37135</v>
+        <v>37.135</v>
       </c>
       <c r="R7">
-        <v>38039</v>
+        <v>38.039</v>
       </c>
       <c r="S7">
-        <v>38872</v>
+        <v>38.872</v>
       </c>
       <c r="T7">
-        <v>39592</v>
+        <v>39.592</v>
       </c>
       <c r="U7">
-        <v>40214</v>
+        <v>40.214</v>
       </c>
       <c r="V7">
-        <v>40732</v>
+        <v>40.732</v>
       </c>
       <c r="W7">
-        <v>41128</v>
+        <v>41.128</v>
       </c>
       <c r="X7">
-        <v>41369</v>
+        <v>41.369</v>
       </c>
       <c r="Y7">
-        <v>41451</v>
+        <v>41.451</v>
       </c>
       <c r="Z7">
-        <v>41406</v>
+        <v>41.406</v>
       </c>
       <c r="AA7">
-        <v>41268</v>
+        <v>41.268</v>
       </c>
     </row>
     <row r="8" spans="1:27">
@@ -1182,70 +1182,70 @@
         <v>66</v>
       </c>
       <c r="F8">
-        <v>108701</v>
+        <v>108.701</v>
       </c>
       <c r="G8">
-        <v>150706</v>
+        <v>150.706</v>
       </c>
       <c r="H8">
-        <v>186797</v>
+        <v>186.797</v>
       </c>
       <c r="I8">
-        <v>196353</v>
+        <v>196.353</v>
       </c>
       <c r="J8">
-        <v>205188</v>
+        <v>205.188</v>
       </c>
       <c r="K8">
-        <v>214326</v>
+        <v>214.326</v>
       </c>
       <c r="L8">
-        <v>218338</v>
+        <v>218.338</v>
       </c>
       <c r="M8">
-        <v>223013</v>
+        <v>223.013</v>
       </c>
       <c r="N8">
-        <v>226408</v>
+        <v>226.408</v>
       </c>
       <c r="O8">
-        <v>228456</v>
+        <v>228.456</v>
       </c>
       <c r="P8">
-        <v>229197</v>
+        <v>229.197</v>
       </c>
       <c r="Q8">
-        <v>228626</v>
+        <v>228.626</v>
       </c>
       <c r="R8">
-        <v>226961</v>
+        <v>226.961</v>
       </c>
       <c r="S8">
-        <v>224325</v>
+        <v>224.325</v>
       </c>
       <c r="T8">
-        <v>220772</v>
+        <v>220.772</v>
       </c>
       <c r="U8">
-        <v>216432</v>
+        <v>216.432</v>
       </c>
       <c r="V8">
-        <v>211422</v>
+        <v>211.422</v>
       </c>
       <c r="W8">
-        <v>205847</v>
+        <v>205.847</v>
       </c>
       <c r="X8">
-        <v>200021</v>
+        <v>200.021</v>
       </c>
       <c r="Y8">
-        <v>194117</v>
+        <v>194.117</v>
       </c>
       <c r="Z8">
-        <v>188295</v>
+        <v>188.295</v>
       </c>
       <c r="AA8">
-        <v>182660</v>
+        <v>182.66</v>
       </c>
     </row>
     <row r="9" spans="1:27">
@@ -1265,70 +1265,70 @@
         <v>66</v>
       </c>
       <c r="F9">
-        <v>23136</v>
+        <v>23.136</v>
       </c>
       <c r="G9">
-        <v>27657</v>
+        <v>27.657</v>
       </c>
       <c r="H9">
-        <v>32216</v>
+        <v>32.216</v>
       </c>
       <c r="I9">
-        <v>33963</v>
+        <v>33.963</v>
       </c>
       <c r="J9">
-        <v>35732</v>
+        <v>35.732</v>
       </c>
       <c r="K9">
-        <v>38155</v>
+        <v>38.155</v>
       </c>
       <c r="L9">
-        <v>38867</v>
+        <v>38.867</v>
       </c>
       <c r="M9">
-        <v>39671</v>
+        <v>39.671</v>
       </c>
       <c r="N9">
-        <v>40419</v>
+        <v>40.419</v>
       </c>
       <c r="O9">
-        <v>41100</v>
+        <v>41.1</v>
       </c>
       <c r="P9">
-        <v>41745</v>
+        <v>41.745</v>
       </c>
       <c r="Q9">
-        <v>42415</v>
+        <v>42.415</v>
       </c>
       <c r="R9">
-        <v>42986</v>
+        <v>42.986</v>
       </c>
       <c r="S9">
-        <v>43524</v>
+        <v>43.524</v>
       </c>
       <c r="T9">
-        <v>44019</v>
+        <v>44.019</v>
       </c>
       <c r="U9">
-        <v>44480</v>
+        <v>44.48</v>
       </c>
       <c r="V9">
-        <v>44859</v>
+        <v>44.859</v>
       </c>
       <c r="W9">
-        <v>45106</v>
+        <v>45.106</v>
       </c>
       <c r="X9">
-        <v>45187</v>
+        <v>45.187</v>
       </c>
       <c r="Y9">
-        <v>45099</v>
+        <v>45.099</v>
       </c>
       <c r="Z9">
-        <v>44874</v>
+        <v>44.874</v>
       </c>
       <c r="AA9">
-        <v>44547</v>
+        <v>44.547</v>
       </c>
     </row>
     <row r="10" spans="1:27">
@@ -1348,70 +1348,70 @@
         <v>66</v>
       </c>
       <c r="F10">
-        <v>45072</v>
+        <v>45.072</v>
       </c>
       <c r="G10">
-        <v>60084</v>
+        <v>60.084</v>
       </c>
       <c r="H10">
-        <v>76123</v>
+        <v>76.123</v>
       </c>
       <c r="I10">
-        <v>81118</v>
+        <v>81.11799999999999</v>
       </c>
       <c r="J10">
-        <v>86189</v>
+        <v>86.18899999999999</v>
       </c>
       <c r="K10">
-        <v>91771</v>
+        <v>91.771</v>
       </c>
       <c r="L10">
-        <v>95375</v>
+        <v>95.375</v>
       </c>
       <c r="M10">
-        <v>99761</v>
+        <v>99.761</v>
       </c>
       <c r="N10">
-        <v>103585</v>
+        <v>103.585</v>
       </c>
       <c r="O10">
-        <v>106763</v>
+        <v>106.763</v>
       </c>
       <c r="P10">
-        <v>109254</v>
+        <v>109.254</v>
       </c>
       <c r="Q10">
-        <v>111080</v>
+        <v>111.08</v>
       </c>
       <c r="R10">
-        <v>112270</v>
+        <v>112.27</v>
       </c>
       <c r="S10">
-        <v>112900</v>
+        <v>112.9</v>
       </c>
       <c r="T10">
-        <v>113102</v>
+        <v>113.102</v>
       </c>
       <c r="U10">
-        <v>112901</v>
+        <v>112.901</v>
       </c>
       <c r="V10">
-        <v>112318</v>
+        <v>112.318</v>
       </c>
       <c r="W10">
-        <v>111367</v>
+        <v>111.367</v>
       </c>
       <c r="X10">
-        <v>110109</v>
+        <v>110.109</v>
       </c>
       <c r="Y10">
-        <v>108612</v>
+        <v>108.612</v>
       </c>
       <c r="Z10">
-        <v>106947</v>
+        <v>106.947</v>
       </c>
       <c r="AA10">
-        <v>105200</v>
+        <v>105.2</v>
       </c>
     </row>
     <row r="11" spans="1:27">
@@ -1431,70 +1431,70 @@
         <v>66</v>
       </c>
       <c r="F11">
-        <v>51627</v>
+        <v>51.627</v>
       </c>
       <c r="G11">
-        <v>69516</v>
+        <v>69.51600000000001</v>
       </c>
       <c r="H11">
-        <v>77462</v>
+        <v>77.462</v>
       </c>
       <c r="I11">
-        <v>82338</v>
+        <v>82.33799999999999</v>
       </c>
       <c r="J11">
-        <v>88469</v>
+        <v>88.46899999999999</v>
       </c>
       <c r="K11">
-        <v>96107</v>
+        <v>96.107</v>
       </c>
       <c r="L11">
-        <v>100959</v>
+        <v>100.959</v>
       </c>
       <c r="M11">
-        <v>106386</v>
+        <v>106.386</v>
       </c>
       <c r="N11">
-        <v>111330</v>
+        <v>111.33</v>
       </c>
       <c r="O11">
-        <v>116062</v>
+        <v>116.062</v>
       </c>
       <c r="P11">
-        <v>120507</v>
+        <v>120.507</v>
       </c>
       <c r="Q11">
-        <v>124395</v>
+        <v>124.395</v>
       </c>
       <c r="R11">
-        <v>127451</v>
+        <v>127.451</v>
       </c>
       <c r="S11">
-        <v>129638</v>
+        <v>129.638</v>
       </c>
       <c r="T11">
-        <v>131189</v>
+        <v>131.189</v>
       </c>
       <c r="U11">
-        <v>132325</v>
+        <v>132.325</v>
       </c>
       <c r="V11">
-        <v>133117</v>
+        <v>133.117</v>
       </c>
       <c r="W11">
-        <v>133580</v>
+        <v>133.58</v>
       </c>
       <c r="X11">
-        <v>133768</v>
+        <v>133.768</v>
       </c>
       <c r="Y11">
-        <v>133722</v>
+        <v>133.722</v>
       </c>
       <c r="Z11">
-        <v>133474</v>
+        <v>133.474</v>
       </c>
       <c r="AA11">
-        <v>132935</v>
+        <v>132.935</v>
       </c>
     </row>
     <row r="12" spans="1:27">
@@ -1514,70 +1514,70 @@
         <v>66</v>
       </c>
       <c r="F12">
-        <v>919823</v>
+        <v>919.823</v>
       </c>
       <c r="G12">
-        <v>1159890</v>
+        <v>1159.89</v>
       </c>
       <c r="H12">
-        <v>1312310</v>
+        <v>1312.31</v>
       </c>
       <c r="I12">
-        <v>1355880</v>
+        <v>1355.88</v>
       </c>
       <c r="J12">
-        <v>1401730</v>
+        <v>1401.73</v>
       </c>
       <c r="K12">
-        <v>1434080</v>
+        <v>1434.08</v>
       </c>
       <c r="L12">
-        <v>1436020</v>
+        <v>1436.02</v>
       </c>
       <c r="M12">
-        <v>1425960</v>
+        <v>1425.96</v>
       </c>
       <c r="N12">
-        <v>1408520</v>
+        <v>1408.52</v>
       </c>
       <c r="O12">
-        <v>1385330</v>
+        <v>1385.33</v>
       </c>
       <c r="P12">
-        <v>1354900</v>
+        <v>1354.9</v>
       </c>
       <c r="Q12">
-        <v>1315550</v>
+        <v>1315.55</v>
       </c>
       <c r="R12">
-        <v>1267040</v>
+        <v>1267.04</v>
       </c>
       <c r="S12">
-        <v>1212540</v>
+        <v>1212.54</v>
       </c>
       <c r="T12">
-        <v>1155930</v>
+        <v>1155.93</v>
       </c>
       <c r="U12">
-        <v>1100670</v>
+        <v>1100.67</v>
       </c>
       <c r="V12">
-        <v>1047540</v>
+        <v>1047.54</v>
       </c>
       <c r="W12">
-        <v>995274</v>
+        <v>995.274</v>
       </c>
       <c r="X12">
-        <v>944011</v>
+        <v>944.011</v>
       </c>
       <c r="Y12">
-        <v>895579</v>
+        <v>895.579</v>
       </c>
       <c r="Z12">
-        <v>850710</v>
+        <v>850.71</v>
       </c>
       <c r="AA12">
-        <v>807888</v>
+        <v>807.888</v>
       </c>
     </row>
     <row r="13" spans="1:27">
@@ -1597,70 +1597,70 @@
         <v>66</v>
       </c>
       <c r="F13">
-        <v>23404</v>
+        <v>23.404</v>
       </c>
       <c r="G13">
-        <v>32601</v>
+        <v>32.601</v>
       </c>
       <c r="H13">
-        <v>42221</v>
+        <v>42.221</v>
       </c>
       <c r="I13">
-        <v>44816</v>
+        <v>44.816</v>
       </c>
       <c r="J13">
-        <v>47120</v>
+        <v>47.12</v>
       </c>
       <c r="K13">
-        <v>51517</v>
+        <v>51.517</v>
       </c>
       <c r="L13">
-        <v>52973</v>
+        <v>52.973</v>
       </c>
       <c r="M13">
-        <v>54767</v>
+        <v>54.767</v>
       </c>
       <c r="N13">
-        <v>56185</v>
+        <v>56.185</v>
       </c>
       <c r="O13">
-        <v>57224</v>
+        <v>57.224</v>
       </c>
       <c r="P13">
-        <v>57879</v>
+        <v>57.879</v>
       </c>
       <c r="Q13">
-        <v>58202</v>
+        <v>58.202</v>
       </c>
       <c r="R13">
-        <v>58246</v>
+        <v>58.246</v>
       </c>
       <c r="S13">
-        <v>58043</v>
+        <v>58.043</v>
       </c>
       <c r="T13">
-        <v>57622</v>
+        <v>57.622</v>
       </c>
       <c r="U13">
-        <v>56990</v>
+        <v>56.99</v>
       </c>
       <c r="V13">
-        <v>56160</v>
+        <v>56.16</v>
       </c>
       <c r="W13">
-        <v>55110</v>
+        <v>55.11</v>
       </c>
       <c r="X13">
-        <v>53912</v>
+        <v>53.912</v>
       </c>
       <c r="Y13">
-        <v>52638</v>
+        <v>52.638</v>
       </c>
       <c r="Z13">
-        <v>51356</v>
+        <v>51.356</v>
       </c>
       <c r="AA13">
-        <v>50132</v>
+        <v>50.132</v>
       </c>
     </row>
     <row r="14" spans="1:27">
@@ -1680,70 +1680,70 @@
         <v>66</v>
       </c>
       <c r="F14">
-        <v>99278</v>
+        <v>99.27800000000001</v>
       </c>
       <c r="G14">
-        <v>106793</v>
+        <v>106.793</v>
       </c>
       <c r="H14">
-        <v>103627</v>
+        <v>103.627</v>
       </c>
       <c r="I14">
-        <v>102551</v>
+        <v>102.551</v>
       </c>
       <c r="J14">
-        <v>101556</v>
+        <v>101.556</v>
       </c>
       <c r="K14">
-        <v>100070</v>
+        <v>100.07</v>
       </c>
       <c r="L14">
-        <v>99797</v>
+        <v>99.797</v>
       </c>
       <c r="M14">
-        <v>97571</v>
+        <v>97.571</v>
       </c>
       <c r="N14">
-        <v>95253</v>
+        <v>95.253</v>
       </c>
       <c r="O14">
-        <v>93009</v>
+        <v>93.009</v>
       </c>
       <c r="P14">
-        <v>90896</v>
+        <v>90.896</v>
       </c>
       <c r="Q14">
-        <v>88951</v>
+        <v>88.95099999999999</v>
       </c>
       <c r="R14">
-        <v>87014</v>
+        <v>87.014</v>
       </c>
       <c r="S14">
-        <v>85002</v>
+        <v>85.002</v>
       </c>
       <c r="T14">
-        <v>82866</v>
+        <v>82.866</v>
       </c>
       <c r="U14">
-        <v>80650</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="V14">
-        <v>78463</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="W14">
-        <v>76413</v>
+        <v>76.413</v>
       </c>
       <c r="X14">
-        <v>74562</v>
+        <v>74.562</v>
       </c>
       <c r="Y14">
-        <v>72919</v>
+        <v>72.919</v>
       </c>
       <c r="Z14">
-        <v>71450</v>
+        <v>71.45</v>
       </c>
       <c r="AA14">
-        <v>70064</v>
+        <v>70.06399999999999</v>
       </c>
     </row>
     <row r="15" spans="1:27">
@@ -1763,70 +1763,70 @@
         <v>66</v>
       </c>
       <c r="F15">
-        <v>349021</v>
+        <v>349.021</v>
       </c>
       <c r="G15">
-        <v>364582</v>
+        <v>364.582</v>
       </c>
       <c r="H15">
-        <v>385538</v>
+        <v>385.538</v>
       </c>
       <c r="I15">
-        <v>396331</v>
+        <v>396.331</v>
       </c>
       <c r="J15">
-        <v>402736</v>
+        <v>402.736</v>
       </c>
       <c r="K15">
-        <v>408854</v>
+        <v>408.854</v>
       </c>
       <c r="L15">
-        <v>410634</v>
+        <v>410.634</v>
       </c>
       <c r="M15">
-        <v>411504</v>
+        <v>411.504</v>
       </c>
       <c r="N15">
-        <v>412591</v>
+        <v>412.591</v>
       </c>
       <c r="O15">
-        <v>414029</v>
+        <v>414.029</v>
       </c>
       <c r="P15">
-        <v>415710</v>
+        <v>415.71</v>
       </c>
       <c r="Q15">
-        <v>417510</v>
+        <v>417.51</v>
       </c>
       <c r="R15">
-        <v>418293</v>
+        <v>418.293</v>
       </c>
       <c r="S15">
-        <v>418305</v>
+        <v>418.305</v>
       </c>
       <c r="T15">
-        <v>417695</v>
+        <v>417.695</v>
       </c>
       <c r="U15">
-        <v>417065</v>
+        <v>417.065</v>
       </c>
       <c r="V15">
-        <v>416598</v>
+        <v>416.598</v>
       </c>
       <c r="W15">
-        <v>416059</v>
+        <v>416.059</v>
       </c>
       <c r="X15">
-        <v>415069</v>
+        <v>415.069</v>
       </c>
       <c r="Y15">
-        <v>413414</v>
+        <v>413.414</v>
       </c>
       <c r="Z15">
-        <v>411070</v>
+        <v>411.07</v>
       </c>
       <c r="AA15">
-        <v>407982</v>
+        <v>407.982</v>
       </c>
     </row>
     <row r="16" spans="1:27">
@@ -1846,70 +1846,70 @@
         <v>66</v>
       </c>
       <c r="F16">
-        <v>75560</v>
+        <v>75.56</v>
       </c>
       <c r="G16">
-        <v>94514</v>
+        <v>94.514</v>
       </c>
       <c r="H16">
-        <v>106565</v>
+        <v>106.565</v>
       </c>
       <c r="I16">
-        <v>109869</v>
+        <v>109.869</v>
       </c>
       <c r="J16">
-        <v>115306</v>
+        <v>115.306</v>
       </c>
       <c r="K16">
-        <v>119291</v>
+        <v>119.291</v>
       </c>
       <c r="L16">
-        <v>121192</v>
+        <v>121.192</v>
       </c>
       <c r="M16">
-        <v>123331</v>
+        <v>123.331</v>
       </c>
       <c r="N16">
-        <v>124895</v>
+        <v>124.895</v>
       </c>
       <c r="O16">
-        <v>126023</v>
+        <v>126.023</v>
       </c>
       <c r="P16">
-        <v>126722</v>
+        <v>126.722</v>
       </c>
       <c r="Q16">
-        <v>126858</v>
+        <v>126.858</v>
       </c>
       <c r="R16">
-        <v>126435</v>
+        <v>126.435</v>
       </c>
       <c r="S16">
-        <v>125434</v>
+        <v>125.434</v>
       </c>
       <c r="T16">
-        <v>123993</v>
+        <v>123.993</v>
       </c>
       <c r="U16">
-        <v>122254</v>
+        <v>122.254</v>
       </c>
       <c r="V16">
-        <v>120290</v>
+        <v>120.29</v>
       </c>
       <c r="W16">
-        <v>118143</v>
+        <v>118.143</v>
       </c>
       <c r="X16">
-        <v>115856</v>
+        <v>115.856</v>
       </c>
       <c r="Y16">
-        <v>113482</v>
+        <v>113.482</v>
       </c>
       <c r="Z16">
-        <v>111055</v>
+        <v>111.055</v>
       </c>
       <c r="AA16">
-        <v>108574</v>
+        <v>108.574</v>
       </c>
     </row>
     <row r="17" spans="1:27">
@@ -1929,70 +1929,70 @@
         <v>66</v>
       </c>
       <c r="F17">
-        <v>10587</v>
+        <v>10.587</v>
       </c>
       <c r="G17">
-        <v>11237</v>
+        <v>11.237</v>
       </c>
       <c r="H17">
-        <v>12384</v>
+        <v>12.384</v>
       </c>
       <c r="I17">
-        <v>13066</v>
+        <v>13.066</v>
       </c>
       <c r="J17">
-        <v>13841</v>
+        <v>13.841</v>
       </c>
       <c r="K17">
-        <v>14504</v>
+        <v>14.504</v>
       </c>
       <c r="L17">
-        <v>14820</v>
+        <v>14.82</v>
       </c>
       <c r="M17">
-        <v>15119</v>
+        <v>15.119</v>
       </c>
       <c r="N17">
-        <v>15401</v>
+        <v>15.401</v>
       </c>
       <c r="O17">
-        <v>15680</v>
+        <v>15.68</v>
       </c>
       <c r="P17">
-        <v>15970</v>
+        <v>15.97</v>
       </c>
       <c r="Q17">
-        <v>16286</v>
+        <v>16.286</v>
       </c>
       <c r="R17">
-        <v>16562</v>
+        <v>16.562</v>
       </c>
       <c r="S17">
-        <v>16799</v>
+        <v>16.799</v>
       </c>
       <c r="T17">
-        <v>16992</v>
+        <v>16.992</v>
       </c>
       <c r="U17">
-        <v>17165</v>
+        <v>17.165</v>
       </c>
       <c r="V17">
-        <v>17326</v>
+        <v>17.326</v>
       </c>
       <c r="W17">
-        <v>17458</v>
+        <v>17.458</v>
       </c>
       <c r="X17">
-        <v>17542</v>
+        <v>17.542</v>
       </c>
       <c r="Y17">
-        <v>17574</v>
+        <v>17.574</v>
       </c>
       <c r="Z17">
-        <v>17566</v>
+        <v>17.566</v>
       </c>
       <c r="AA17">
-        <v>17526</v>
+        <v>17.526</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -2012,70 +2012,70 @@
         <v>66</v>
       </c>
       <c r="F18">
-        <v>623524</v>
+        <v>623.524</v>
       </c>
       <c r="G18">
-        <v>870452</v>
+        <v>870.452</v>
       </c>
       <c r="H18">
-        <v>1154640</v>
+        <v>1154.64</v>
       </c>
       <c r="I18">
-        <v>1240610</v>
+        <v>1240.61</v>
       </c>
       <c r="J18">
-        <v>1322870</v>
+        <v>1322.87</v>
       </c>
       <c r="K18">
-        <v>1407560</v>
+        <v>1407.56</v>
       </c>
       <c r="L18">
-        <v>1452180</v>
+        <v>1452.18</v>
       </c>
       <c r="M18">
-        <v>1508690</v>
+        <v>1508.69</v>
       </c>
       <c r="N18">
-        <v>1555240</v>
+        <v>1555.24</v>
       </c>
       <c r="O18">
-        <v>1591030</v>
+        <v>1591.03</v>
       </c>
       <c r="P18">
-        <v>1615150</v>
+        <v>1615.15</v>
       </c>
       <c r="Q18">
-        <v>1627870</v>
+        <v>1627.87</v>
       </c>
       <c r="R18">
-        <v>1632600</v>
+        <v>1632.6</v>
       </c>
       <c r="S18">
-        <v>1630090</v>
+        <v>1630.09</v>
       </c>
       <c r="T18">
-        <v>1619620</v>
+        <v>1619.62</v>
       </c>
       <c r="U18">
-        <v>1602070</v>
+        <v>1602.07</v>
       </c>
       <c r="V18">
-        <v>1577300</v>
+        <v>1577.3</v>
       </c>
       <c r="W18">
-        <v>1546630</v>
+        <v>1546.63</v>
       </c>
       <c r="X18">
-        <v>1511960</v>
+        <v>1511.96</v>
       </c>
       <c r="Y18">
-        <v>1475070</v>
+        <v>1475.07</v>
       </c>
       <c r="Z18">
-        <v>1436800</v>
+        <v>1436.8</v>
       </c>
       <c r="AA18">
-        <v>1398060</v>
+        <v>1398.06</v>
       </c>
     </row>
     <row r="19" spans="1:27">
@@ -2095,70 +2095,70 @@
         <v>66</v>
       </c>
       <c r="F19">
-        <v>131213</v>
+        <v>131.213</v>
       </c>
       <c r="G19">
-        <v>182160</v>
+        <v>182.16</v>
       </c>
       <c r="H19">
-        <v>228805</v>
+        <v>228.805</v>
       </c>
       <c r="I19">
-        <v>244016</v>
+        <v>244.016</v>
       </c>
       <c r="J19">
-        <v>259092</v>
+        <v>259.092</v>
       </c>
       <c r="K19">
-        <v>273753</v>
+        <v>273.753</v>
       </c>
       <c r="L19">
-        <v>281674</v>
+        <v>281.674</v>
       </c>
       <c r="M19">
-        <v>291598</v>
+        <v>291.598</v>
       </c>
       <c r="N19">
-        <v>299683</v>
+        <v>299.683</v>
       </c>
       <c r="O19">
-        <v>305698</v>
+        <v>305.698</v>
       </c>
       <c r="P19">
-        <v>309677</v>
+        <v>309.677</v>
       </c>
       <c r="Q19">
-        <v>311687</v>
+        <v>311.687</v>
       </c>
       <c r="R19">
-        <v>312298</v>
+        <v>312.298</v>
       </c>
       <c r="S19">
-        <v>311593</v>
+        <v>311.593</v>
       </c>
       <c r="T19">
-        <v>309739</v>
+        <v>309.739</v>
       </c>
       <c r="U19">
-        <v>306900</v>
+        <v>306.9</v>
       </c>
       <c r="V19">
-        <v>303234</v>
+        <v>303.234</v>
       </c>
       <c r="W19">
-        <v>298700</v>
+        <v>298.7</v>
       </c>
       <c r="X19">
-        <v>293422</v>
+        <v>293.422</v>
       </c>
       <c r="Y19">
-        <v>287519</v>
+        <v>287.519</v>
       </c>
       <c r="Z19">
-        <v>281099</v>
+        <v>281.099</v>
       </c>
       <c r="AA19">
-        <v>274310</v>
+        <v>274.31</v>
       </c>
     </row>
     <row r="20" spans="1:27">
@@ -2178,70 +2178,70 @@
         <v>66</v>
       </c>
       <c r="F20">
-        <v>112412</v>
+        <v>112.412</v>
       </c>
       <c r="G20">
-        <v>123686</v>
+        <v>123.686</v>
       </c>
       <c r="H20">
-        <v>127798</v>
+        <v>127.798</v>
       </c>
       <c r="I20">
-        <v>128105</v>
+        <v>128.105</v>
       </c>
       <c r="J20">
-        <v>127251</v>
+        <v>127.251</v>
       </c>
       <c r="K20">
-        <v>124613</v>
+        <v>124.613</v>
       </c>
       <c r="L20">
-        <v>122163</v>
+        <v>122.163</v>
       </c>
       <c r="M20">
-        <v>119046</v>
+        <v>119.046</v>
       </c>
       <c r="N20">
-        <v>115757</v>
+        <v>115.757</v>
       </c>
       <c r="O20">
-        <v>112381</v>
+        <v>112.381</v>
       </c>
       <c r="P20">
-        <v>108986</v>
+        <v>108.986</v>
       </c>
       <c r="Q20">
-        <v>105713</v>
+        <v>105.713</v>
       </c>
       <c r="R20">
-        <v>102592</v>
+        <v>102.592</v>
       </c>
       <c r="S20">
-        <v>99481</v>
+        <v>99.48099999999999</v>
       </c>
       <c r="T20">
-        <v>96196</v>
+        <v>96.196</v>
       </c>
       <c r="U20">
-        <v>92719</v>
+        <v>92.71899999999999</v>
       </c>
       <c r="V20">
-        <v>89209</v>
+        <v>89.209</v>
       </c>
       <c r="W20">
-        <v>85930</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="X20">
-        <v>82962</v>
+        <v>82.962</v>
       </c>
       <c r="Y20">
-        <v>80209</v>
+        <v>80.209</v>
       </c>
       <c r="Z20">
-        <v>77538</v>
+        <v>77.538</v>
       </c>
       <c r="AA20">
-        <v>74851</v>
+        <v>74.851</v>
       </c>
     </row>
     <row r="21" spans="1:27">
@@ -2261,70 +2261,70 @@
         <v>66</v>
       </c>
       <c r="F21">
-        <v>58692</v>
+        <v>58.692</v>
       </c>
       <c r="G21">
-        <v>81720</v>
+        <v>81.72</v>
       </c>
       <c r="H21">
-        <v>105442</v>
+        <v>105.442</v>
       </c>
       <c r="I21">
-        <v>112532</v>
+        <v>112.532</v>
       </c>
       <c r="J21">
-        <v>120150</v>
+        <v>120.15</v>
       </c>
       <c r="K21">
-        <v>126705</v>
+        <v>126.705</v>
       </c>
       <c r="L21">
-        <v>130549</v>
+        <v>130.549</v>
       </c>
       <c r="M21">
-        <v>135763</v>
+        <v>135.763</v>
       </c>
       <c r="N21">
-        <v>140375</v>
+        <v>140.375</v>
       </c>
       <c r="O21">
-        <v>144253</v>
+        <v>144.253</v>
       </c>
       <c r="P21">
-        <v>147313</v>
+        <v>147.313</v>
       </c>
       <c r="Q21">
-        <v>149577</v>
+        <v>149.577</v>
       </c>
       <c r="R21">
-        <v>151213</v>
+        <v>151.213</v>
       </c>
       <c r="S21">
-        <v>152237</v>
+        <v>152.237</v>
       </c>
       <c r="T21">
-        <v>152739</v>
+        <v>152.739</v>
       </c>
       <c r="U21">
-        <v>152757</v>
+        <v>152.757</v>
       </c>
       <c r="V21">
-        <v>152317</v>
+        <v>152.317</v>
       </c>
       <c r="W21">
-        <v>151500</v>
+        <v>151.5</v>
       </c>
       <c r="X21">
-        <v>150391</v>
+        <v>150.391</v>
       </c>
       <c r="Y21">
-        <v>149048</v>
+        <v>149.048</v>
       </c>
       <c r="Z21">
-        <v>147567</v>
+        <v>147.567</v>
       </c>
       <c r="AA21">
-        <v>145892</v>
+        <v>145.892</v>
       </c>
     </row>
     <row r="22" spans="1:27">
@@ -2344,70 +2344,70 @@
         <v>66</v>
       </c>
       <c r="F22">
-        <v>79862</v>
+        <v>79.86199999999999</v>
       </c>
       <c r="G22">
-        <v>135582</v>
+        <v>135.582</v>
       </c>
       <c r="H22">
-        <v>194542</v>
+        <v>194.542</v>
       </c>
       <c r="I22">
-        <v>223614</v>
+        <v>223.614</v>
       </c>
       <c r="J22">
-        <v>249200</v>
+        <v>249.2</v>
       </c>
       <c r="K22">
-        <v>274775</v>
+        <v>274.775</v>
       </c>
       <c r="L22">
-        <v>291874</v>
+        <v>291.874</v>
       </c>
       <c r="M22">
-        <v>312900</v>
+        <v>312.9</v>
       </c>
       <c r="N22">
-        <v>332850</v>
+        <v>332.85</v>
       </c>
       <c r="O22">
-        <v>351568</v>
+        <v>351.568</v>
       </c>
       <c r="P22">
-        <v>368684</v>
+        <v>368.684</v>
       </c>
       <c r="Q22">
-        <v>383644</v>
+        <v>383.644</v>
       </c>
       <c r="R22">
-        <v>396282</v>
+        <v>396.282</v>
       </c>
       <c r="S22">
-        <v>406366</v>
+        <v>406.366</v>
       </c>
       <c r="T22">
-        <v>413733</v>
+        <v>413.733</v>
       </c>
       <c r="U22">
-        <v>418612</v>
+        <v>418.612</v>
       </c>
       <c r="V22">
-        <v>421392</v>
+        <v>421.392</v>
       </c>
       <c r="W22">
-        <v>422509</v>
+        <v>422.509</v>
       </c>
       <c r="X22">
-        <v>422396</v>
+        <v>422.396</v>
       </c>
       <c r="Y22">
-        <v>421369</v>
+        <v>421.369</v>
       </c>
       <c r="Z22">
-        <v>419452</v>
+        <v>419.452</v>
       </c>
       <c r="AA22">
-        <v>416522</v>
+        <v>416.522</v>
       </c>
     </row>
     <row r="23" spans="1:27">
@@ -2427,70 +2427,70 @@
         <v>66</v>
       </c>
       <c r="F23">
-        <v>68127</v>
+        <v>68.127</v>
       </c>
       <c r="G23">
-        <v>115414</v>
+        <v>115.414</v>
       </c>
       <c r="H23">
-        <v>174372</v>
+        <v>174.372</v>
       </c>
       <c r="I23">
-        <v>194454</v>
+        <v>194.454</v>
       </c>
       <c r="J23">
-        <v>210969</v>
+        <v>210.969</v>
       </c>
       <c r="K23">
-        <v>231402</v>
+        <v>231.402</v>
       </c>
       <c r="L23">
-        <v>250417</v>
+        <v>250.417</v>
       </c>
       <c r="M23">
-        <v>275485</v>
+        <v>275.485</v>
       </c>
       <c r="N23">
-        <v>300884</v>
+        <v>300.884</v>
       </c>
       <c r="O23">
-        <v>325815</v>
+        <v>325.815</v>
       </c>
       <c r="P23">
-        <v>349828</v>
+        <v>349.828</v>
       </c>
       <c r="Q23">
-        <v>373012</v>
+        <v>373.012</v>
       </c>
       <c r="R23">
-        <v>394733</v>
+        <v>394.733</v>
       </c>
       <c r="S23">
-        <v>414935</v>
+        <v>414.935</v>
       </c>
       <c r="T23">
-        <v>432883</v>
+        <v>432.883</v>
       </c>
       <c r="U23">
-        <v>448387</v>
+        <v>448.387</v>
       </c>
       <c r="V23">
-        <v>461249</v>
+        <v>461.249</v>
       </c>
       <c r="W23">
-        <v>471456</v>
+        <v>471.456</v>
       </c>
       <c r="X23">
-        <v>479585</v>
+        <v>479.585</v>
       </c>
       <c r="Y23">
-        <v>486094</v>
+        <v>486.094</v>
       </c>
       <c r="Z23">
-        <v>491096</v>
+        <v>491.096</v>
       </c>
       <c r="AA23">
-        <v>494804</v>
+        <v>494.804</v>
       </c>
     </row>
     <row r="24" spans="1:27">
@@ -2510,70 +2510,70 @@
         <v>66</v>
       </c>
       <c r="F24">
-        <v>133842</v>
+        <v>133.842</v>
       </c>
       <c r="G24">
-        <v>148006</v>
+        <v>148.006</v>
       </c>
       <c r="H24">
-        <v>143800</v>
+        <v>143.8</v>
       </c>
       <c r="I24">
-        <v>143243</v>
+        <v>143.243</v>
       </c>
       <c r="J24">
-        <v>144668</v>
+        <v>144.668</v>
       </c>
       <c r="K24">
-        <v>145103</v>
+        <v>145.103</v>
       </c>
       <c r="L24">
-        <v>144791</v>
+        <v>144.791</v>
       </c>
       <c r="M24">
-        <v>142828</v>
+        <v>142.828</v>
       </c>
       <c r="N24">
-        <v>141003</v>
+        <v>141.003</v>
       </c>
       <c r="O24">
-        <v>139631</v>
+        <v>139.631</v>
       </c>
       <c r="P24">
-        <v>138777</v>
+        <v>138.777</v>
       </c>
       <c r="Q24">
-        <v>138203</v>
+        <v>138.203</v>
       </c>
       <c r="R24">
-        <v>137419</v>
+        <v>137.419</v>
       </c>
       <c r="S24">
-        <v>136396</v>
+        <v>136.396</v>
       </c>
       <c r="T24">
-        <v>135082</v>
+        <v>135.082</v>
       </c>
       <c r="U24">
-        <v>133644</v>
+        <v>133.644</v>
       </c>
       <c r="V24">
-        <v>132204</v>
+        <v>132.204</v>
       </c>
       <c r="W24">
-        <v>130793</v>
+        <v>130.793</v>
       </c>
       <c r="X24">
-        <v>129417</v>
+        <v>129.417</v>
       </c>
       <c r="Y24">
-        <v>128031</v>
+        <v>128.031</v>
       </c>
       <c r="Z24">
-        <v>126538</v>
+        <v>126.538</v>
       </c>
       <c r="AA24">
-        <v>124773</v>
+        <v>124.773</v>
       </c>
     </row>
     <row r="25" spans="1:27">
@@ -2593,70 +2593,70 @@
         <v>66</v>
       </c>
       <c r="F25">
-        <v>25778</v>
+        <v>25.778</v>
       </c>
       <c r="G25">
-        <v>39878</v>
+        <v>39.878</v>
       </c>
       <c r="H25">
-        <v>49017</v>
+        <v>49.017</v>
       </c>
       <c r="I25">
-        <v>51785</v>
+        <v>51.785</v>
       </c>
       <c r="J25">
-        <v>55877</v>
+        <v>55.877</v>
       </c>
       <c r="K25">
-        <v>59392</v>
+        <v>59.392</v>
       </c>
       <c r="L25">
-        <v>61298</v>
+        <v>61.298</v>
       </c>
       <c r="M25">
-        <v>63764</v>
+        <v>63.764</v>
       </c>
       <c r="N25">
-        <v>65756</v>
+        <v>65.756</v>
       </c>
       <c r="O25">
-        <v>67295</v>
+        <v>67.295</v>
       </c>
       <c r="P25">
-        <v>68384</v>
+        <v>68.384</v>
       </c>
       <c r="Q25">
-        <v>68949</v>
+        <v>68.949</v>
       </c>
       <c r="R25">
-        <v>69100</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="S25">
-        <v>68882</v>
+        <v>68.88200000000001</v>
       </c>
       <c r="T25">
-        <v>68358</v>
+        <v>68.358</v>
       </c>
       <c r="U25">
-        <v>67546</v>
+        <v>67.54600000000001</v>
       </c>
       <c r="V25">
-        <v>66500</v>
+        <v>66.5</v>
       </c>
       <c r="W25">
-        <v>65238</v>
+        <v>65.238</v>
       </c>
       <c r="X25">
-        <v>63870</v>
+        <v>63.87</v>
       </c>
       <c r="Y25">
-        <v>62414</v>
+        <v>62.414</v>
       </c>
       <c r="Z25">
-        <v>60874</v>
+        <v>60.874</v>
       </c>
       <c r="AA25">
-        <v>59263</v>
+        <v>59.263</v>
       </c>
     </row>
     <row r="26" spans="1:27">
@@ -2676,70 +2676,70 @@
         <v>66</v>
       </c>
       <c r="F26">
-        <v>14368</v>
+        <v>14.368</v>
       </c>
       <c r="G26">
-        <v>21024</v>
+        <v>21.024</v>
       </c>
       <c r="H26">
-        <v>28146</v>
+        <v>28.146</v>
       </c>
       <c r="I26">
-        <v>30237</v>
+        <v>30.237</v>
       </c>
       <c r="J26">
-        <v>32117</v>
+        <v>32.117</v>
       </c>
       <c r="K26">
-        <v>29915</v>
+        <v>29.915</v>
       </c>
       <c r="L26">
-        <v>30883</v>
+        <v>30.883</v>
       </c>
       <c r="M26">
-        <v>32176</v>
+        <v>32.176</v>
       </c>
       <c r="N26">
-        <v>33358</v>
+        <v>33.358</v>
       </c>
       <c r="O26">
-        <v>34335</v>
+        <v>34.335</v>
       </c>
       <c r="P26">
-        <v>35092</v>
+        <v>35.092</v>
       </c>
       <c r="Q26">
-        <v>35657</v>
+        <v>35.657</v>
       </c>
       <c r="R26">
-        <v>36096</v>
+        <v>36.096</v>
       </c>
       <c r="S26">
-        <v>36437</v>
+        <v>36.437</v>
       </c>
       <c r="T26">
-        <v>36669</v>
+        <v>36.669</v>
       </c>
       <c r="U26">
-        <v>36799</v>
+        <v>36.799</v>
       </c>
       <c r="V26">
-        <v>36837</v>
+        <v>36.837</v>
       </c>
       <c r="W26">
-        <v>36791</v>
+        <v>36.791</v>
       </c>
       <c r="X26">
-        <v>36672</v>
+        <v>36.672</v>
       </c>
       <c r="Y26">
-        <v>36467</v>
+        <v>36.467</v>
       </c>
       <c r="Z26">
-        <v>36154</v>
+        <v>36.154</v>
       </c>
       <c r="AA26">
-        <v>35732</v>
+        <v>35.732</v>
       </c>
     </row>
     <row r="27" spans="1:27">
@@ -2759,70 +2759,70 @@
         <v>66</v>
       </c>
       <c r="F27">
-        <v>43901</v>
+        <v>43.901</v>
       </c>
       <c r="G27">
-        <v>60174</v>
+        <v>60.174</v>
       </c>
       <c r="H27">
-        <v>76265</v>
+        <v>76.265</v>
       </c>
       <c r="I27">
-        <v>80568</v>
+        <v>80.568</v>
       </c>
       <c r="J27">
-        <v>85449</v>
+        <v>85.449</v>
       </c>
       <c r="K27">
-        <v>93216</v>
+        <v>93.21599999999999</v>
       </c>
       <c r="L27">
-        <v>96383</v>
+        <v>96.383</v>
       </c>
       <c r="M27">
-        <v>100364</v>
+        <v>100.364</v>
       </c>
       <c r="N27">
-        <v>103774</v>
+        <v>103.774</v>
       </c>
       <c r="O27">
-        <v>106510</v>
+        <v>106.51</v>
       </c>
       <c r="P27">
-        <v>108630</v>
+        <v>108.63</v>
       </c>
       <c r="Q27">
-        <v>110157</v>
+        <v>110.157</v>
       </c>
       <c r="R27">
-        <v>111101</v>
+        <v>111.101</v>
       </c>
       <c r="S27">
-        <v>111493</v>
+        <v>111.493</v>
       </c>
       <c r="T27">
-        <v>111412</v>
+        <v>111.412</v>
       </c>
       <c r="U27">
-        <v>110905</v>
+        <v>110.905</v>
       </c>
       <c r="V27">
-        <v>109998</v>
+        <v>109.998</v>
       </c>
       <c r="W27">
-        <v>108712</v>
+        <v>108.712</v>
       </c>
       <c r="X27">
-        <v>107122</v>
+        <v>107.122</v>
       </c>
       <c r="Y27">
-        <v>105308</v>
+        <v>105.308</v>
       </c>
       <c r="Z27">
-        <v>103343</v>
+        <v>103.343</v>
       </c>
       <c r="AA27">
-        <v>101300</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="28" spans="1:27">
@@ -2842,70 +2842,70 @@
         <v>66</v>
       </c>
       <c r="F28">
-        <v>114942</v>
+        <v>114.942</v>
       </c>
       <c r="G28">
-        <v>155446</v>
+        <v>155.446</v>
       </c>
       <c r="H28">
-        <v>212253</v>
+        <v>212.253</v>
       </c>
       <c r="I28">
-        <v>225478</v>
+        <v>225.478</v>
       </c>
       <c r="J28">
-        <v>241709</v>
+        <v>241.709</v>
       </c>
       <c r="K28">
-        <v>262563</v>
+        <v>262.563</v>
       </c>
       <c r="L28">
-        <v>276432</v>
+        <v>276.432</v>
       </c>
       <c r="M28">
-        <v>292514</v>
+        <v>292.514</v>
       </c>
       <c r="N28">
-        <v>306644</v>
+        <v>306.644</v>
       </c>
       <c r="O28">
-        <v>318867</v>
+        <v>318.867</v>
       </c>
       <c r="P28">
-        <v>329242</v>
+        <v>329.242</v>
       </c>
       <c r="Q28">
-        <v>337852</v>
+        <v>337.852</v>
       </c>
       <c r="R28">
-        <v>344738</v>
+        <v>344.738</v>
       </c>
       <c r="S28">
-        <v>349742</v>
+        <v>349.742</v>
       </c>
       <c r="T28">
-        <v>353011</v>
+        <v>353.011</v>
       </c>
       <c r="U28">
-        <v>354526</v>
+        <v>354.526</v>
       </c>
       <c r="V28">
-        <v>354414</v>
+        <v>354.414</v>
       </c>
       <c r="W28">
-        <v>352723</v>
+        <v>352.723</v>
       </c>
       <c r="X28">
-        <v>349561</v>
+        <v>349.561</v>
       </c>
       <c r="Y28">
-        <v>345333</v>
+        <v>345.333</v>
       </c>
       <c r="Z28">
-        <v>340346</v>
+        <v>340.346</v>
       </c>
       <c r="AA28">
-        <v>334952</v>
+        <v>334.952</v>
       </c>
     </row>
     <row r="29" spans="1:27">
@@ -2925,70 +2925,70 @@
         <v>66</v>
       </c>
       <c r="F29">
-        <v>35931</v>
+        <v>35.931</v>
       </c>
       <c r="G29">
-        <v>44120</v>
+        <v>44.12</v>
       </c>
       <c r="H29">
-        <v>47890</v>
+        <v>47.89</v>
       </c>
       <c r="I29">
-        <v>48813</v>
+        <v>48.813</v>
       </c>
       <c r="J29">
-        <v>50994</v>
+        <v>50.994</v>
       </c>
       <c r="K29">
-        <v>51830</v>
+        <v>51.83</v>
       </c>
       <c r="L29">
-        <v>51544</v>
+        <v>51.544</v>
       </c>
       <c r="M29">
-        <v>51024</v>
+        <v>51.024</v>
       </c>
       <c r="N29">
-        <v>50296</v>
+        <v>50.296</v>
       </c>
       <c r="O29">
-        <v>49268</v>
+        <v>49.268</v>
       </c>
       <c r="P29">
-        <v>47962</v>
+        <v>47.962</v>
       </c>
       <c r="Q29">
-        <v>46502</v>
+        <v>46.502</v>
       </c>
       <c r="R29">
-        <v>44655</v>
+        <v>44.655</v>
       </c>
       <c r="S29">
-        <v>42510</v>
+        <v>42.51</v>
       </c>
       <c r="T29">
-        <v>40305</v>
+        <v>40.305</v>
       </c>
       <c r="U29">
-        <v>38185</v>
+        <v>38.185</v>
       </c>
       <c r="V29">
-        <v>36179</v>
+        <v>36.179</v>
       </c>
       <c r="W29">
-        <v>34280</v>
+        <v>34.28</v>
       </c>
       <c r="X29">
-        <v>32496</v>
+        <v>32.496</v>
       </c>
       <c r="Y29">
-        <v>30774</v>
+        <v>30.774</v>
       </c>
       <c r="Z29">
-        <v>29094</v>
+        <v>29.094</v>
       </c>
       <c r="AA29">
-        <v>27531</v>
+        <v>27.531</v>
       </c>
     </row>
     <row r="30" spans="1:27">
@@ -3008,70 +3008,70 @@
         <v>66</v>
       </c>
       <c r="F30">
-        <v>206339</v>
+        <v>206.339</v>
       </c>
       <c r="G30">
-        <v>285832</v>
+        <v>285.832</v>
       </c>
       <c r="H30">
-        <v>367521</v>
+        <v>367.521</v>
       </c>
       <c r="I30">
-        <v>391477</v>
+        <v>391.477</v>
       </c>
       <c r="J30">
-        <v>415139</v>
+        <v>415.139</v>
       </c>
       <c r="K30">
-        <v>441867</v>
+        <v>441.867</v>
       </c>
       <c r="L30">
-        <v>457865</v>
+        <v>457.865</v>
       </c>
       <c r="M30">
-        <v>475348</v>
+        <v>475.348</v>
       </c>
       <c r="N30">
-        <v>489662</v>
+        <v>489.662</v>
       </c>
       <c r="O30">
-        <v>500899</v>
+        <v>500.899</v>
       </c>
       <c r="P30">
-        <v>509310</v>
+        <v>509.31</v>
       </c>
       <c r="Q30">
-        <v>515076</v>
+        <v>515.076</v>
       </c>
       <c r="R30">
-        <v>518208</v>
+        <v>518.208</v>
       </c>
       <c r="S30">
-        <v>518721</v>
+        <v>518.721</v>
       </c>
       <c r="T30">
-        <v>517076</v>
+        <v>517.076</v>
       </c>
       <c r="U30">
-        <v>513698</v>
+        <v>513.698</v>
       </c>
       <c r="V30">
-        <v>508698</v>
+        <v>508.698</v>
       </c>
       <c r="W30">
-        <v>502372</v>
+        <v>502.372</v>
       </c>
       <c r="X30">
-        <v>494746</v>
+        <v>494.746</v>
       </c>
       <c r="Y30">
-        <v>486142</v>
+        <v>486.142</v>
       </c>
       <c r="Z30">
-        <v>476885</v>
+        <v>476.885</v>
       </c>
       <c r="AA30">
-        <v>467257</v>
+        <v>467.257</v>
       </c>
     </row>
     <row r="31" spans="1:27">
@@ -3091,70 +3091,70 @@
         <v>66</v>
       </c>
       <c r="F31">
-        <v>16552</v>
+        <v>16.552</v>
       </c>
       <c r="G31">
-        <v>20586</v>
+        <v>20.586</v>
       </c>
       <c r="H31">
-        <v>22796</v>
+        <v>22.796</v>
       </c>
       <c r="I31">
-        <v>23083</v>
+        <v>23.083</v>
       </c>
       <c r="J31">
-        <v>23512</v>
+        <v>23.512</v>
       </c>
       <c r="K31">
-        <v>23860</v>
+        <v>23.86</v>
       </c>
       <c r="L31">
-        <v>23607</v>
+        <v>23.607</v>
       </c>
       <c r="M31">
-        <v>23197</v>
+        <v>23.197</v>
       </c>
       <c r="N31">
-        <v>22659</v>
+        <v>22.659</v>
       </c>
       <c r="O31">
-        <v>21953</v>
+        <v>21.953</v>
       </c>
       <c r="P31">
-        <v>21117</v>
+        <v>21.117</v>
       </c>
       <c r="Q31">
-        <v>20222</v>
+        <v>20.222</v>
       </c>
       <c r="R31">
-        <v>19244</v>
+        <v>19.244</v>
       </c>
       <c r="S31">
-        <v>18244</v>
+        <v>18.244</v>
       </c>
       <c r="T31">
-        <v>17274</v>
+        <v>17.274</v>
       </c>
       <c r="U31">
-        <v>16332</v>
+        <v>16.332</v>
       </c>
       <c r="V31">
-        <v>15431</v>
+        <v>15.431</v>
       </c>
       <c r="W31">
-        <v>14604</v>
+        <v>14.604</v>
       </c>
       <c r="X31">
-        <v>13868</v>
+        <v>13.868</v>
       </c>
       <c r="Y31">
-        <v>13219</v>
+        <v>13.219</v>
       </c>
       <c r="Z31">
-        <v>12652</v>
+        <v>12.652</v>
       </c>
       <c r="AA31">
-        <v>12153</v>
+        <v>12.153</v>
       </c>
     </row>
     <row r="32" spans="1:27">
@@ -3174,70 +3174,70 @@
         <v>66</v>
       </c>
       <c r="F32">
-        <v>214328</v>
+        <v>214.328</v>
       </c>
       <c r="G32">
-        <v>251728</v>
+        <v>251.728</v>
       </c>
       <c r="H32">
-        <v>300755</v>
+        <v>300.755</v>
       </c>
       <c r="I32">
-        <v>315007</v>
+        <v>315.007</v>
       </c>
       <c r="J32">
-        <v>328208</v>
+        <v>328.208</v>
       </c>
       <c r="K32">
-        <v>340354</v>
+        <v>340.354</v>
       </c>
       <c r="L32">
-        <v>345517</v>
+        <v>345.517</v>
       </c>
       <c r="M32">
-        <v>353058</v>
+        <v>353.058</v>
       </c>
       <c r="N32">
-        <v>360456</v>
+        <v>360.456</v>
       </c>
       <c r="O32">
-        <v>367421</v>
+        <v>367.421</v>
       </c>
       <c r="P32">
-        <v>373815</v>
+        <v>373.815</v>
       </c>
       <c r="Q32">
-        <v>379824</v>
+        <v>379.824</v>
       </c>
       <c r="R32">
-        <v>384968</v>
+        <v>384.968</v>
       </c>
       <c r="S32">
-        <v>389941</v>
+        <v>389.941</v>
       </c>
       <c r="T32">
-        <v>394779</v>
+        <v>394.779</v>
       </c>
       <c r="U32">
-        <v>399435</v>
+        <v>399.435</v>
       </c>
       <c r="V32">
-        <v>403542</v>
+        <v>403.542</v>
       </c>
       <c r="W32">
-        <v>406575</v>
+        <v>406.575</v>
       </c>
       <c r="X32">
-        <v>408306</v>
+        <v>408.306</v>
       </c>
       <c r="Y32">
-        <v>408854</v>
+        <v>408.854</v>
       </c>
       <c r="Z32">
-        <v>408567</v>
+        <v>408.567</v>
       </c>
       <c r="AA32">
-        <v>407605</v>
+        <v>407.605</v>
       </c>
     </row>
     <row r="33" spans="1:27">
@@ -3257,70 +3257,70 @@
         <v>66</v>
       </c>
       <c r="F33">
-        <v>48892</v>
+        <v>48.892</v>
       </c>
       <c r="G33">
-        <v>51590</v>
+        <v>51.59</v>
       </c>
       <c r="H33">
-        <v>46913</v>
+        <v>46.913</v>
       </c>
       <c r="I33">
-        <v>45683</v>
+        <v>45.683</v>
       </c>
       <c r="J33">
-        <v>44983</v>
+        <v>44.983</v>
       </c>
       <c r="K33">
-        <v>43531</v>
+        <v>43.531</v>
       </c>
       <c r="L33">
-        <v>37226</v>
+        <v>37.226</v>
       </c>
       <c r="M33">
-        <v>37785</v>
+        <v>37.785</v>
       </c>
       <c r="N33">
-        <v>37779</v>
+        <v>37.779</v>
       </c>
       <c r="O33">
-        <v>37333</v>
+        <v>37.333</v>
       </c>
       <c r="P33">
-        <v>36601</v>
+        <v>36.601</v>
       </c>
       <c r="Q33">
-        <v>35770</v>
+        <v>35.77</v>
       </c>
       <c r="R33">
-        <v>34888</v>
+        <v>34.888</v>
       </c>
       <c r="S33">
-        <v>34019</v>
+        <v>34.019</v>
       </c>
       <c r="T33">
-        <v>33146</v>
+        <v>33.146</v>
       </c>
       <c r="U33">
-        <v>32289</v>
+        <v>32.289</v>
       </c>
       <c r="V33">
-        <v>31466</v>
+        <v>31.466</v>
       </c>
       <c r="W33">
-        <v>30686</v>
+        <v>30.686</v>
       </c>
       <c r="X33">
-        <v>29944</v>
+        <v>29.944</v>
       </c>
       <c r="Y33">
-        <v>29238</v>
+        <v>29.238</v>
       </c>
       <c r="Z33">
-        <v>28545</v>
+        <v>28.545</v>
       </c>
       <c r="AA33">
-        <v>27824</v>
+        <v>27.824</v>
       </c>
     </row>
     <row r="34" spans="1:27">
@@ -3340,70 +3340,70 @@
         <v>66</v>
       </c>
       <c r="F34">
-        <v>4069439</v>
+        <v>4069.439</v>
       </c>
       <c r="G34">
-        <v>5316171</v>
+        <v>5316.171</v>
       </c>
       <c r="H34">
-        <v>6558176</v>
+        <v>6558.176</v>
       </c>
       <c r="I34">
-        <v>6985595</v>
+        <v>6985.595</v>
       </c>
       <c r="J34">
-        <v>7426599</v>
+        <v>7426.599</v>
       </c>
       <c r="K34">
-        <v>7909299</v>
+        <v>7909.298999999999</v>
       </c>
       <c r="L34">
-        <v>8188939</v>
+        <v>8188.939</v>
       </c>
       <c r="M34">
-        <v>8537044</v>
+        <v>8537.044</v>
       </c>
       <c r="N34">
-        <v>8860535</v>
+        <v>8860.535</v>
       </c>
       <c r="O34">
-        <v>9157149</v>
+        <v>9157.148999999999</v>
       </c>
       <c r="P34">
-        <v>9420723</v>
+        <v>9420.723</v>
       </c>
       <c r="Q34">
-        <v>9646217</v>
+        <v>9646.217000000001</v>
       </c>
       <c r="R34">
-        <v>9829334</v>
+        <v>9829.333999999999</v>
       </c>
       <c r="S34">
-        <v>9972905</v>
+        <v>9972.905000000001</v>
       </c>
       <c r="T34">
-        <v>10078003</v>
+        <v>10078.003</v>
       </c>
       <c r="U34">
-        <v>10149932</v>
+        <v>10149.932</v>
       </c>
       <c r="V34">
-        <v>10189047</v>
+        <v>10189.047</v>
       </c>
       <c r="W34">
-        <v>10194578</v>
+        <v>10194.578</v>
       </c>
       <c r="X34">
-        <v>10169374</v>
+        <v>10169.374</v>
       </c>
       <c r="Y34">
-        <v>10118982</v>
+        <v>10118.982</v>
       </c>
       <c r="Z34">
-        <v>10046177</v>
+        <v>10046.177</v>
       </c>
       <c r="AA34">
-        <v>9951879</v>
+        <v>9951.878999999999</v>
       </c>
     </row>
     <row r="35" spans="1:27">

--- a/gcam/output/SSP2/iamc_template_gcam_other.xlsx
+++ b/gcam/output/SSP2/iamc_template_gcam_other.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="70">
   <si>
     <t>Scenario</t>
   </si>
@@ -217,7 +217,7 @@
     <t>thousand people</t>
   </si>
   <si>
-    <t>thousand 1990 US$ per capita</t>
+    <t>1990 US$ per capita</t>
   </si>
   <si>
     <t>degC</t>
@@ -581,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA100"/>
+  <dimension ref="A1:AA101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -3423,70 +3423,70 @@
         <v>67</v>
       </c>
       <c r="F35">
-        <v>0.873977</v>
+        <v>873.977</v>
       </c>
       <c r="G35">
-        <v>0.899043</v>
+        <v>899.043</v>
       </c>
       <c r="H35">
-        <v>1.10648</v>
+        <v>1106.48</v>
       </c>
       <c r="I35">
-        <v>1.33117</v>
+        <v>1331.17</v>
       </c>
       <c r="J35">
-        <v>1.498</v>
+        <v>1498</v>
       </c>
       <c r="K35">
-        <v>1.62481</v>
+        <v>1624.81</v>
       </c>
       <c r="L35">
-        <v>1.74151</v>
+        <v>1741.51</v>
       </c>
       <c r="M35">
-        <v>2.07171</v>
+        <v>2071.71</v>
       </c>
       <c r="N35">
-        <v>2.46601</v>
+        <v>2466.01</v>
       </c>
       <c r="O35">
-        <v>2.91054</v>
+        <v>2910.54</v>
       </c>
       <c r="P35">
-        <v>3.43997</v>
+        <v>3439.97</v>
       </c>
       <c r="Q35">
-        <v>4.07045</v>
+        <v>4070.45</v>
       </c>
       <c r="R35">
-        <v>4.82331</v>
+        <v>4823.31</v>
       </c>
       <c r="S35">
-        <v>5.71549</v>
+        <v>5715.49</v>
       </c>
       <c r="T35">
-        <v>6.77798</v>
+        <v>6777.98</v>
       </c>
       <c r="U35">
-        <v>8.01159</v>
+        <v>8011.59</v>
       </c>
       <c r="V35">
-        <v>9.44758</v>
+        <v>9447.58</v>
       </c>
       <c r="W35">
-        <v>11.0868</v>
+        <v>11086.8</v>
       </c>
       <c r="X35">
-        <v>12.9357</v>
+        <v>12935.7</v>
       </c>
       <c r="Y35">
-        <v>15.0067</v>
+        <v>15006.7</v>
       </c>
       <c r="Z35">
-        <v>17.3236</v>
+        <v>17323.6</v>
       </c>
       <c r="AA35">
-        <v>19.9108</v>
+        <v>19910.8</v>
       </c>
     </row>
     <row r="36" spans="1:27">
@@ -3506,70 +3506,70 @@
         <v>67</v>
       </c>
       <c r="F36">
-        <v>3.04463</v>
+        <v>3044.63</v>
       </c>
       <c r="G36">
-        <v>3.99013</v>
+        <v>3990.13</v>
       </c>
       <c r="H36">
-        <v>5.21914</v>
+        <v>5219.14</v>
       </c>
       <c r="I36">
-        <v>6.03329</v>
+        <v>6033.29</v>
       </c>
       <c r="J36">
-        <v>6.03158</v>
+        <v>6031.58</v>
       </c>
       <c r="K36">
-        <v>6.451</v>
+        <v>6451</v>
       </c>
       <c r="L36">
-        <v>7.14423</v>
+        <v>7144.23</v>
       </c>
       <c r="M36">
-        <v>8.33211</v>
+        <v>8332.110000000001</v>
       </c>
       <c r="N36">
-        <v>9.812239999999999</v>
+        <v>9812.24</v>
       </c>
       <c r="O36">
-        <v>11.5378</v>
+        <v>11537.8</v>
       </c>
       <c r="P36">
-        <v>13.5434</v>
+        <v>13543.4</v>
       </c>
       <c r="Q36">
-        <v>15.8846</v>
+        <v>15884.6</v>
       </c>
       <c r="R36">
-        <v>18.625</v>
+        <v>18625</v>
       </c>
       <c r="S36">
-        <v>21.7819</v>
+        <v>21781.9</v>
       </c>
       <c r="T36">
-        <v>25.3446</v>
+        <v>25344.6</v>
       </c>
       <c r="U36">
-        <v>29.1833</v>
+        <v>29183.3</v>
       </c>
       <c r="V36">
-        <v>33.3028</v>
+        <v>33302.8</v>
       </c>
       <c r="W36">
-        <v>37.6869</v>
+        <v>37686.9</v>
       </c>
       <c r="X36">
-        <v>42.3576</v>
+        <v>42357.6</v>
       </c>
       <c r="Y36">
-        <v>47.3581</v>
+        <v>47358.1</v>
       </c>
       <c r="Z36">
-        <v>52.7565</v>
+        <v>52756.5</v>
       </c>
       <c r="AA36">
-        <v>58.5613</v>
+        <v>58561.3</v>
       </c>
     </row>
     <row r="37" spans="1:27">
@@ -3589,70 +3589,70 @@
         <v>67</v>
       </c>
       <c r="F37">
-        <v>1.46766</v>
+        <v>1467.66</v>
       </c>
       <c r="G37">
-        <v>1.261</v>
+        <v>1261</v>
       </c>
       <c r="H37">
-        <v>1.48424</v>
+        <v>1484.24</v>
       </c>
       <c r="I37">
-        <v>1.84949</v>
+        <v>1849.49</v>
       </c>
       <c r="J37">
-        <v>2.06961</v>
+        <v>2069.61</v>
       </c>
       <c r="K37">
-        <v>1.90055</v>
+        <v>1900.55</v>
       </c>
       <c r="L37">
-        <v>1.99752</v>
+        <v>1997.52</v>
       </c>
       <c r="M37">
-        <v>2.28874</v>
+        <v>2288.74</v>
       </c>
       <c r="N37">
-        <v>2.6661</v>
+        <v>2666.1</v>
       </c>
       <c r="O37">
-        <v>3.0849</v>
+        <v>3084.9</v>
       </c>
       <c r="P37">
-        <v>3.58181</v>
+        <v>3581.81</v>
       </c>
       <c r="Q37">
-        <v>4.18185</v>
+        <v>4181.849999999999</v>
       </c>
       <c r="R37">
-        <v>4.91095</v>
+        <v>4910.95</v>
       </c>
       <c r="S37">
-        <v>5.78939</v>
+        <v>5789.39</v>
       </c>
       <c r="T37">
-        <v>6.84251</v>
+        <v>6842.51</v>
       </c>
       <c r="U37">
-        <v>8.07995</v>
+        <v>8079.95</v>
       </c>
       <c r="V37">
-        <v>9.52575</v>
+        <v>9525.75</v>
       </c>
       <c r="W37">
-        <v>11.2011</v>
+        <v>11201.1</v>
       </c>
       <c r="X37">
-        <v>13.1355</v>
+        <v>13135.5</v>
       </c>
       <c r="Y37">
-        <v>15.3574</v>
+        <v>15357.4</v>
       </c>
       <c r="Z37">
-        <v>17.8728</v>
+        <v>17872.8</v>
       </c>
       <c r="AA37">
-        <v>20.6886</v>
+        <v>20688.6</v>
       </c>
     </row>
     <row r="38" spans="1:27">
@@ -3672,70 +3672,70 @@
         <v>67</v>
       </c>
       <c r="F38">
-        <v>1.82787</v>
+        <v>1827.87</v>
       </c>
       <c r="G38">
-        <v>1.50284</v>
+        <v>1502.84</v>
       </c>
       <c r="H38">
-        <v>1.64398</v>
+        <v>1643.98</v>
       </c>
       <c r="I38">
-        <v>1.92796</v>
+        <v>1927.96</v>
       </c>
       <c r="J38">
-        <v>2.18747</v>
+        <v>2187.47</v>
       </c>
       <c r="K38">
-        <v>2.10297</v>
+        <v>2102.97</v>
       </c>
       <c r="L38">
-        <v>2.20745</v>
+        <v>2207.45</v>
       </c>
       <c r="M38">
-        <v>2.42367</v>
+        <v>2423.67</v>
       </c>
       <c r="N38">
-        <v>2.79547</v>
+        <v>2795.47</v>
       </c>
       <c r="O38">
-        <v>3.21097</v>
+        <v>3210.97</v>
       </c>
       <c r="P38">
-        <v>3.69759</v>
+        <v>3697.59</v>
       </c>
       <c r="Q38">
-        <v>4.27773</v>
+        <v>4277.73</v>
       </c>
       <c r="R38">
-        <v>4.97537</v>
+        <v>4975.37</v>
       </c>
       <c r="S38">
-        <v>5.80715</v>
+        <v>5807.15</v>
       </c>
       <c r="T38">
-        <v>6.78816</v>
+        <v>6788.160000000001</v>
       </c>
       <c r="U38">
-        <v>7.92227</v>
+        <v>7922.27</v>
       </c>
       <c r="V38">
-        <v>9.225350000000001</v>
+        <v>9225.35</v>
       </c>
       <c r="W38">
-        <v>10.713</v>
+        <v>10713</v>
       </c>
       <c r="X38">
-        <v>12.4072</v>
+        <v>12407.2</v>
       </c>
       <c r="Y38">
-        <v>14.3355</v>
+        <v>14335.5</v>
       </c>
       <c r="Z38">
-        <v>16.5279</v>
+        <v>16527.9</v>
       </c>
       <c r="AA38">
-        <v>19.011</v>
+        <v>19011</v>
       </c>
     </row>
     <row r="39" spans="1:27">
@@ -3755,70 +3755,70 @@
         <v>67</v>
       </c>
       <c r="F39">
-        <v>8.13181</v>
+        <v>8131.809999999999</v>
       </c>
       <c r="G39">
-        <v>6.44481</v>
+        <v>6444.81</v>
       </c>
       <c r="H39">
-        <v>8.957240000000001</v>
+        <v>8957.24</v>
       </c>
       <c r="I39">
-        <v>10.8124</v>
+        <v>10812.4</v>
       </c>
       <c r="J39">
-        <v>11.054</v>
+        <v>11054</v>
       </c>
       <c r="K39">
-        <v>9.41337</v>
+        <v>9413.370000000001</v>
       </c>
       <c r="L39">
-        <v>10.2891</v>
+        <v>10289.1</v>
       </c>
       <c r="M39">
-        <v>11.3549</v>
+        <v>11354.9</v>
       </c>
       <c r="N39">
-        <v>12.3509</v>
+        <v>12350.9</v>
       </c>
       <c r="O39">
-        <v>13.4928</v>
+        <v>13492.8</v>
       </c>
       <c r="P39">
-        <v>14.8479</v>
+        <v>14847.9</v>
       </c>
       <c r="Q39">
-        <v>16.4528</v>
+        <v>16452.8</v>
       </c>
       <c r="R39">
-        <v>18.3132</v>
+        <v>18313.2</v>
       </c>
       <c r="S39">
-        <v>20.4124</v>
+        <v>20412.4</v>
       </c>
       <c r="T39">
-        <v>22.7605</v>
+        <v>22760.5</v>
       </c>
       <c r="U39">
-        <v>25.3317</v>
+        <v>25331.7</v>
       </c>
       <c r="V39">
-        <v>28.0923</v>
+        <v>28092.3</v>
       </c>
       <c r="W39">
-        <v>31.0448</v>
+        <v>31044.8</v>
       </c>
       <c r="X39">
-        <v>34.2139</v>
+        <v>34213.9</v>
       </c>
       <c r="Y39">
-        <v>37.6178</v>
+        <v>37617.8</v>
       </c>
       <c r="Z39">
-        <v>41.2532</v>
+        <v>41253.2</v>
       </c>
       <c r="AA39">
-        <v>45.1007</v>
+        <v>45100.7</v>
       </c>
     </row>
     <row r="40" spans="1:27">
@@ -3838,70 +3838,70 @@
         <v>67</v>
       </c>
       <c r="F40">
-        <v>13.3325</v>
+        <v>13332.5</v>
       </c>
       <c r="G40">
-        <v>16.5575</v>
+        <v>16557.5</v>
       </c>
       <c r="H40">
-        <v>23.3505</v>
+        <v>23350.5</v>
       </c>
       <c r="I40">
-        <v>24.4876</v>
+        <v>24487.6</v>
       </c>
       <c r="J40">
-        <v>26.1505</v>
+        <v>26150.5</v>
       </c>
       <c r="K40">
-        <v>27.1617</v>
+        <v>27161.7</v>
       </c>
       <c r="L40">
-        <v>29.3985</v>
+        <v>29398.5</v>
       </c>
       <c r="M40">
-        <v>32.3069</v>
+        <v>32306.9</v>
       </c>
       <c r="N40">
-        <v>35.3509</v>
+        <v>35350.9</v>
       </c>
       <c r="O40">
-        <v>38.5289</v>
+        <v>38528.9</v>
       </c>
       <c r="P40">
-        <v>41.8641</v>
+        <v>41864.1</v>
       </c>
       <c r="Q40">
-        <v>45.1732</v>
+        <v>45173.2</v>
       </c>
       <c r="R40">
-        <v>48.4753</v>
+        <v>48475.3</v>
       </c>
       <c r="S40">
-        <v>51.8823</v>
+        <v>51882.3</v>
       </c>
       <c r="T40">
-        <v>55.4528</v>
+        <v>55452.8</v>
       </c>
       <c r="U40">
-        <v>59.047</v>
+        <v>59047</v>
       </c>
       <c r="V40">
-        <v>62.607</v>
+        <v>62607</v>
       </c>
       <c r="W40">
-        <v>66.1215</v>
+        <v>66121.5</v>
       </c>
       <c r="X40">
-        <v>69.62430000000001</v>
+        <v>69624.3</v>
       </c>
       <c r="Y40">
-        <v>73.1401</v>
+        <v>73140.10000000001</v>
       </c>
       <c r="Z40">
-        <v>76.6503</v>
+        <v>76650.3</v>
       </c>
       <c r="AA40">
-        <v>80.10339999999999</v>
+        <v>80103.39999999999</v>
       </c>
     </row>
     <row r="41" spans="1:27">
@@ -3921,70 +3921,70 @@
         <v>67</v>
       </c>
       <c r="F41">
-        <v>5.0144</v>
+        <v>5014.400000000001</v>
       </c>
       <c r="G41">
-        <v>5.98819</v>
+        <v>5988.190000000001</v>
       </c>
       <c r="H41">
-        <v>7.1255</v>
+        <v>7125.5</v>
       </c>
       <c r="I41">
-        <v>8.436629999999999</v>
+        <v>8436.629999999999</v>
       </c>
       <c r="J41">
-        <v>8.54294</v>
+        <v>8542.940000000001</v>
       </c>
       <c r="K41">
-        <v>8.24532</v>
+        <v>8245.32</v>
       </c>
       <c r="L41">
-        <v>9.10655</v>
+        <v>9106.550000000001</v>
       </c>
       <c r="M41">
-        <v>9.691330000000001</v>
+        <v>9691.33</v>
       </c>
       <c r="N41">
-        <v>10.8556</v>
+        <v>10855.6</v>
       </c>
       <c r="O41">
-        <v>12.4579</v>
+        <v>12457.9</v>
       </c>
       <c r="P41">
-        <v>14.4815</v>
+        <v>14481.5</v>
       </c>
       <c r="Q41">
-        <v>16.8926</v>
+        <v>16892.6</v>
       </c>
       <c r="R41">
-        <v>19.6645</v>
+        <v>19664.5</v>
       </c>
       <c r="S41">
-        <v>22.7619</v>
+        <v>22761.9</v>
       </c>
       <c r="T41">
-        <v>26.2269</v>
+        <v>26226.9</v>
       </c>
       <c r="U41">
-        <v>29.9958</v>
+        <v>29995.8</v>
       </c>
       <c r="V41">
-        <v>34.0932</v>
+        <v>34093.2</v>
       </c>
       <c r="W41">
-        <v>38.4725</v>
+        <v>38472.5</v>
       </c>
       <c r="X41">
-        <v>43.1276</v>
+        <v>43127.6</v>
       </c>
       <c r="Y41">
-        <v>48.0536</v>
+        <v>48053.60000000001</v>
       </c>
       <c r="Z41">
-        <v>53.2366</v>
+        <v>53236.60000000001</v>
       </c>
       <c r="AA41">
-        <v>58.6593</v>
+        <v>58659.3</v>
       </c>
     </row>
     <row r="42" spans="1:27">
@@ -4004,70 +4004,70 @@
         <v>67</v>
       </c>
       <c r="F42">
-        <v>14.4374</v>
+        <v>14437.4</v>
       </c>
       <c r="G42">
-        <v>18.8438</v>
+        <v>18843.8</v>
       </c>
       <c r="H42">
-        <v>24.3511</v>
+        <v>24351.1</v>
       </c>
       <c r="I42">
-        <v>24.4591</v>
+        <v>24459.1</v>
       </c>
       <c r="J42">
-        <v>25.8563</v>
+        <v>25856.3</v>
       </c>
       <c r="K42">
-        <v>25.6956</v>
+        <v>25695.6</v>
       </c>
       <c r="L42">
-        <v>27.7602</v>
+        <v>27760.2</v>
       </c>
       <c r="M42">
-        <v>30.1889</v>
+        <v>30188.9</v>
       </c>
       <c r="N42">
-        <v>32.9308</v>
+        <v>32930.8</v>
       </c>
       <c r="O42">
-        <v>35.9905</v>
+        <v>35990.5</v>
       </c>
       <c r="P42">
-        <v>39.1442</v>
+        <v>39144.2</v>
       </c>
       <c r="Q42">
-        <v>42.1822</v>
+        <v>42182.2</v>
       </c>
       <c r="R42">
-        <v>45.2304</v>
+        <v>45230.4</v>
       </c>
       <c r="S42">
-        <v>48.27</v>
+        <v>48270</v>
       </c>
       <c r="T42">
-        <v>51.3983</v>
+        <v>51398.3</v>
       </c>
       <c r="U42">
-        <v>54.5202</v>
+        <v>54520.2</v>
       </c>
       <c r="V42">
-        <v>57.563</v>
+        <v>57563</v>
       </c>
       <c r="W42">
-        <v>60.5394</v>
+        <v>60539.4</v>
       </c>
       <c r="X42">
-        <v>63.5051</v>
+        <v>63505.1</v>
       </c>
       <c r="Y42">
-        <v>66.49809999999999</v>
+        <v>66498.09999999999</v>
       </c>
       <c r="Z42">
-        <v>69.5093</v>
+        <v>69509.3</v>
       </c>
       <c r="AA42">
-        <v>72.486</v>
+        <v>72486</v>
       </c>
     </row>
     <row r="43" spans="1:27">
@@ -4087,70 +4087,70 @@
         <v>67</v>
       </c>
       <c r="F43">
-        <v>3.11041</v>
+        <v>3110.41</v>
       </c>
       <c r="G43">
-        <v>3.51271</v>
+        <v>3512.71</v>
       </c>
       <c r="H43">
-        <v>4.47198</v>
+        <v>4471.98</v>
       </c>
       <c r="I43">
-        <v>5.12365</v>
+        <v>5123.65</v>
       </c>
       <c r="J43">
-        <v>5.69609</v>
+        <v>5696.09</v>
       </c>
       <c r="K43">
-        <v>5.74591</v>
+        <v>5745.91</v>
       </c>
       <c r="L43">
-        <v>6.70346</v>
+        <v>6703.46</v>
       </c>
       <c r="M43">
-        <v>7.69068</v>
+        <v>7690.68</v>
       </c>
       <c r="N43">
-        <v>8.88918</v>
+        <v>8889.18</v>
       </c>
       <c r="O43">
-        <v>10.2635</v>
+        <v>10263.5</v>
       </c>
       <c r="P43">
-        <v>11.8433</v>
+        <v>11843.3</v>
       </c>
       <c r="Q43">
-        <v>13.6431</v>
+        <v>13643.1</v>
       </c>
       <c r="R43">
-        <v>15.6824</v>
+        <v>15682.4</v>
       </c>
       <c r="S43">
-        <v>17.9799</v>
+        <v>17979.9</v>
       </c>
       <c r="T43">
-        <v>20.5584</v>
+        <v>20558.4</v>
       </c>
       <c r="U43">
-        <v>23.381</v>
+        <v>23381</v>
       </c>
       <c r="V43">
-        <v>26.4643</v>
+        <v>26464.3</v>
       </c>
       <c r="W43">
-        <v>29.7868</v>
+        <v>29786.8</v>
       </c>
       <c r="X43">
-        <v>33.3496</v>
+        <v>33349.60000000001</v>
       </c>
       <c r="Y43">
-        <v>37.1751</v>
+        <v>37175.1</v>
       </c>
       <c r="Z43">
-        <v>41.277</v>
+        <v>41277</v>
       </c>
       <c r="AA43">
-        <v>45.6583</v>
+        <v>45658.3</v>
       </c>
     </row>
     <row r="44" spans="1:27">
@@ -4170,70 +4170,70 @@
         <v>67</v>
       </c>
       <c r="F44">
-        <v>2.73158</v>
+        <v>2731.58</v>
       </c>
       <c r="G44">
-        <v>8.188750000000001</v>
+        <v>8188.750000000001</v>
       </c>
       <c r="H44">
-        <v>4.02587</v>
+        <v>4025.87</v>
       </c>
       <c r="I44">
-        <v>5.67634</v>
+        <v>5676.34</v>
       </c>
       <c r="J44">
-        <v>6.79879</v>
+        <v>6798.79</v>
       </c>
       <c r="K44">
-        <v>7.47339</v>
+        <v>7473.39</v>
       </c>
       <c r="L44">
-        <v>8.504110000000001</v>
+        <v>8504.110000000001</v>
       </c>
       <c r="M44">
-        <v>9.671889999999999</v>
+        <v>9671.889999999999</v>
       </c>
       <c r="N44">
-        <v>10.9778</v>
+        <v>10977.8</v>
       </c>
       <c r="O44">
-        <v>12.1965</v>
+        <v>12196.5</v>
       </c>
       <c r="P44">
-        <v>13.3297</v>
+        <v>13329.7</v>
       </c>
       <c r="Q44">
-        <v>14.4794</v>
+        <v>14479.4</v>
       </c>
       <c r="R44">
-        <v>15.7733</v>
+        <v>15773.3</v>
       </c>
       <c r="S44">
-        <v>17.2964</v>
+        <v>17296.4</v>
       </c>
       <c r="T44">
-        <v>19.0562</v>
+        <v>19056.2</v>
       </c>
       <c r="U44">
-        <v>20.9835</v>
+        <v>20983.5</v>
       </c>
       <c r="V44">
-        <v>23.0377</v>
+        <v>23037.7</v>
       </c>
       <c r="W44">
-        <v>25.2433</v>
+        <v>25243.3</v>
       </c>
       <c r="X44">
-        <v>27.6486</v>
+        <v>27648.6</v>
       </c>
       <c r="Y44">
-        <v>30.2912</v>
+        <v>30291.2</v>
       </c>
       <c r="Z44">
-        <v>33.1716</v>
+        <v>33171.6</v>
       </c>
       <c r="AA44">
-        <v>36.2942</v>
+        <v>36294.2</v>
       </c>
     </row>
     <row r="45" spans="1:27">
@@ -4253,70 +4253,70 @@
         <v>67</v>
       </c>
       <c r="F45">
-        <v>0.350882</v>
+        <v>350.882</v>
       </c>
       <c r="G45">
-        <v>0.926142</v>
+        <v>926.1420000000001</v>
       </c>
       <c r="H45">
-        <v>3.29253</v>
+        <v>3292.53</v>
       </c>
       <c r="I45">
-        <v>5.37063</v>
+        <v>5370.63</v>
       </c>
       <c r="J45">
-        <v>7.54382</v>
+        <v>7543.820000000001</v>
       </c>
       <c r="K45">
-        <v>10.1986</v>
+        <v>10198.6</v>
       </c>
       <c r="L45">
-        <v>12.3513</v>
+        <v>12351.3</v>
       </c>
       <c r="M45">
-        <v>14.9347</v>
+        <v>14934.7</v>
       </c>
       <c r="N45">
-        <v>17.4092</v>
+        <v>17409.2</v>
       </c>
       <c r="O45">
-        <v>19.5611</v>
+        <v>19561.1</v>
       </c>
       <c r="P45">
-        <v>21.8155</v>
+        <v>21815.5</v>
       </c>
       <c r="Q45">
-        <v>24.2094</v>
+        <v>24209.4</v>
       </c>
       <c r="R45">
-        <v>26.7033</v>
+        <v>26703.3</v>
       </c>
       <c r="S45">
-        <v>29.481</v>
+        <v>29481</v>
       </c>
       <c r="T45">
-        <v>32.4924</v>
+        <v>32492.40000000001</v>
       </c>
       <c r="U45">
-        <v>35.4471</v>
+        <v>35447.1</v>
       </c>
       <c r="V45">
-        <v>38.2786</v>
+        <v>38278.6</v>
       </c>
       <c r="W45">
-        <v>41.0854</v>
+        <v>41085.4</v>
       </c>
       <c r="X45">
-        <v>43.9318</v>
+        <v>43931.8</v>
       </c>
       <c r="Y45">
-        <v>46.8302</v>
+        <v>46830.2</v>
       </c>
       <c r="Z45">
-        <v>49.7459</v>
+        <v>49745.9</v>
       </c>
       <c r="AA45">
-        <v>52.6454</v>
+        <v>52645.4</v>
       </c>
     </row>
     <row r="46" spans="1:27">
@@ -4336,70 +4336,70 @@
         <v>67</v>
       </c>
       <c r="F46">
-        <v>3.40354</v>
+        <v>3403.54</v>
       </c>
       <c r="G46">
-        <v>4.43462</v>
+        <v>4434.62</v>
       </c>
       <c r="H46">
-        <v>5.31304</v>
+        <v>5313.04</v>
       </c>
       <c r="I46">
-        <v>6.22356</v>
+        <v>6223.56</v>
       </c>
       <c r="J46">
-        <v>7.44072</v>
+        <v>7440.719999999999</v>
       </c>
       <c r="K46">
-        <v>7.26978</v>
+        <v>7269.78</v>
       </c>
       <c r="L46">
-        <v>8.460179999999999</v>
+        <v>8460.179999999998</v>
       </c>
       <c r="M46">
-        <v>9.44655</v>
+        <v>9446.550000000001</v>
       </c>
       <c r="N46">
-        <v>10.887</v>
+        <v>10887</v>
       </c>
       <c r="O46">
-        <v>12.7555</v>
+        <v>12755.5</v>
       </c>
       <c r="P46">
-        <v>14.9485</v>
+        <v>14948.5</v>
       </c>
       <c r="Q46">
-        <v>17.377</v>
+        <v>17377</v>
       </c>
       <c r="R46">
-        <v>20.0168</v>
+        <v>20016.8</v>
       </c>
       <c r="S46">
-        <v>22.8454</v>
+        <v>22845.4</v>
       </c>
       <c r="T46">
-        <v>25.8827</v>
+        <v>25882.7</v>
       </c>
       <c r="U46">
-        <v>29.1111</v>
+        <v>29111.1</v>
       </c>
       <c r="V46">
-        <v>32.4945</v>
+        <v>32494.5</v>
       </c>
       <c r="W46">
-        <v>35.9912</v>
+        <v>35991.2</v>
       </c>
       <c r="X46">
-        <v>39.5824</v>
+        <v>39582.4</v>
       </c>
       <c r="Y46">
-        <v>43.2592</v>
+        <v>43259.2</v>
       </c>
       <c r="Z46">
-        <v>47.0022</v>
+        <v>47002.2</v>
       </c>
       <c r="AA46">
-        <v>50.7806</v>
+        <v>50780.6</v>
       </c>
     </row>
     <row r="47" spans="1:27">
@@ -4419,70 +4419,70 @@
         <v>67</v>
       </c>
       <c r="F47">
-        <v>6.43015</v>
+        <v>6430.150000000001</v>
       </c>
       <c r="G47">
-        <v>8.749639999999999</v>
+        <v>8749.639999999999</v>
       </c>
       <c r="H47">
-        <v>11.2892</v>
+        <v>11289.2</v>
       </c>
       <c r="I47">
-        <v>13.2358</v>
+        <v>13235.8</v>
       </c>
       <c r="J47">
-        <v>15.123</v>
+        <v>15123</v>
       </c>
       <c r="K47">
-        <v>18.1494</v>
+        <v>18149.4</v>
       </c>
       <c r="L47">
-        <v>20.6358</v>
+        <v>20635.8</v>
       </c>
       <c r="M47">
-        <v>24.155</v>
+        <v>24155</v>
       </c>
       <c r="N47">
-        <v>27.2755</v>
+        <v>27275.5</v>
       </c>
       <c r="O47">
-        <v>30.0759</v>
+        <v>30075.9</v>
       </c>
       <c r="P47">
-        <v>32.408</v>
+        <v>32408</v>
       </c>
       <c r="Q47">
-        <v>34.5005</v>
+        <v>34500.5</v>
       </c>
       <c r="R47">
-        <v>36.5153</v>
+        <v>36515.3</v>
       </c>
       <c r="S47">
-        <v>38.5694</v>
+        <v>38569.4</v>
       </c>
       <c r="T47">
-        <v>40.7066</v>
+        <v>40706.6</v>
       </c>
       <c r="U47">
-        <v>42.821</v>
+        <v>42821</v>
       </c>
       <c r="V47">
-        <v>44.8346</v>
+        <v>44834.6</v>
       </c>
       <c r="W47">
-        <v>46.7126</v>
+        <v>46712.6</v>
       </c>
       <c r="X47">
-        <v>48.4855</v>
+        <v>48485.5</v>
       </c>
       <c r="Y47">
-        <v>50.2104</v>
+        <v>50210.4</v>
       </c>
       <c r="Z47">
-        <v>51.925</v>
+        <v>51925</v>
       </c>
       <c r="AA47">
-        <v>53.6217</v>
+        <v>53621.7</v>
       </c>
     </row>
     <row r="48" spans="1:27">
@@ -4502,70 +4502,70 @@
         <v>67</v>
       </c>
       <c r="F48">
-        <v>12.4932</v>
+        <v>12493.2</v>
       </c>
       <c r="G48">
-        <v>17.8828</v>
+        <v>17882.8</v>
       </c>
       <c r="H48">
-        <v>23.0581</v>
+        <v>23058.1</v>
       </c>
       <c r="I48">
-        <v>23.2753</v>
+        <v>23275.3</v>
       </c>
       <c r="J48">
-        <v>24.1508</v>
+        <v>24150.8</v>
       </c>
       <c r="K48">
-        <v>24.591</v>
+        <v>24591</v>
       </c>
       <c r="L48">
-        <v>27.0555</v>
+        <v>27055.5</v>
       </c>
       <c r="M48">
-        <v>29.0608</v>
+        <v>29060.8</v>
       </c>
       <c r="N48">
-        <v>31.1078</v>
+        <v>31107.8</v>
       </c>
       <c r="O48">
-        <v>33.3106</v>
+        <v>33310.6</v>
       </c>
       <c r="P48">
-        <v>35.6137</v>
+        <v>35613.7</v>
       </c>
       <c r="Q48">
-        <v>37.9313</v>
+        <v>37931.3</v>
       </c>
       <c r="R48">
-        <v>40.3402</v>
+        <v>40340.2</v>
       </c>
       <c r="S48">
-        <v>42.8564</v>
+        <v>42856.4</v>
       </c>
       <c r="T48">
-        <v>45.4568</v>
+        <v>45456.8</v>
       </c>
       <c r="U48">
-        <v>47.9726</v>
+        <v>47972.6</v>
       </c>
       <c r="V48">
-        <v>50.3547</v>
+        <v>50354.7</v>
       </c>
       <c r="W48">
-        <v>52.6078</v>
+        <v>52607.8</v>
       </c>
       <c r="X48">
-        <v>54.7731</v>
+        <v>54773.1</v>
       </c>
       <c r="Y48">
-        <v>56.8839</v>
+        <v>56883.89999999999</v>
       </c>
       <c r="Z48">
-        <v>58.9367</v>
+        <v>58936.7</v>
       </c>
       <c r="AA48">
-        <v>60.8966</v>
+        <v>60896.6</v>
       </c>
     </row>
     <row r="49" spans="1:27">
@@ -4585,70 +4585,70 @@
         <v>67</v>
       </c>
       <c r="F49">
-        <v>4.4155</v>
+        <v>4415.5</v>
       </c>
       <c r="G49">
-        <v>6.89874</v>
+        <v>6898.74</v>
       </c>
       <c r="H49">
-        <v>8.71308</v>
+        <v>8713.08</v>
       </c>
       <c r="I49">
-        <v>9.92221</v>
+        <v>9922.209999999999</v>
       </c>
       <c r="J49">
-        <v>12.5197</v>
+        <v>12519.7</v>
       </c>
       <c r="K49">
-        <v>14.7639</v>
+        <v>14763.9</v>
       </c>
       <c r="L49">
-        <v>17.5947</v>
+        <v>17594.7</v>
       </c>
       <c r="M49">
-        <v>20.7162</v>
+        <v>20716.2</v>
       </c>
       <c r="N49">
-        <v>23.7882</v>
+        <v>23788.2</v>
       </c>
       <c r="O49">
-        <v>26.5941</v>
+        <v>26594.1</v>
       </c>
       <c r="P49">
-        <v>29.2723</v>
+        <v>29272.3</v>
       </c>
       <c r="Q49">
-        <v>31.8558</v>
+        <v>31855.8</v>
       </c>
       <c r="R49">
-        <v>34.4514</v>
+        <v>34451.4</v>
       </c>
       <c r="S49">
-        <v>37.0831</v>
+        <v>37083.1</v>
       </c>
       <c r="T49">
-        <v>39.6545</v>
+        <v>39654.5</v>
       </c>
       <c r="U49">
-        <v>42.057</v>
+        <v>42057</v>
       </c>
       <c r="V49">
-        <v>44.3123</v>
+        <v>44312.3</v>
       </c>
       <c r="W49">
-        <v>46.4497</v>
+        <v>46449.7</v>
       </c>
       <c r="X49">
-        <v>48.5443</v>
+        <v>48544.3</v>
       </c>
       <c r="Y49">
-        <v>50.6575</v>
+        <v>50657.5</v>
       </c>
       <c r="Z49">
-        <v>52.8165</v>
+        <v>52816.5</v>
       </c>
       <c r="AA49">
-        <v>55.0262</v>
+        <v>55026.2</v>
       </c>
     </row>
     <row r="50" spans="1:27">
@@ -4668,70 +4668,70 @@
         <v>67</v>
       </c>
       <c r="F50">
-        <v>20.9324</v>
+        <v>20932.4</v>
       </c>
       <c r="G50">
-        <v>28.2002</v>
+        <v>28200.2</v>
       </c>
       <c r="H50">
-        <v>34.1521</v>
+        <v>34152.1</v>
       </c>
       <c r="I50">
-        <v>35.3874</v>
+        <v>35387.4</v>
       </c>
       <c r="J50">
-        <v>36.4551</v>
+        <v>36455.1</v>
       </c>
       <c r="K50">
-        <v>37.3999</v>
+        <v>37399.9</v>
       </c>
       <c r="L50">
-        <v>39.9368</v>
+        <v>39936.8</v>
       </c>
       <c r="M50">
-        <v>41.9139</v>
+        <v>41913.9</v>
       </c>
       <c r="N50">
-        <v>43.8957</v>
+        <v>43895.7</v>
       </c>
       <c r="O50">
-        <v>45.7442</v>
+        <v>45744.2</v>
       </c>
       <c r="P50">
-        <v>47.5203</v>
+        <v>47520.3</v>
       </c>
       <c r="Q50">
-        <v>49.196</v>
+        <v>49196</v>
       </c>
       <c r="R50">
-        <v>50.949</v>
+        <v>50949</v>
       </c>
       <c r="S50">
-        <v>52.8663</v>
+        <v>52866.3</v>
       </c>
       <c r="T50">
-        <v>54.9902</v>
+        <v>54990.2</v>
       </c>
       <c r="U50">
-        <v>57.1061</v>
+        <v>57106.1</v>
       </c>
       <c r="V50">
-        <v>59.1351</v>
+        <v>59135.1</v>
       </c>
       <c r="W50">
-        <v>61.0619</v>
+        <v>61061.9</v>
       </c>
       <c r="X50">
-        <v>62.9143</v>
+        <v>62914.3</v>
       </c>
       <c r="Y50">
-        <v>64.72320000000001</v>
+        <v>64723.2</v>
       </c>
       <c r="Z50">
-        <v>66.476</v>
+        <v>66476</v>
       </c>
       <c r="AA50">
-        <v>68.1341</v>
+        <v>68134.10000000001</v>
       </c>
     </row>
     <row r="51" spans="1:27">
@@ -4751,70 +4751,70 @@
         <v>67</v>
       </c>
       <c r="F51">
-        <v>0.7342610000000001</v>
+        <v>734.2610000000001</v>
       </c>
       <c r="G51">
-        <v>1.05295</v>
+        <v>1052.95</v>
       </c>
       <c r="H51">
-        <v>1.86713</v>
+        <v>1867.13</v>
       </c>
       <c r="I51">
-        <v>2.43894</v>
+        <v>2438.94</v>
       </c>
       <c r="J51">
-        <v>3.13271</v>
+        <v>3132.71</v>
       </c>
       <c r="K51">
-        <v>3.82354</v>
+        <v>3823.54</v>
       </c>
       <c r="L51">
-        <v>4.78846</v>
+        <v>4788.46</v>
       </c>
       <c r="M51">
-        <v>6.10879</v>
+        <v>6108.79</v>
       </c>
       <c r="N51">
-        <v>7.47388</v>
+        <v>7473.88</v>
       </c>
       <c r="O51">
-        <v>8.94097</v>
+        <v>8940.969999999999</v>
       </c>
       <c r="P51">
-        <v>10.5403</v>
+        <v>10540.3</v>
       </c>
       <c r="Q51">
-        <v>12.3022</v>
+        <v>12302.2</v>
       </c>
       <c r="R51">
-        <v>14.2436</v>
+        <v>14243.6</v>
       </c>
       <c r="S51">
-        <v>16.3663</v>
+        <v>16366.3</v>
       </c>
       <c r="T51">
-        <v>18.6707</v>
+        <v>18670.7</v>
       </c>
       <c r="U51">
-        <v>21.1027</v>
+        <v>21102.7</v>
       </c>
       <c r="V51">
-        <v>23.6839</v>
+        <v>23683.9</v>
       </c>
       <c r="W51">
-        <v>26.3664</v>
+        <v>26366.4</v>
       </c>
       <c r="X51">
-        <v>29.1327</v>
+        <v>29132.7</v>
       </c>
       <c r="Y51">
-        <v>31.9692</v>
+        <v>31969.2</v>
       </c>
       <c r="Z51">
-        <v>34.8776</v>
+        <v>34877.6</v>
       </c>
       <c r="AA51">
-        <v>37.8667</v>
+        <v>37866.7</v>
       </c>
     </row>
     <row r="52" spans="1:27">
@@ -4834,70 +4834,70 @@
         <v>67</v>
       </c>
       <c r="F52">
-        <v>1.37111</v>
+        <v>1371.11</v>
       </c>
       <c r="G52">
-        <v>2.6574</v>
+        <v>2657.4</v>
       </c>
       <c r="H52">
-        <v>4.02952</v>
+        <v>4029.52</v>
       </c>
       <c r="I52">
-        <v>4.9947</v>
+        <v>4994.7</v>
       </c>
       <c r="J52">
-        <v>6.15582</v>
+        <v>6155.820000000001</v>
       </c>
       <c r="K52">
-        <v>7.32691</v>
+        <v>7326.91</v>
       </c>
       <c r="L52">
-        <v>8.566520000000001</v>
+        <v>8566.52</v>
       </c>
       <c r="M52">
-        <v>10.2949</v>
+        <v>10294.9</v>
       </c>
       <c r="N52">
-        <v>11.9889</v>
+        <v>11988.9</v>
       </c>
       <c r="O52">
-        <v>13.7756</v>
+        <v>13775.6</v>
       </c>
       <c r="P52">
-        <v>15.602</v>
+        <v>15602</v>
       </c>
       <c r="Q52">
-        <v>17.4473</v>
+        <v>17447.3</v>
       </c>
       <c r="R52">
-        <v>19.4023</v>
+        <v>19402.3</v>
       </c>
       <c r="S52">
-        <v>21.4603</v>
+        <v>21460.3</v>
       </c>
       <c r="T52">
-        <v>23.5941</v>
+        <v>23594.1</v>
       </c>
       <c r="U52">
-        <v>25.7993</v>
+        <v>25799.3</v>
       </c>
       <c r="V52">
-        <v>28.0721</v>
+        <v>28072.1</v>
       </c>
       <c r="W52">
-        <v>30.3935</v>
+        <v>30393.5</v>
       </c>
       <c r="X52">
-        <v>32.7631</v>
+        <v>32763.1</v>
       </c>
       <c r="Y52">
-        <v>35.1673</v>
+        <v>35167.3</v>
       </c>
       <c r="Z52">
-        <v>37.5955</v>
+        <v>37595.5</v>
       </c>
       <c r="AA52">
-        <v>40.0332</v>
+        <v>40033.2</v>
       </c>
     </row>
     <row r="53" spans="1:27">
@@ -4917,70 +4917,70 @@
         <v>67</v>
       </c>
       <c r="F53">
-        <v>11.1826</v>
+        <v>11182.6</v>
       </c>
       <c r="G53">
-        <v>19.6204</v>
+        <v>19620.4</v>
       </c>
       <c r="H53">
-        <v>22.8134</v>
+        <v>22813.4</v>
       </c>
       <c r="I53">
-        <v>22.7039</v>
+        <v>22703.9</v>
       </c>
       <c r="J53">
-        <v>24.0807</v>
+        <v>24080.7</v>
       </c>
       <c r="K53">
-        <v>24.5229</v>
+        <v>24522.9</v>
       </c>
       <c r="L53">
-        <v>26.4521</v>
+        <v>26452.1</v>
       </c>
       <c r="M53">
-        <v>28.231</v>
+        <v>28231</v>
       </c>
       <c r="N53">
-        <v>30.2725</v>
+        <v>30272.5</v>
       </c>
       <c r="O53">
-        <v>32.2738</v>
+        <v>32273.8</v>
       </c>
       <c r="P53">
-        <v>34.4378</v>
+        <v>34437.8</v>
       </c>
       <c r="Q53">
-        <v>36.77</v>
+        <v>36770</v>
       </c>
       <c r="R53">
-        <v>39.1347</v>
+        <v>39134.7</v>
       </c>
       <c r="S53">
-        <v>41.497</v>
+        <v>41497</v>
       </c>
       <c r="T53">
-        <v>43.9289</v>
+        <v>43928.9</v>
       </c>
       <c r="U53">
-        <v>46.4225</v>
+        <v>46422.5</v>
       </c>
       <c r="V53">
-        <v>48.951</v>
+        <v>48951</v>
       </c>
       <c r="W53">
-        <v>51.4734</v>
+        <v>51473.4</v>
       </c>
       <c r="X53">
-        <v>53.9771</v>
+        <v>53977.1</v>
       </c>
       <c r="Y53">
-        <v>56.4559</v>
+        <v>56455.9</v>
       </c>
       <c r="Z53">
-        <v>58.8935</v>
+        <v>58893.5</v>
       </c>
       <c r="AA53">
-        <v>61.2503</v>
+        <v>61250.3</v>
       </c>
     </row>
     <row r="54" spans="1:27">
@@ -5000,70 +5000,70 @@
         <v>67</v>
       </c>
       <c r="F54">
-        <v>7.55151</v>
+        <v>7551.51</v>
       </c>
       <c r="G54">
-        <v>8.95308</v>
+        <v>8953.08</v>
       </c>
       <c r="H54">
-        <v>10.5453</v>
+        <v>10545.3</v>
       </c>
       <c r="I54">
-        <v>10.4959</v>
+        <v>10495.9</v>
       </c>
       <c r="J54">
-        <v>11.1801</v>
+        <v>11180.1</v>
       </c>
       <c r="K54">
-        <v>10.6036</v>
+        <v>10603.6</v>
       </c>
       <c r="L54">
-        <v>11.7962</v>
+        <v>11796.2</v>
       </c>
       <c r="M54">
-        <v>12.9686</v>
+        <v>12968.6</v>
       </c>
       <c r="N54">
-        <v>14.3578</v>
+        <v>14357.8</v>
       </c>
       <c r="O54">
-        <v>15.9384</v>
+        <v>15938.4</v>
       </c>
       <c r="P54">
-        <v>17.7324</v>
+        <v>17732.4</v>
       </c>
       <c r="Q54">
-        <v>19.7166</v>
+        <v>19716.6</v>
       </c>
       <c r="R54">
-        <v>21.8388</v>
+        <v>21838.8</v>
       </c>
       <c r="S54">
-        <v>24.0374</v>
+        <v>24037.4</v>
       </c>
       <c r="T54">
-        <v>26.3289</v>
+        <v>26328.9</v>
       </c>
       <c r="U54">
-        <v>28.7065</v>
+        <v>28706.5</v>
       </c>
       <c r="V54">
-        <v>31.1311</v>
+        <v>31131.1</v>
       </c>
       <c r="W54">
-        <v>33.5469</v>
+        <v>33546.9</v>
       </c>
       <c r="X54">
-        <v>35.9302</v>
+        <v>35930.2</v>
       </c>
       <c r="Y54">
-        <v>38.2569</v>
+        <v>38256.9</v>
       </c>
       <c r="Z54">
-        <v>40.4919</v>
+        <v>40491.9</v>
       </c>
       <c r="AA54">
-        <v>42.6374</v>
+        <v>42637.4</v>
       </c>
     </row>
     <row r="55" spans="1:27">
@@ -5083,70 +5083,70 @@
         <v>67</v>
       </c>
       <c r="F55">
-        <v>10.6356</v>
+        <v>10635.6</v>
       </c>
       <c r="G55">
-        <v>7.77126</v>
+        <v>7771.26</v>
       </c>
       <c r="H55">
-        <v>10.131</v>
+        <v>10131</v>
       </c>
       <c r="I55">
-        <v>10.9625</v>
+        <v>10962.5</v>
       </c>
       <c r="J55">
-        <v>11.6899</v>
+        <v>11689.9</v>
       </c>
       <c r="K55">
-        <v>11.4421</v>
+        <v>11442.1</v>
       </c>
       <c r="L55">
-        <v>12.3705</v>
+        <v>12370.5</v>
       </c>
       <c r="M55">
-        <v>13.711</v>
+        <v>13711</v>
       </c>
       <c r="N55">
-        <v>15.0462</v>
+        <v>15046.2</v>
       </c>
       <c r="O55">
-        <v>16.398</v>
+        <v>16398</v>
       </c>
       <c r="P55">
-        <v>17.7037</v>
+        <v>17703.7</v>
       </c>
       <c r="Q55">
-        <v>18.998</v>
+        <v>18998</v>
       </c>
       <c r="R55">
-        <v>20.3638</v>
+        <v>20363.8</v>
       </c>
       <c r="S55">
-        <v>21.8591</v>
+        <v>21859.1</v>
       </c>
       <c r="T55">
-        <v>23.5033</v>
+        <v>23503.3</v>
       </c>
       <c r="U55">
-        <v>25.224</v>
+        <v>25224</v>
       </c>
       <c r="V55">
-        <v>27.0078</v>
+        <v>27007.8</v>
       </c>
       <c r="W55">
-        <v>28.8671</v>
+        <v>28867.1</v>
       </c>
       <c r="X55">
-        <v>30.8148</v>
+        <v>30814.8</v>
       </c>
       <c r="Y55">
-        <v>32.8765</v>
+        <v>32876.5</v>
       </c>
       <c r="Z55">
-        <v>35.0782</v>
+        <v>35078.2</v>
       </c>
       <c r="AA55">
-        <v>37.4324</v>
+        <v>37432.4</v>
       </c>
     </row>
     <row r="56" spans="1:27">
@@ -5166,70 +5166,70 @@
         <v>67</v>
       </c>
       <c r="F56">
-        <v>1.10923</v>
+        <v>1109.23</v>
       </c>
       <c r="G56">
-        <v>1.59399</v>
+        <v>1593.99</v>
       </c>
       <c r="H56">
-        <v>1.98113</v>
+        <v>1981.13</v>
       </c>
       <c r="I56">
-        <v>2.20303</v>
+        <v>2203.03</v>
       </c>
       <c r="J56">
-        <v>2.62205</v>
+        <v>2622.05</v>
       </c>
       <c r="K56">
-        <v>2.97007</v>
+        <v>2970.07</v>
       </c>
       <c r="L56">
-        <v>3.13838</v>
+        <v>3138.38</v>
       </c>
       <c r="M56">
-        <v>3.624</v>
+        <v>3624</v>
       </c>
       <c r="N56">
-        <v>4.2213</v>
+        <v>4221.3</v>
       </c>
       <c r="O56">
-        <v>4.99952</v>
+        <v>4999.52</v>
       </c>
       <c r="P56">
-        <v>5.99727</v>
+        <v>5997.27</v>
       </c>
       <c r="Q56">
-        <v>7.21905</v>
+        <v>7219.05</v>
       </c>
       <c r="R56">
-        <v>8.68309</v>
+        <v>8683.09</v>
       </c>
       <c r="S56">
-        <v>10.4049</v>
+        <v>10404.9</v>
       </c>
       <c r="T56">
-        <v>12.4357</v>
+        <v>12435.7</v>
       </c>
       <c r="U56">
-        <v>14.759</v>
+        <v>14759</v>
       </c>
       <c r="V56">
-        <v>17.4122</v>
+        <v>17412.2</v>
       </c>
       <c r="W56">
-        <v>20.3835</v>
+        <v>20383.5</v>
       </c>
       <c r="X56">
-        <v>23.6499</v>
+        <v>23649.9</v>
       </c>
       <c r="Y56">
-        <v>27.2086</v>
+        <v>27208.6</v>
       </c>
       <c r="Z56">
-        <v>31.0596</v>
+        <v>31059.6</v>
       </c>
       <c r="AA56">
-        <v>35.2236</v>
+        <v>35223.6</v>
       </c>
     </row>
     <row r="57" spans="1:27">
@@ -5249,70 +5249,70 @@
         <v>67</v>
       </c>
       <c r="F57">
-        <v>6.50249</v>
+        <v>6502.49</v>
       </c>
       <c r="G57">
-        <v>11.8219</v>
+        <v>11821.9</v>
       </c>
       <c r="H57">
-        <v>10.7759</v>
+        <v>10775.9</v>
       </c>
       <c r="I57">
-        <v>12.8744</v>
+        <v>12874.4</v>
       </c>
       <c r="J57">
-        <v>13.8538</v>
+        <v>13853.8</v>
       </c>
       <c r="K57">
-        <v>14.6148</v>
+        <v>14614.8</v>
       </c>
       <c r="L57">
-        <v>15.4557</v>
+        <v>15455.7</v>
       </c>
       <c r="M57">
-        <v>16.8424</v>
+        <v>16842.4</v>
       </c>
       <c r="N57">
-        <v>18.7182</v>
+        <v>18718.2</v>
       </c>
       <c r="O57">
-        <v>20.637</v>
+        <v>20637</v>
       </c>
       <c r="P57">
-        <v>22.5345</v>
+        <v>22534.5</v>
       </c>
       <c r="Q57">
-        <v>24.4168</v>
+        <v>24416.8</v>
       </c>
       <c r="R57">
-        <v>26.53</v>
+        <v>26530</v>
       </c>
       <c r="S57">
-        <v>29.0263</v>
+        <v>29026.3</v>
       </c>
       <c r="T57">
-        <v>31.7689</v>
+        <v>31768.9</v>
       </c>
       <c r="U57">
-        <v>34.7028</v>
+        <v>34702.8</v>
       </c>
       <c r="V57">
-        <v>37.7343</v>
+        <v>37734.3</v>
       </c>
       <c r="W57">
-        <v>40.8674</v>
+        <v>40867.4</v>
       </c>
       <c r="X57">
-        <v>44.1884</v>
+        <v>44188.4</v>
       </c>
       <c r="Y57">
-        <v>47.7958</v>
+        <v>47795.8</v>
       </c>
       <c r="Z57">
-        <v>51.7175</v>
+        <v>51717.5</v>
       </c>
       <c r="AA57">
-        <v>55.9127</v>
+        <v>55912.7</v>
       </c>
     </row>
     <row r="58" spans="1:27">
@@ -5332,70 +5332,70 @@
         <v>67</v>
       </c>
       <c r="F58">
-        <v>6.19618</v>
+        <v>6196.18</v>
       </c>
       <c r="G58">
-        <v>5.41851</v>
+        <v>5418.51</v>
       </c>
       <c r="H58">
-        <v>6.90111</v>
+        <v>6901.11</v>
       </c>
       <c r="I58">
-        <v>7.60908</v>
+        <v>7609.08</v>
       </c>
       <c r="J58">
-        <v>7.84509</v>
+        <v>7845.09</v>
       </c>
       <c r="K58">
-        <v>7.33881</v>
+        <v>7338.809999999999</v>
       </c>
       <c r="L58">
-        <v>7.66277</v>
+        <v>7662.77</v>
       </c>
       <c r="M58">
-        <v>7.98724</v>
+        <v>7987.24</v>
       </c>
       <c r="N58">
-        <v>8.852980000000001</v>
+        <v>8852.980000000001</v>
       </c>
       <c r="O58">
-        <v>10.1318</v>
+        <v>10131.8</v>
       </c>
       <c r="P58">
-        <v>11.7589</v>
+        <v>11758.9</v>
       </c>
       <c r="Q58">
-        <v>13.6924</v>
+        <v>13692.4</v>
       </c>
       <c r="R58">
-        <v>15.9299</v>
+        <v>15929.9</v>
       </c>
       <c r="S58">
-        <v>18.4867</v>
+        <v>18486.7</v>
       </c>
       <c r="T58">
-        <v>21.3552</v>
+        <v>21355.2</v>
       </c>
       <c r="U58">
-        <v>24.5354</v>
+        <v>24535.4</v>
       </c>
       <c r="V58">
-        <v>28.0241</v>
+        <v>28024.1</v>
       </c>
       <c r="W58">
-        <v>31.8579</v>
+        <v>31857.9</v>
       </c>
       <c r="X58">
-        <v>36.0401</v>
+        <v>36040.10000000001</v>
       </c>
       <c r="Y58">
-        <v>40.5855</v>
+        <v>40585.5</v>
       </c>
       <c r="Z58">
-        <v>45.4871</v>
+        <v>45487.1</v>
       </c>
       <c r="AA58">
-        <v>50.7471</v>
+        <v>50747.10000000001</v>
       </c>
     </row>
     <row r="59" spans="1:27">
@@ -5415,70 +5415,70 @@
         <v>67</v>
       </c>
       <c r="F59">
-        <v>2.82424</v>
+        <v>2824.24</v>
       </c>
       <c r="G59">
-        <v>2.44247</v>
+        <v>2442.47</v>
       </c>
       <c r="H59">
-        <v>2.53435</v>
+        <v>2534.35</v>
       </c>
       <c r="I59">
-        <v>2.56321</v>
+        <v>2563.21</v>
       </c>
       <c r="J59">
-        <v>2.08691</v>
+        <v>2086.91</v>
       </c>
       <c r="K59">
-        <v>2.0277</v>
+        <v>2027.7</v>
       </c>
       <c r="L59">
-        <v>2.36399</v>
+        <v>2363.99</v>
       </c>
       <c r="M59">
-        <v>3.63505</v>
+        <v>3635.05</v>
       </c>
       <c r="N59">
-        <v>5.01828</v>
+        <v>5018.28</v>
       </c>
       <c r="O59">
-        <v>6.17654</v>
+        <v>6176.54</v>
       </c>
       <c r="P59">
-        <v>6.91002</v>
+        <v>6910.02</v>
       </c>
       <c r="Q59">
-        <v>7.12724</v>
+        <v>7127.24</v>
       </c>
       <c r="R59">
-        <v>7.04848</v>
+        <v>7048.48</v>
       </c>
       <c r="S59">
-        <v>6.98252</v>
+        <v>6982.52</v>
       </c>
       <c r="T59">
-        <v>6.93834</v>
+        <v>6938.34</v>
       </c>
       <c r="U59">
-        <v>6.91383</v>
+        <v>6913.83</v>
       </c>
       <c r="V59">
-        <v>6.9067</v>
+        <v>6906.7</v>
       </c>
       <c r="W59">
-        <v>6.91533</v>
+        <v>6915.33</v>
       </c>
       <c r="X59">
-        <v>6.93777</v>
+        <v>6937.77</v>
       </c>
       <c r="Y59">
-        <v>6.99501</v>
+        <v>6995.009999999999</v>
       </c>
       <c r="Z59">
-        <v>7.10662</v>
+        <v>7106.620000000001</v>
       </c>
       <c r="AA59">
-        <v>7.23516</v>
+        <v>7235.16</v>
       </c>
     </row>
     <row r="60" spans="1:27">
@@ -5498,70 +5498,70 @@
         <v>67</v>
       </c>
       <c r="F60">
-        <v>3.82112</v>
+        <v>3821.12</v>
       </c>
       <c r="G60">
-        <v>3.92199</v>
+        <v>3921.99</v>
       </c>
       <c r="H60">
-        <v>5.71648</v>
+        <v>5716.48</v>
       </c>
       <c r="I60">
-        <v>6.85737</v>
+        <v>6857.370000000001</v>
       </c>
       <c r="J60">
-        <v>8.01459</v>
+        <v>8014.59</v>
       </c>
       <c r="K60">
-        <v>7.6854</v>
+        <v>7685.4</v>
       </c>
       <c r="L60">
-        <v>8.55457</v>
+        <v>8554.57</v>
       </c>
       <c r="M60">
-        <v>9.25783</v>
+        <v>9257.83</v>
       </c>
       <c r="N60">
-        <v>10.1994</v>
+        <v>10199.4</v>
       </c>
       <c r="O60">
-        <v>11.3332</v>
+        <v>11333.2</v>
       </c>
       <c r="P60">
-        <v>12.6601</v>
+        <v>12660.1</v>
       </c>
       <c r="Q60">
-        <v>14.1807</v>
+        <v>14180.7</v>
       </c>
       <c r="R60">
-        <v>15.8917</v>
+        <v>15891.7</v>
       </c>
       <c r="S60">
-        <v>17.805</v>
+        <v>17805</v>
       </c>
       <c r="T60">
-        <v>19.9514</v>
+        <v>19951.4</v>
       </c>
       <c r="U60">
-        <v>22.3015</v>
+        <v>22301.5</v>
       </c>
       <c r="V60">
-        <v>24.8386</v>
+        <v>24838.6</v>
       </c>
       <c r="W60">
-        <v>27.5458</v>
+        <v>27545.8</v>
       </c>
       <c r="X60">
-        <v>30.4246</v>
+        <v>30424.6</v>
       </c>
       <c r="Y60">
-        <v>33.4737</v>
+        <v>33473.7</v>
       </c>
       <c r="Z60">
-        <v>36.6882</v>
+        <v>36688.2</v>
       </c>
       <c r="AA60">
-        <v>40.064</v>
+        <v>40064</v>
       </c>
     </row>
     <row r="61" spans="1:27">
@@ -5581,70 +5581,70 @@
         <v>67</v>
       </c>
       <c r="F61">
-        <v>0.8453270000000001</v>
+        <v>845.327</v>
       </c>
       <c r="G61">
-        <v>1.04587</v>
+        <v>1045.87</v>
       </c>
       <c r="H61">
-        <v>1.50791</v>
+        <v>1507.91</v>
       </c>
       <c r="I61">
-        <v>2.02852</v>
+        <v>2028.52</v>
       </c>
       <c r="J61">
-        <v>2.69087</v>
+        <v>2690.87</v>
       </c>
       <c r="K61">
-        <v>3.37768</v>
+        <v>3377.68</v>
       </c>
       <c r="L61">
-        <v>3.89006</v>
+        <v>3890.06</v>
       </c>
       <c r="M61">
-        <v>4.99369</v>
+        <v>4993.69</v>
       </c>
       <c r="N61">
-        <v>6.20972</v>
+        <v>6209.72</v>
       </c>
       <c r="O61">
-        <v>7.42254</v>
+        <v>7422.54</v>
       </c>
       <c r="P61">
-        <v>8.68186</v>
+        <v>8681.860000000001</v>
       </c>
       <c r="Q61">
-        <v>10.0115</v>
+        <v>10011.5</v>
       </c>
       <c r="R61">
-        <v>11.428</v>
+        <v>11428</v>
       </c>
       <c r="S61">
-        <v>12.9586</v>
+        <v>12958.6</v>
       </c>
       <c r="T61">
-        <v>14.628</v>
+        <v>14628</v>
       </c>
       <c r="U61">
-        <v>16.3854</v>
+        <v>16385.4</v>
       </c>
       <c r="V61">
-        <v>18.2434</v>
+        <v>18243.4</v>
       </c>
       <c r="W61">
-        <v>20.1572</v>
+        <v>20157.2</v>
       </c>
       <c r="X61">
-        <v>22.1155</v>
+        <v>22115.5</v>
       </c>
       <c r="Y61">
-        <v>24.132</v>
+        <v>24132</v>
       </c>
       <c r="Z61">
-        <v>26.228</v>
+        <v>26228</v>
       </c>
       <c r="AA61">
-        <v>28.4096</v>
+        <v>28409.6</v>
       </c>
     </row>
     <row r="62" spans="1:27">
@@ -5664,70 +5664,70 @@
         <v>67</v>
       </c>
       <c r="F62">
-        <v>2.19682</v>
+        <v>2196.82</v>
       </c>
       <c r="G62">
-        <v>7.00684</v>
+        <v>7006.84</v>
       </c>
       <c r="H62">
-        <v>16.4191</v>
+        <v>16419.1</v>
       </c>
       <c r="I62">
-        <v>19.8946</v>
+        <v>19894.6</v>
       </c>
       <c r="J62">
-        <v>22.1327</v>
+        <v>22132.7</v>
       </c>
       <c r="K62">
-        <v>24.8022</v>
+        <v>24802.2</v>
       </c>
       <c r="L62">
-        <v>27.5251</v>
+        <v>27525.1</v>
       </c>
       <c r="M62">
-        <v>30.5453</v>
+        <v>30545.3</v>
       </c>
       <c r="N62">
-        <v>33.0155</v>
+        <v>33015.5</v>
       </c>
       <c r="O62">
-        <v>35.1776</v>
+        <v>35177.6</v>
       </c>
       <c r="P62">
-        <v>37.2248</v>
+        <v>37224.8</v>
       </c>
       <c r="Q62">
-        <v>39.1654</v>
+        <v>39165.4</v>
       </c>
       <c r="R62">
-        <v>41.153</v>
+        <v>41153</v>
       </c>
       <c r="S62">
-        <v>43.2126</v>
+        <v>43212.6</v>
       </c>
       <c r="T62">
-        <v>45.3782</v>
+        <v>45378.2</v>
       </c>
       <c r="U62">
-        <v>47.451</v>
+        <v>47451</v>
       </c>
       <c r="V62">
-        <v>49.3552</v>
+        <v>49355.2</v>
       </c>
       <c r="W62">
-        <v>51.0699</v>
+        <v>51069.89999999999</v>
       </c>
       <c r="X62">
-        <v>52.609</v>
+        <v>52609</v>
       </c>
       <c r="Y62">
-        <v>54.0569</v>
+        <v>54056.9</v>
       </c>
       <c r="Z62">
-        <v>55.4632</v>
+        <v>55463.2</v>
       </c>
       <c r="AA62">
-        <v>56.7352</v>
+        <v>56735.2</v>
       </c>
     </row>
     <row r="63" spans="1:27">
@@ -5747,70 +5747,70 @@
         <v>67</v>
       </c>
       <c r="F63">
-        <v>1.61895</v>
+        <v>1618.95</v>
       </c>
       <c r="G63">
-        <v>2.59468</v>
+        <v>2594.68</v>
       </c>
       <c r="H63">
-        <v>4.26271</v>
+        <v>4262.71</v>
       </c>
       <c r="I63">
-        <v>5.26435</v>
+        <v>5264.35</v>
       </c>
       <c r="J63">
-        <v>6.27095</v>
+        <v>6270.95</v>
       </c>
       <c r="K63">
-        <v>7.10099</v>
+        <v>7100.990000000001</v>
       </c>
       <c r="L63">
-        <v>8.062139999999999</v>
+        <v>8062.139999999999</v>
       </c>
       <c r="M63">
-        <v>9.79659</v>
+        <v>9796.59</v>
       </c>
       <c r="N63">
-        <v>11.6534</v>
+        <v>11653.4</v>
       </c>
       <c r="O63">
-        <v>13.398</v>
+        <v>13398</v>
       </c>
       <c r="P63">
-        <v>15.1077</v>
+        <v>15107.7</v>
       </c>
       <c r="Q63">
-        <v>16.8404</v>
+        <v>16840.4</v>
       </c>
       <c r="R63">
-        <v>18.6552</v>
+        <v>18655.2</v>
       </c>
       <c r="S63">
-        <v>20.6</v>
+        <v>20600</v>
       </c>
       <c r="T63">
-        <v>22.6914</v>
+        <v>22691.4</v>
       </c>
       <c r="U63">
-        <v>24.8824</v>
+        <v>24882.4</v>
       </c>
       <c r="V63">
-        <v>27.1532</v>
+        <v>27153.2</v>
       </c>
       <c r="W63">
-        <v>29.5032</v>
+        <v>29503.2</v>
       </c>
       <c r="X63">
-        <v>31.9742</v>
+        <v>31974.2</v>
       </c>
       <c r="Y63">
-        <v>34.5945</v>
+        <v>34594.5</v>
       </c>
       <c r="Z63">
-        <v>37.3883</v>
+        <v>37388.3</v>
       </c>
       <c r="AA63">
-        <v>40.357</v>
+        <v>40357</v>
       </c>
     </row>
     <row r="64" spans="1:27">
@@ -5830,70 +5830,70 @@
         <v>67</v>
       </c>
       <c r="F64">
-        <v>1.11852</v>
+        <v>1118.52</v>
       </c>
       <c r="G64">
-        <v>9.410970000000001</v>
+        <v>9410.970000000001</v>
       </c>
       <c r="H64">
-        <v>19.2905</v>
+        <v>19290.5</v>
       </c>
       <c r="I64">
-        <v>22.2535</v>
+        <v>22253.5</v>
       </c>
       <c r="J64">
-        <v>26.5008</v>
+        <v>26500.8</v>
       </c>
       <c r="K64">
-        <v>31.4259</v>
+        <v>31425.9</v>
       </c>
       <c r="L64">
-        <v>35.7841</v>
+        <v>35784.10000000001</v>
       </c>
       <c r="M64">
-        <v>40.7999</v>
+        <v>40799.9</v>
       </c>
       <c r="N64">
-        <v>44.3752</v>
+        <v>44375.2</v>
       </c>
       <c r="O64">
-        <v>46.104</v>
+        <v>46104</v>
       </c>
       <c r="P64">
-        <v>47.9292</v>
+        <v>47929.2</v>
       </c>
       <c r="Q64">
-        <v>50.0505</v>
+        <v>50050.5</v>
       </c>
       <c r="R64">
-        <v>52.5941</v>
+        <v>52594.1</v>
       </c>
       <c r="S64">
-        <v>55.4769</v>
+        <v>55476.9</v>
       </c>
       <c r="T64">
-        <v>58.5921</v>
+        <v>58592.1</v>
       </c>
       <c r="U64">
-        <v>61.9716</v>
+        <v>61971.60000000001</v>
       </c>
       <c r="V64">
-        <v>65.59010000000001</v>
+        <v>65590.10000000001</v>
       </c>
       <c r="W64">
-        <v>69.3043</v>
+        <v>69304.3</v>
       </c>
       <c r="X64">
-        <v>72.9824</v>
+        <v>72982.39999999999</v>
       </c>
       <c r="Y64">
-        <v>76.5656</v>
+        <v>76565.60000000001</v>
       </c>
       <c r="Z64">
-        <v>79.9969</v>
+        <v>79996.89999999999</v>
       </c>
       <c r="AA64">
-        <v>83.28149999999999</v>
+        <v>83281.5</v>
       </c>
     </row>
     <row r="65" spans="1:27">
@@ -5913,70 +5913,70 @@
         <v>67</v>
       </c>
       <c r="F65">
-        <v>15.979</v>
+        <v>15979</v>
       </c>
       <c r="G65">
-        <v>22.587</v>
+        <v>22587</v>
       </c>
       <c r="H65">
-        <v>30.0655</v>
+        <v>30065.5</v>
       </c>
       <c r="I65">
-        <v>30.1214</v>
+        <v>30121.4</v>
       </c>
       <c r="J65">
-        <v>32.3356</v>
+        <v>32335.6</v>
       </c>
       <c r="K65">
-        <v>34.4662</v>
+        <v>34466.2</v>
       </c>
       <c r="L65">
-        <v>37.6444</v>
+        <v>37644.39999999999</v>
       </c>
       <c r="M65">
-        <v>40.405</v>
+        <v>40405</v>
       </c>
       <c r="N65">
-        <v>42.7157</v>
+        <v>42715.7</v>
       </c>
       <c r="O65">
-        <v>44.7981</v>
+        <v>44798.1</v>
       </c>
       <c r="P65">
-        <v>46.7968</v>
+        <v>46796.8</v>
       </c>
       <c r="Q65">
-        <v>48.7512</v>
+        <v>48751.2</v>
       </c>
       <c r="R65">
-        <v>50.8047</v>
+        <v>50804.7</v>
       </c>
       <c r="S65">
-        <v>52.9054</v>
+        <v>52905.4</v>
       </c>
       <c r="T65">
-        <v>55.0502</v>
+        <v>55050.2</v>
       </c>
       <c r="U65">
-        <v>57.1402</v>
+        <v>57140.2</v>
       </c>
       <c r="V65">
-        <v>59.2124</v>
+        <v>59212.4</v>
       </c>
       <c r="W65">
-        <v>61.342</v>
+        <v>61342</v>
       </c>
       <c r="X65">
-        <v>63.5861</v>
+        <v>63586.1</v>
       </c>
       <c r="Y65">
-        <v>65.95610000000001</v>
+        <v>65956.10000000001</v>
       </c>
       <c r="Z65">
-        <v>68.4171</v>
+        <v>68417.10000000001</v>
       </c>
       <c r="AA65">
-        <v>70.9269</v>
+        <v>70926.90000000001</v>
       </c>
     </row>
     <row r="66" spans="1:27">
@@ -5996,70 +5996,70 @@
         <v>67</v>
       </c>
       <c r="F66">
-        <v>4.41003</v>
+        <v>4410.03</v>
       </c>
       <c r="G66">
-        <v>17.5073</v>
+        <v>17507.3</v>
       </c>
       <c r="H66">
-        <v>6.27935</v>
+        <v>6279.35</v>
       </c>
       <c r="I66">
-        <v>6.53098</v>
+        <v>6530.98</v>
       </c>
       <c r="J66">
-        <v>5.91047</v>
+        <v>5910.47</v>
       </c>
       <c r="K66">
-        <v>6.34939</v>
+        <v>6349.389999999999</v>
       </c>
       <c r="L66">
-        <v>6.3315</v>
+        <v>6331.5</v>
       </c>
       <c r="M66">
-        <v>7.78336</v>
+        <v>7783.36</v>
       </c>
       <c r="N66">
-        <v>9.425649999999999</v>
+        <v>9425.65</v>
       </c>
       <c r="O66">
-        <v>11.1969</v>
+        <v>11196.9</v>
       </c>
       <c r="P66">
-        <v>13.0514</v>
+        <v>13051.4</v>
       </c>
       <c r="Q66">
-        <v>15.0243</v>
+        <v>15024.3</v>
       </c>
       <c r="R66">
-        <v>17.1717</v>
+        <v>17171.7</v>
       </c>
       <c r="S66">
-        <v>19.5256</v>
+        <v>19525.6</v>
       </c>
       <c r="T66">
-        <v>22.0548</v>
+        <v>22054.8</v>
       </c>
       <c r="U66">
-        <v>24.7073</v>
+        <v>24707.3</v>
       </c>
       <c r="V66">
-        <v>27.4369</v>
+        <v>27436.9</v>
       </c>
       <c r="W66">
-        <v>30.2488</v>
+        <v>30248.8</v>
       </c>
       <c r="X66">
-        <v>33.2092</v>
+        <v>33209.2</v>
       </c>
       <c r="Y66">
-        <v>36.3679</v>
+        <v>36367.9</v>
       </c>
       <c r="Z66">
-        <v>39.7417</v>
+        <v>39741.7</v>
       </c>
       <c r="AA66">
-        <v>43.3506</v>
+        <v>43350.6</v>
       </c>
     </row>
     <row r="67" spans="1:27">
@@ -6073,76 +6073,76 @@
         <v>61</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>180094.897</v>
       </c>
       <c r="G67">
-        <v>0.322944</v>
+        <v>259687.525</v>
       </c>
       <c r="H67">
-        <v>0.603615</v>
+        <v>322674.47</v>
       </c>
       <c r="I67">
-        <v>0.721912</v>
+        <v>353348.91</v>
       </c>
       <c r="J67">
-        <v>0.862991</v>
+        <v>385621.48</v>
       </c>
       <c r="K67">
-        <v>1.02495</v>
+        <v>408065.39</v>
       </c>
       <c r="L67">
-        <v>1.12292</v>
+        <v>451273.4</v>
       </c>
       <c r="M67">
-        <v>1.25038</v>
+        <v>503232.63</v>
       </c>
       <c r="N67">
-        <v>1.3808</v>
+        <v>557003.01</v>
       </c>
       <c r="O67">
-        <v>1.52164</v>
+        <v>610417.6800000001</v>
       </c>
       <c r="P67">
-        <v>1.63928</v>
+        <v>666020.52</v>
       </c>
       <c r="Q67">
-        <v>1.7217</v>
+        <v>724021.52</v>
       </c>
       <c r="R67">
-        <v>1.7814</v>
+        <v>786322.8</v>
       </c>
       <c r="S67">
-        <v>1.82932</v>
+        <v>854003.05</v>
       </c>
       <c r="T67">
-        <v>1.86936</v>
+        <v>927259.6900000001</v>
       </c>
       <c r="U67">
-        <v>1.90241</v>
+        <v>1003976.64</v>
       </c>
       <c r="V67">
-        <v>1.92946</v>
+        <v>1083521.78</v>
       </c>
       <c r="W67">
-        <v>1.95125</v>
+        <v>1165647.33</v>
       </c>
       <c r="X67">
-        <v>1.96792</v>
+        <v>1250871.57</v>
       </c>
       <c r="Y67">
-        <v>1.97883</v>
+        <v>1339855.41</v>
       </c>
       <c r="Z67">
-        <v>1.98361</v>
+        <v>1432712.02</v>
       </c>
       <c r="AA67">
-        <v>1.98268</v>
+        <v>1529041.56</v>
       </c>
     </row>
     <row r="68" spans="1:27">
@@ -6150,82 +6150,82 @@
         <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C68" t="s">
         <v>61</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E68" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F68">
-        <v>2.685467169</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>6.887464960700001</v>
+        <v>0.322944</v>
       </c>
       <c r="H68">
-        <v>12.0500971124</v>
+        <v>0.603615</v>
       </c>
       <c r="I68">
-        <v>17.38970952133</v>
+        <v>0.721912</v>
       </c>
       <c r="J68">
-        <v>21.575193945352</v>
+        <v>0.862991</v>
       </c>
       <c r="K68">
-        <v>25.175611518137</v>
+        <v>1.02495</v>
       </c>
       <c r="L68">
-        <v>29.6799011937504</v>
+        <v>1.12292</v>
       </c>
       <c r="M68">
-        <v>35.25415651185492</v>
+        <v>1.25038</v>
       </c>
       <c r="N68">
-        <v>43.33268921254802</v>
+        <v>1.3808</v>
       </c>
       <c r="O68">
-        <v>30.47269563783445</v>
+        <v>1.52164</v>
       </c>
       <c r="P68">
-        <v>13.79754081232854</v>
+        <v>1.63928</v>
       </c>
       <c r="Q68">
-        <v>2.041708732643872</v>
+        <v>1.7217</v>
       </c>
       <c r="R68">
-        <v>-5.925266621156727</v>
+        <v>1.7814</v>
       </c>
       <c r="S68">
-        <v>-7.947540323759798</v>
+        <v>1.82932</v>
       </c>
       <c r="T68">
-        <v>-6.990123235860637</v>
+        <v>1.86936</v>
       </c>
       <c r="U68">
-        <v>-4.839004425530838</v>
+        <v>1.90241</v>
       </c>
       <c r="V68">
-        <v>-4.661874492421879</v>
+        <v>1.92946</v>
       </c>
       <c r="W68">
-        <v>-4.097005026597143</v>
+        <v>1.95125</v>
       </c>
       <c r="X68">
-        <v>-4.429309910501796</v>
+        <v>1.96792</v>
       </c>
       <c r="Y68">
-        <v>-4.994005034478003</v>
+        <v>1.97883</v>
       </c>
       <c r="Z68">
-        <v>-6.011536890919284</v>
+        <v>1.98361</v>
       </c>
       <c r="AA68">
-        <v>2.717508635729339</v>
+        <v>1.98268</v>
       </c>
     </row>
     <row r="69" spans="1:27">
@@ -6233,7 +6233,7 @@
         <v>27</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
         <v>61</v>
@@ -6245,70 +6245,70 @@
         <v>69</v>
       </c>
       <c r="F69">
-        <v>19.414345079</v>
+        <v>2.685467169</v>
       </c>
       <c r="G69">
-        <v>67.418306415765</v>
+        <v>6.887464960700001</v>
       </c>
       <c r="H69">
-        <v>112.17997964207</v>
+        <v>12.0500971124</v>
       </c>
       <c r="I69">
-        <v>133.758375228078</v>
+        <v>17.38970952133</v>
       </c>
       <c r="J69">
-        <v>153.94569403639</v>
+        <v>21.575193945352</v>
       </c>
       <c r="K69">
-        <v>169.61551508994</v>
+        <v>25.175611518137</v>
       </c>
       <c r="L69">
-        <v>185.70838925279</v>
+        <v>29.6799011937504</v>
       </c>
       <c r="M69">
-        <v>201.487504915285</v>
+        <v>35.25415651185492</v>
       </c>
       <c r="N69">
-        <v>223.669211484696</v>
+        <v>43.33268921254802</v>
       </c>
       <c r="O69">
-        <v>160.4260148986938</v>
+        <v>30.47269563783445</v>
       </c>
       <c r="P69">
-        <v>122.7626988232123</v>
+        <v>13.79754081232854</v>
       </c>
       <c r="Q69">
-        <v>98.99300586475354</v>
+        <v>2.041708732643872</v>
       </c>
       <c r="R69">
-        <v>90.95656537486104</v>
+        <v>-5.925266621156727</v>
       </c>
       <c r="S69">
-        <v>88.03105067199529</v>
+        <v>-7.947540323759798</v>
       </c>
       <c r="T69">
-        <v>84.80332044181259</v>
+        <v>-6.990123235860637</v>
       </c>
       <c r="U69">
-        <v>80.3948413199254</v>
+        <v>-4.839004425530838</v>
       </c>
       <c r="V69">
-        <v>73.92235401362537</v>
+        <v>-4.661874492421879</v>
       </c>
       <c r="W69">
-        <v>66.01053741786473</v>
+        <v>-4.097005026597143</v>
       </c>
       <c r="X69">
-        <v>58.3929079179662</v>
+        <v>-4.429309910501796</v>
       </c>
       <c r="Y69">
-        <v>46.66676791626917</v>
+        <v>-4.994005034478003</v>
       </c>
       <c r="Z69">
-        <v>36.66123396035743</v>
+        <v>-6.011536890919284</v>
       </c>
       <c r="AA69">
-        <v>28.7743615725999</v>
+        <v>2.717508635729339</v>
       </c>
     </row>
     <row r="70" spans="1:27">
@@ -6316,7 +6316,7 @@
         <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
         <v>61</v>
@@ -6328,70 +6328,70 @@
         <v>69</v>
       </c>
       <c r="F70">
-        <v>4.613721474</v>
+        <v>19.414345079</v>
       </c>
       <c r="G70">
-        <v>12.4200417986</v>
+        <v>67.418306415765</v>
       </c>
       <c r="H70">
-        <v>13.9510607976</v>
+        <v>112.17997964207</v>
       </c>
       <c r="I70">
-        <v>16.300991368</v>
+        <v>133.758375228078</v>
       </c>
       <c r="J70">
-        <v>23.56070651995</v>
+        <v>153.94569403639</v>
       </c>
       <c r="K70">
-        <v>23.4619035927</v>
+        <v>169.61551508994</v>
       </c>
       <c r="L70">
-        <v>28.90998029979</v>
+        <v>185.70838925279</v>
       </c>
       <c r="M70">
-        <v>36.24443325298654</v>
+        <v>201.487504915285</v>
       </c>
       <c r="N70">
-        <v>45.71386234336008</v>
+        <v>223.669211484696</v>
       </c>
       <c r="O70">
-        <v>29.57968944975158</v>
+        <v>160.4260148986938</v>
       </c>
       <c r="P70">
-        <v>17.12456672854569</v>
+        <v>122.7626988232123</v>
       </c>
       <c r="Q70">
-        <v>9.622278200216709</v>
+        <v>98.99300586475354</v>
       </c>
       <c r="R70">
-        <v>6.108903058258133</v>
+        <v>90.95656537486104</v>
       </c>
       <c r="S70">
-        <v>5.471853025999273</v>
+        <v>88.03105067199529</v>
       </c>
       <c r="T70">
-        <v>6.83692540700299</v>
+        <v>84.80332044181259</v>
       </c>
       <c r="U70">
-        <v>8.607551128160928</v>
+        <v>80.3948413199254</v>
       </c>
       <c r="V70">
-        <v>8.945946966387528</v>
+        <v>73.92235401362537</v>
       </c>
       <c r="W70">
-        <v>8.663940780062116</v>
+        <v>66.01053741786473</v>
       </c>
       <c r="X70">
-        <v>6.938177474819254</v>
+        <v>58.3929079179662</v>
       </c>
       <c r="Y70">
-        <v>14.18441470252098</v>
+        <v>46.66676791626917</v>
       </c>
       <c r="Z70">
-        <v>11.77907180701449</v>
+        <v>36.66123396035743</v>
       </c>
       <c r="AA70">
-        <v>7.609473338437544</v>
+        <v>28.7743615725999</v>
       </c>
     </row>
     <row r="71" spans="1:27">
@@ -6399,7 +6399,7 @@
         <v>27</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C71" t="s">
         <v>61</v>
@@ -6411,70 +6411,70 @@
         <v>69</v>
       </c>
       <c r="F71">
-        <v>22.860556731</v>
+        <v>4.613721474</v>
       </c>
       <c r="G71">
-        <v>30.97663263963</v>
+        <v>12.4200417986</v>
       </c>
       <c r="H71">
-        <v>33.21583657488</v>
+        <v>13.9510607976</v>
       </c>
       <c r="I71">
-        <v>38.91733828508</v>
+        <v>16.300991368</v>
       </c>
       <c r="J71">
-        <v>55.42842773779999</v>
+        <v>23.56070651995</v>
       </c>
       <c r="K71">
-        <v>61.20581912982</v>
+        <v>23.4619035927</v>
       </c>
       <c r="L71">
-        <v>72.75787010825</v>
+        <v>28.90998029979</v>
       </c>
       <c r="M71">
-        <v>81.5580822965</v>
+        <v>36.24443325298654</v>
       </c>
       <c r="N71">
-        <v>98.16805181739998</v>
+        <v>45.71386234336008</v>
       </c>
       <c r="O71">
-        <v>77.15539544444499</v>
+        <v>29.57968944975158</v>
       </c>
       <c r="P71">
-        <v>58.4628243552314</v>
+        <v>17.12456672854569</v>
       </c>
       <c r="Q71">
-        <v>44.21759800751593</v>
+        <v>9.622278200216709</v>
       </c>
       <c r="R71">
-        <v>34.07172575993715</v>
+        <v>6.108903058258133</v>
       </c>
       <c r="S71">
-        <v>30.37640324331296</v>
+        <v>5.471853025999273</v>
       </c>
       <c r="T71">
-        <v>32.88198059507673</v>
+        <v>6.83692540700299</v>
       </c>
       <c r="U71">
-        <v>39.97735690589082</v>
+        <v>8.607551128160928</v>
       </c>
       <c r="V71">
-        <v>44.96388966528768</v>
+        <v>8.945946966387528</v>
       </c>
       <c r="W71">
-        <v>47.35363534744138</v>
+        <v>8.663940780062116</v>
       </c>
       <c r="X71">
-        <v>44.36555415594469</v>
+        <v>6.938177474819254</v>
       </c>
       <c r="Y71">
-        <v>37.05824326796628</v>
+        <v>14.18441470252098</v>
       </c>
       <c r="Z71">
-        <v>50.15449285868311</v>
+        <v>11.77907180701449</v>
       </c>
       <c r="AA71">
-        <v>35.91511258128122</v>
+        <v>7.609473338437544</v>
       </c>
     </row>
     <row r="72" spans="1:27">
@@ -6482,7 +6482,7 @@
         <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
         <v>61</v>
@@ -6494,70 +6494,70 @@
         <v>69</v>
       </c>
       <c r="F72">
-        <v>11.54704905</v>
+        <v>22.860556731</v>
       </c>
       <c r="G72">
-        <v>27.5871312732</v>
+        <v>30.97663263963</v>
       </c>
       <c r="H72">
-        <v>41.6122021432</v>
+        <v>33.21583657488</v>
       </c>
       <c r="I72">
-        <v>48.7586034824</v>
+        <v>38.91733828508</v>
       </c>
       <c r="J72">
-        <v>53.5778487623</v>
+        <v>55.42842773779999</v>
       </c>
       <c r="K72">
-        <v>49.96180334465</v>
+        <v>61.20581912982</v>
       </c>
       <c r="L72">
-        <v>48.7761036891</v>
+        <v>72.75787010825</v>
       </c>
       <c r="M72">
-        <v>49.332576064742</v>
+        <v>81.5580822965</v>
       </c>
       <c r="N72">
-        <v>50.5482709285875</v>
+        <v>98.16805181739998</v>
       </c>
       <c r="O72">
-        <v>29.6871084809318</v>
+        <v>77.15539544444499</v>
       </c>
       <c r="P72">
-        <v>14.9342326120261</v>
+        <v>58.4628243552314</v>
       </c>
       <c r="Q72">
-        <v>4.086036087281058</v>
+        <v>44.21759800751593</v>
       </c>
       <c r="R72">
-        <v>-4.549897165352234</v>
+        <v>34.07172575993715</v>
       </c>
       <c r="S72">
-        <v>-12.12673195008975</v>
+        <v>30.37640324331296</v>
       </c>
       <c r="T72">
-        <v>-18.40686673701209</v>
+        <v>32.88198059507673</v>
       </c>
       <c r="U72">
-        <v>-25.96740418060439</v>
+        <v>39.97735690589082</v>
       </c>
       <c r="V72">
-        <v>-34.97266696393282</v>
+        <v>44.96388966528768</v>
       </c>
       <c r="W72">
-        <v>-45.36709152831285</v>
+        <v>47.35363534744138</v>
       </c>
       <c r="X72">
-        <v>-59.91904342892133</v>
+        <v>44.36555415594469</v>
       </c>
       <c r="Y72">
-        <v>-78.30374367776464</v>
+        <v>37.05824326796628</v>
       </c>
       <c r="Z72">
-        <v>-95.53912621552765</v>
+        <v>50.15449285868311</v>
       </c>
       <c r="AA72">
-        <v>-115.6364055343506</v>
+        <v>35.91511258128122</v>
       </c>
     </row>
     <row r="73" spans="1:27">
@@ -6565,7 +6565,7 @@
         <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C73" t="s">
         <v>61</v>
@@ -6577,70 +6577,70 @@
         <v>69</v>
       </c>
       <c r="F73">
-        <v>29.28685081</v>
+        <v>11.54704905</v>
       </c>
       <c r="G73">
-        <v>84.2464724391</v>
+        <v>27.5871312732</v>
       </c>
       <c r="H73">
-        <v>117.181117219</v>
+        <v>41.6122021432</v>
       </c>
       <c r="I73">
-        <v>126.574947528</v>
+        <v>48.7586034824</v>
       </c>
       <c r="J73">
-        <v>122.820126958</v>
+        <v>53.5778487623</v>
       </c>
       <c r="K73">
-        <v>117.6822505352</v>
+        <v>49.96180334465</v>
       </c>
       <c r="L73">
-        <v>137.9190872613002</v>
+        <v>48.7761036891</v>
       </c>
       <c r="M73">
-        <v>138.8640115733416</v>
+        <v>49.332576064742</v>
       </c>
       <c r="N73">
-        <v>139.6485659666913</v>
+        <v>50.5482709285875</v>
       </c>
       <c r="O73">
-        <v>76.89058590529464</v>
+        <v>29.6871084809318</v>
       </c>
       <c r="P73">
-        <v>59.18452637549662</v>
+        <v>14.9342326120261</v>
       </c>
       <c r="Q73">
-        <v>42.12165614973082</v>
+        <v>4.086036087281058</v>
       </c>
       <c r="R73">
-        <v>25.15205272189603</v>
+        <v>-4.549897165352234</v>
       </c>
       <c r="S73">
-        <v>9.408131732297781</v>
+        <v>-12.12673195008975</v>
       </c>
       <c r="T73">
-        <v>-3.088503163344979</v>
+        <v>-18.40686673701209</v>
       </c>
       <c r="U73">
-        <v>-15.9545061178727</v>
+        <v>-25.96740418060439</v>
       </c>
       <c r="V73">
-        <v>-28.14473633714336</v>
+        <v>-34.97266696393282</v>
       </c>
       <c r="W73">
-        <v>-43.46183517562861</v>
+        <v>-45.36709152831285</v>
       </c>
       <c r="X73">
-        <v>-63.86875543216812</v>
+        <v>-59.91904342892133</v>
       </c>
       <c r="Y73">
-        <v>-90.20039172666723</v>
+        <v>-78.30374367776464</v>
       </c>
       <c r="Z73">
-        <v>-118.242646307418</v>
+        <v>-95.53912621552765</v>
       </c>
       <c r="AA73">
-        <v>-149.9407850193919</v>
+        <v>-115.6364055343506</v>
       </c>
     </row>
     <row r="74" spans="1:27">
@@ -6648,7 +6648,7 @@
         <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C74" t="s">
         <v>61</v>
@@ -6660,70 +6660,70 @@
         <v>69</v>
       </c>
       <c r="F74">
-        <v>26.92539474</v>
+        <v>29.28685081</v>
       </c>
       <c r="G74">
-        <v>60.48794375234</v>
+        <v>84.2464724391</v>
       </c>
       <c r="H74">
-        <v>99.26631382559999</v>
+        <v>117.181117219</v>
       </c>
       <c r="I74">
-        <v>117.7811917316</v>
+        <v>126.574947528</v>
       </c>
       <c r="J74">
-        <v>140.179054265</v>
+        <v>122.820126958</v>
       </c>
       <c r="K74">
-        <v>133.9896748012</v>
+        <v>117.6822505352</v>
       </c>
       <c r="L74">
-        <v>139.6261193277</v>
+        <v>137.9190872613002</v>
       </c>
       <c r="M74">
-        <v>142.48412675956</v>
+        <v>138.8640115733416</v>
       </c>
       <c r="N74">
-        <v>150.84721799004</v>
+        <v>139.6485659666913</v>
       </c>
       <c r="O74">
-        <v>83.87000587430001</v>
+        <v>76.89058590529464</v>
       </c>
       <c r="P74">
-        <v>44.54758066640262</v>
+        <v>59.18452637549662</v>
       </c>
       <c r="Q74">
-        <v>10.11339379799618</v>
+        <v>42.12165614973082</v>
       </c>
       <c r="R74">
-        <v>-24.78607977745955</v>
+        <v>25.15205272189603</v>
       </c>
       <c r="S74">
-        <v>-57.64480321884018</v>
+        <v>9.408131732297781</v>
       </c>
       <c r="T74">
-        <v>-83.86245931175631</v>
+        <v>-3.088503163344979</v>
       </c>
       <c r="U74">
-        <v>-108.0360248416964</v>
+        <v>-15.9545061178727</v>
       </c>
       <c r="V74">
-        <v>-133.8943280181178</v>
+        <v>-28.14473633714336</v>
       </c>
       <c r="W74">
-        <v>-162.6484364179364</v>
+        <v>-43.46183517562861</v>
       </c>
       <c r="X74">
-        <v>-198.1848048181328</v>
+        <v>-63.86875543216812</v>
       </c>
       <c r="Y74">
-        <v>-246.5704987087828</v>
+        <v>-90.20039172666723</v>
       </c>
       <c r="Z74">
-        <v>-294.9332923104827</v>
+        <v>-118.242646307418</v>
       </c>
       <c r="AA74">
-        <v>-351.6766012392087</v>
+        <v>-149.9407850193919</v>
       </c>
     </row>
     <row r="75" spans="1:27">
@@ -6731,7 +6731,7 @@
         <v>27</v>
       </c>
       <c r="B75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
         <v>61</v>
@@ -6743,70 +6743,70 @@
         <v>69</v>
       </c>
       <c r="F75">
-        <v>55.12194158</v>
+        <v>26.92539474</v>
       </c>
       <c r="G75">
-        <v>120.210906461</v>
+        <v>60.48794375234</v>
       </c>
       <c r="H75">
-        <v>160.662459613</v>
+        <v>99.26631382559999</v>
       </c>
       <c r="I75">
-        <v>155.493415164</v>
+        <v>117.7811917316</v>
       </c>
       <c r="J75">
-        <v>165.293038857</v>
+        <v>140.179054265</v>
       </c>
       <c r="K75">
-        <v>162.740458593</v>
+        <v>133.9896748012</v>
       </c>
       <c r="L75">
-        <v>180.08926626292</v>
+        <v>139.6261193277</v>
       </c>
       <c r="M75">
-        <v>180.119148782225</v>
+        <v>142.48412675956</v>
       </c>
       <c r="N75">
-        <v>181.861939585569</v>
+        <v>150.84721799004</v>
       </c>
       <c r="O75">
-        <v>103.226799718487</v>
+        <v>83.87000587430001</v>
       </c>
       <c r="P75">
-        <v>58.529036573288</v>
+        <v>44.54758066640262</v>
       </c>
       <c r="Q75">
-        <v>36.56560799817306</v>
+        <v>10.11339379799618</v>
       </c>
       <c r="R75">
-        <v>13.34895068253516</v>
+        <v>-24.78607977745955</v>
       </c>
       <c r="S75">
-        <v>-5.204360487415164</v>
+        <v>-57.64480321884018</v>
       </c>
       <c r="T75">
-        <v>-16.69052619318921</v>
+        <v>-83.86245931175631</v>
       </c>
       <c r="U75">
-        <v>-24.13683209991486</v>
+        <v>-108.0360248416964</v>
       </c>
       <c r="V75">
-        <v>-26.73905336906643</v>
+        <v>-133.8943280181178</v>
       </c>
       <c r="W75">
-        <v>-28.21973128733085</v>
+        <v>-162.6484364179364</v>
       </c>
       <c r="X75">
-        <v>-30.54635651135812</v>
+        <v>-198.1848048181328</v>
       </c>
       <c r="Y75">
-        <v>-31.68479824649337</v>
+        <v>-246.5704987087828</v>
       </c>
       <c r="Z75">
-        <v>-33.74126472307793</v>
+        <v>-294.9332923104827</v>
       </c>
       <c r="AA75">
-        <v>-37.72455296431362</v>
+        <v>-351.6766012392087</v>
       </c>
     </row>
     <row r="76" spans="1:27">
@@ -6814,7 +6814,7 @@
         <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C76" t="s">
         <v>61</v>
@@ -6826,70 +6826,70 @@
         <v>69</v>
       </c>
       <c r="F76">
-        <v>11.2100710294036</v>
+        <v>55.12194158</v>
       </c>
       <c r="G76">
-        <v>31.122462663253</v>
+        <v>120.210906461</v>
       </c>
       <c r="H76">
-        <v>46.914597290169</v>
+        <v>160.662459613</v>
       </c>
       <c r="I76">
-        <v>53.325731609493</v>
+        <v>155.493415164</v>
       </c>
       <c r="J76">
-        <v>57.46169756462</v>
+        <v>165.293038857</v>
       </c>
       <c r="K76">
-        <v>53.117951993791</v>
+        <v>162.740458593</v>
       </c>
       <c r="L76">
-        <v>55.86227052748</v>
+        <v>180.08926626292</v>
       </c>
       <c r="M76">
-        <v>58.548530458943</v>
+        <v>180.119148782225</v>
       </c>
       <c r="N76">
-        <v>62.338248653344</v>
+        <v>181.861939585569</v>
       </c>
       <c r="O76">
-        <v>36.769638392241</v>
+        <v>103.226799718487</v>
       </c>
       <c r="P76">
-        <v>18.0675394298295</v>
+        <v>58.529036573288</v>
       </c>
       <c r="Q76">
-        <v>2.15860550968747</v>
+        <v>36.56560799817306</v>
       </c>
       <c r="R76">
-        <v>-13.32884758456481</v>
+        <v>13.34895068253516</v>
       </c>
       <c r="S76">
-        <v>-26.83138265962117</v>
+        <v>-5.204360487415164</v>
       </c>
       <c r="T76">
-        <v>-38.69066094558481</v>
+        <v>-16.69052619318921</v>
       </c>
       <c r="U76">
-        <v>-50.67968794336908</v>
+        <v>-24.13683209991486</v>
       </c>
       <c r="V76">
-        <v>-60.36367444451269</v>
+        <v>-26.73905336906643</v>
       </c>
       <c r="W76">
-        <v>-67.10740113734255</v>
+        <v>-28.21973128733085</v>
       </c>
       <c r="X76">
-        <v>-72.93549736616698</v>
+        <v>-30.54635651135812</v>
       </c>
       <c r="Y76">
-        <v>-75.68539964091671</v>
+        <v>-31.68479824649337</v>
       </c>
       <c r="Z76">
-        <v>-76.79373107974949</v>
+        <v>-33.74126472307793</v>
       </c>
       <c r="AA76">
-        <v>-74.26527833420437</v>
+        <v>-37.72455296431362</v>
       </c>
     </row>
     <row r="77" spans="1:27">
@@ -6897,7 +6897,7 @@
         <v>27</v>
       </c>
       <c r="B77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C77" t="s">
         <v>61</v>
@@ -6909,70 +6909,70 @@
         <v>69</v>
       </c>
       <c r="F77">
-        <v>65.09281855</v>
+        <v>11.2100710294036</v>
       </c>
       <c r="G77">
-        <v>157.1541007854</v>
+        <v>31.122462663253</v>
       </c>
       <c r="H77">
-        <v>115.222417852</v>
+        <v>46.914597290169</v>
       </c>
       <c r="I77">
-        <v>138.322717767</v>
+        <v>53.325731609493</v>
       </c>
       <c r="J77">
-        <v>121.50226065</v>
+        <v>57.46169756462</v>
       </c>
       <c r="K77">
-        <v>141.959463474</v>
+        <v>53.117951993791</v>
       </c>
       <c r="L77">
-        <v>151.432908404874</v>
+        <v>55.86227052748</v>
       </c>
       <c r="M77">
-        <v>156.976801022152</v>
+        <v>58.548530458943</v>
       </c>
       <c r="N77">
-        <v>162.977795004884</v>
+        <v>62.338248653344</v>
       </c>
       <c r="O77">
-        <v>94.555568048363</v>
+        <v>36.769638392241</v>
       </c>
       <c r="P77">
-        <v>67.4431918507818</v>
+        <v>18.0675394298295</v>
       </c>
       <c r="Q77">
-        <v>46.6775796211314</v>
+        <v>2.15860550968747</v>
       </c>
       <c r="R77">
-        <v>30.27903566230068</v>
+        <v>-13.32884758456481</v>
       </c>
       <c r="S77">
-        <v>14.67171476777385</v>
+        <v>-26.83138265962117</v>
       </c>
       <c r="T77">
-        <v>1.012523478036656</v>
+        <v>-38.69066094558481</v>
       </c>
       <c r="U77">
-        <v>-13.40017876046258</v>
+        <v>-50.67968794336908</v>
       </c>
       <c r="V77">
-        <v>-29.16946549728238</v>
+        <v>-60.36367444451269</v>
       </c>
       <c r="W77">
-        <v>-46.06279448336478</v>
+        <v>-67.10740113734255</v>
       </c>
       <c r="X77">
-        <v>-70.55751635041884</v>
+        <v>-72.93549736616698</v>
       </c>
       <c r="Y77">
-        <v>-96.75203053004846</v>
+        <v>-75.68539964091671</v>
       </c>
       <c r="Z77">
-        <v>-120.8455277390867</v>
+        <v>-76.79373107974949</v>
       </c>
       <c r="AA77">
-        <v>-152.6927090485523</v>
+        <v>-74.26527833420437</v>
       </c>
     </row>
     <row r="78" spans="1:27">
@@ -6980,7 +6980,7 @@
         <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
         <v>61</v>
@@ -6992,70 +6992,70 @@
         <v>69</v>
       </c>
       <c r="F78">
-        <v>199.4040951</v>
+        <v>65.09281855</v>
       </c>
       <c r="G78">
-        <v>706.64431908502</v>
+        <v>157.1541007854</v>
       </c>
       <c r="H78">
-        <v>1839.5118966448</v>
+        <v>115.222417852</v>
       </c>
       <c r="I78">
-        <v>2652.8656639431</v>
+        <v>138.322717767</v>
       </c>
       <c r="J78">
-        <v>3079.6009821626</v>
+        <v>121.50226065</v>
       </c>
       <c r="K78">
-        <v>3478.81594453961</v>
+        <v>141.959463474</v>
       </c>
       <c r="L78">
-        <v>3858.646748044429</v>
+        <v>151.432908404874</v>
       </c>
       <c r="M78">
-        <v>3894.360027938582</v>
+        <v>156.976801022152</v>
       </c>
       <c r="N78">
-        <v>3865.810264789333</v>
+        <v>162.977795004884</v>
       </c>
       <c r="O78">
-        <v>1480.10144716593</v>
+        <v>94.555568048363</v>
       </c>
       <c r="P78">
-        <v>713.0282151847026</v>
+        <v>67.4431918507818</v>
       </c>
       <c r="Q78">
-        <v>300.2960845298022</v>
+        <v>46.6775796211314</v>
       </c>
       <c r="R78">
-        <v>18.38215125808541</v>
+        <v>30.27903566230068</v>
       </c>
       <c r="S78">
-        <v>-190.7631764292504</v>
+        <v>14.67171476777385</v>
       </c>
       <c r="T78">
-        <v>-346.415247804918</v>
+        <v>1.012523478036656</v>
       </c>
       <c r="U78">
-        <v>-509.3470015725304</v>
+        <v>-13.40017876046258</v>
       </c>
       <c r="V78">
-        <v>-598.0619867729422</v>
+        <v>-29.16946549728238</v>
       </c>
       <c r="W78">
-        <v>-652.426655353833</v>
+        <v>-46.06279448336478</v>
       </c>
       <c r="X78">
-        <v>-684.5706971552613</v>
+        <v>-70.55751635041884</v>
       </c>
       <c r="Y78">
-        <v>-687.6046176659221</v>
+        <v>-96.75203053004846</v>
       </c>
       <c r="Z78">
-        <v>-682.292697548917</v>
+        <v>-120.8455277390867</v>
       </c>
       <c r="AA78">
-        <v>-714.452104825559</v>
+        <v>-152.6927090485523</v>
       </c>
     </row>
     <row r="79" spans="1:27">
@@ -7063,7 +7063,7 @@
         <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C79" t="s">
         <v>61</v>
@@ -7075,70 +7075,70 @@
         <v>69</v>
       </c>
       <c r="F79">
-        <v>6.135872179</v>
+        <v>199.4040951</v>
       </c>
       <c r="G79">
-        <v>15.7942725306</v>
+        <v>706.64431908502</v>
       </c>
       <c r="H79">
-        <v>18.11854172</v>
+        <v>1839.5118966448</v>
       </c>
       <c r="I79">
-        <v>21.833005389</v>
+        <v>2652.8656639431</v>
       </c>
       <c r="J79">
-        <v>27.447622871</v>
+        <v>3079.6009821626</v>
       </c>
       <c r="K79">
-        <v>27.241888482</v>
+        <v>3478.81594453961</v>
       </c>
       <c r="L79">
-        <v>30.1220909911</v>
+        <v>3858.646748044429</v>
       </c>
       <c r="M79">
-        <v>31.761766533359</v>
+        <v>3894.360027938582</v>
       </c>
       <c r="N79">
-        <v>34.274787034104</v>
+        <v>3865.810264789333</v>
       </c>
       <c r="O79">
-        <v>19.830519149103</v>
+        <v>1480.10144716593</v>
       </c>
       <c r="P79">
-        <v>10.510786995665</v>
+        <v>713.0282151847026</v>
       </c>
       <c r="Q79">
-        <v>2.711312864826869</v>
+        <v>300.2960845298022</v>
       </c>
       <c r="R79">
-        <v>-4.010412893396711</v>
+        <v>18.38215125808541</v>
       </c>
       <c r="S79">
-        <v>-9.838802402041932</v>
+        <v>-190.7631764292504</v>
       </c>
       <c r="T79">
-        <v>-14.62830089344762</v>
+        <v>-346.415247804918</v>
       </c>
       <c r="U79">
-        <v>-20.04022930989466</v>
+        <v>-509.3470015725304</v>
       </c>
       <c r="V79">
-        <v>-25.87536598514086</v>
+        <v>-598.0619867729422</v>
       </c>
       <c r="W79">
-        <v>-31.50854990324867</v>
+        <v>-652.426655353833</v>
       </c>
       <c r="X79">
-        <v>-38.5084962934073</v>
+        <v>-684.5706971552613</v>
       </c>
       <c r="Y79">
-        <v>-46.44812545598441</v>
+        <v>-687.6046176659221</v>
       </c>
       <c r="Z79">
-        <v>-53.59251861854534</v>
+        <v>-682.292697548917</v>
       </c>
       <c r="AA79">
-        <v>-59.13857545525666</v>
+        <v>-714.452104825559</v>
       </c>
     </row>
     <row r="80" spans="1:27">
@@ -7146,7 +7146,7 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C80" t="s">
         <v>61</v>
@@ -7158,70 +7158,70 @@
         <v>69</v>
       </c>
       <c r="F80">
-        <v>131.704263407</v>
+        <v>6.135872179</v>
       </c>
       <c r="G80">
-        <v>282.850500476</v>
+        <v>15.7942725306</v>
       </c>
       <c r="H80">
-        <v>210.485102924</v>
+        <v>18.11854172</v>
       </c>
       <c r="I80">
-        <v>205.5846233015</v>
+        <v>21.833005389</v>
       </c>
       <c r="J80">
-        <v>189.7968319907</v>
+        <v>27.447622871</v>
       </c>
       <c r="K80">
-        <v>188.0197045795</v>
+        <v>27.241888482</v>
       </c>
       <c r="L80">
-        <v>202.4885030229</v>
+        <v>30.1220909911</v>
       </c>
       <c r="M80">
-        <v>201.936475463962</v>
+        <v>31.761766533359</v>
       </c>
       <c r="N80">
-        <v>199.443546438701</v>
+        <v>34.274787034104</v>
       </c>
       <c r="O80">
-        <v>99.88727870079768</v>
+        <v>19.830519149103</v>
       </c>
       <c r="P80">
-        <v>63.96238279099666</v>
+        <v>10.510786995665</v>
       </c>
       <c r="Q80">
-        <v>43.5585149205649</v>
+        <v>2.711312864826869</v>
       </c>
       <c r="R80">
-        <v>33.65470960665763</v>
+        <v>-4.010412893396711</v>
       </c>
       <c r="S80">
-        <v>29.12199272332229</v>
+        <v>-9.838802402041932</v>
       </c>
       <c r="T80">
-        <v>25.24677671953496</v>
+        <v>-14.62830089344762</v>
       </c>
       <c r="U80">
-        <v>21.48656963061465</v>
+        <v>-20.04022930989466</v>
       </c>
       <c r="V80">
-        <v>18.37936668591695</v>
+        <v>-25.87536598514086</v>
       </c>
       <c r="W80">
-        <v>15.45891678079367</v>
+        <v>-31.50854990324867</v>
       </c>
       <c r="X80">
-        <v>11.99894108059613</v>
+        <v>-38.5084962934073</v>
       </c>
       <c r="Y80">
-        <v>8.552204396628609</v>
+        <v>-46.44812545598441</v>
       </c>
       <c r="Z80">
-        <v>5.29605378122572</v>
+        <v>-53.59251861854534</v>
       </c>
       <c r="AA80">
-        <v>2.287909047134298</v>
+        <v>-59.13857545525666</v>
       </c>
     </row>
     <row r="81" spans="1:27">
@@ -7229,7 +7229,7 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C81" t="s">
         <v>61</v>
@@ -7241,70 +7241,70 @@
         <v>69</v>
       </c>
       <c r="F81">
-        <v>416.8498639239</v>
+        <v>131.704263407</v>
       </c>
       <c r="G81">
-        <v>931.175059547</v>
+        <v>282.850500476</v>
       </c>
       <c r="H81">
-        <v>979.573340683</v>
+        <v>210.485102924</v>
       </c>
       <c r="I81">
-        <v>890.880026408</v>
+        <v>205.5846233015</v>
       </c>
       <c r="J81">
-        <v>797.832774611</v>
+        <v>189.7968319907</v>
       </c>
       <c r="K81">
-        <v>684.474139468</v>
+        <v>188.0197045795</v>
       </c>
       <c r="L81">
-        <v>697.55274187591</v>
+        <v>202.4885030229</v>
       </c>
       <c r="M81">
-        <v>678.125083679018</v>
+        <v>201.936475463962</v>
       </c>
       <c r="N81">
-        <v>662.7527707655</v>
+        <v>199.443546438701</v>
       </c>
       <c r="O81">
-        <v>386.8461187908758</v>
+        <v>99.88727870079768</v>
       </c>
       <c r="P81">
-        <v>271.5632754678829</v>
+        <v>63.96238279099666</v>
       </c>
       <c r="Q81">
-        <v>175.7755552070184</v>
+        <v>43.5585149205649</v>
       </c>
       <c r="R81">
-        <v>156.514521972458</v>
+        <v>33.65470960665763</v>
       </c>
       <c r="S81">
-        <v>152.3609027712552</v>
+        <v>29.12199272332229</v>
       </c>
       <c r="T81">
-        <v>141.7889253415948</v>
+        <v>25.24677671953496</v>
       </c>
       <c r="U81">
-        <v>126.8257659546066</v>
+        <v>21.48656963061465</v>
       </c>
       <c r="V81">
-        <v>117.3808172700346</v>
+        <v>18.37936668591695</v>
       </c>
       <c r="W81">
-        <v>106.2802643560607</v>
+        <v>15.45891678079367</v>
       </c>
       <c r="X81">
-        <v>93.26346674304696</v>
+        <v>11.99894108059613</v>
       </c>
       <c r="Y81">
-        <v>76.59426324226926</v>
+        <v>8.552204396628609</v>
       </c>
       <c r="Z81">
-        <v>72.36625033714397</v>
+        <v>5.29605378122572</v>
       </c>
       <c r="AA81">
-        <v>60.35356496964448</v>
+        <v>2.287909047134298</v>
       </c>
     </row>
     <row r="82" spans="1:27">
@@ -7312,7 +7312,7 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C82" t="s">
         <v>61</v>
@@ -7324,70 +7324,70 @@
         <v>69</v>
       </c>
       <c r="F82">
-        <v>37.805100058</v>
+        <v>416.8498639239</v>
       </c>
       <c r="G82">
-        <v>113.071279975</v>
+        <v>931.175059547</v>
       </c>
       <c r="H82">
-        <v>117.12130277731</v>
+        <v>979.573340683</v>
       </c>
       <c r="I82">
-        <v>134.6139363766</v>
+        <v>890.880026408</v>
       </c>
       <c r="J82">
-        <v>147.9962126795</v>
+        <v>797.832774611</v>
       </c>
       <c r="K82">
-        <v>167.5352937504</v>
+        <v>684.474139468</v>
       </c>
       <c r="L82">
-        <v>194.65563035619</v>
+        <v>697.55274187591</v>
       </c>
       <c r="M82">
-        <v>209.48414834546</v>
+        <v>678.125083679018</v>
       </c>
       <c r="N82">
-        <v>221.53331477226</v>
+        <v>662.7527707655</v>
       </c>
       <c r="O82">
-        <v>135.7815042838007</v>
+        <v>386.8461187908758</v>
       </c>
       <c r="P82">
-        <v>94.3683556627245</v>
+        <v>271.5632754678829</v>
       </c>
       <c r="Q82">
-        <v>70.58513175367655</v>
+        <v>175.7755552070184</v>
       </c>
       <c r="R82">
-        <v>61.95041745518545</v>
+        <v>156.514521972458</v>
       </c>
       <c r="S82">
-        <v>57.0351676034341</v>
+        <v>152.3609027712552</v>
       </c>
       <c r="T82">
-        <v>52.32737614210357</v>
+        <v>141.7889253415948</v>
       </c>
       <c r="U82">
-        <v>47.5294207231469</v>
+        <v>126.8257659546066</v>
       </c>
       <c r="V82">
-        <v>42.99446129582498</v>
+        <v>117.3808172700346</v>
       </c>
       <c r="W82">
-        <v>38.21922001229224</v>
+        <v>106.2802643560607</v>
       </c>
       <c r="X82">
-        <v>33.33292309630156</v>
+        <v>93.26346674304696</v>
       </c>
       <c r="Y82">
-        <v>27.56471076244554</v>
+        <v>76.59426324226926</v>
       </c>
       <c r="Z82">
-        <v>19.78760590681228</v>
+        <v>72.36625033714397</v>
       </c>
       <c r="AA82">
-        <v>13.40318925659928</v>
+        <v>60.35356496964448</v>
       </c>
     </row>
     <row r="83" spans="1:27">
@@ -7395,7 +7395,7 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C83" t="s">
         <v>61</v>
@@ -7407,70 +7407,70 @@
         <v>69</v>
       </c>
       <c r="F83">
-        <v>11.976397889</v>
+        <v>37.805100058</v>
       </c>
       <c r="G83">
-        <v>21.76024062437</v>
+        <v>113.071279975</v>
       </c>
       <c r="H83">
-        <v>24.6177736181</v>
+        <v>117.12130277731</v>
       </c>
       <c r="I83">
-        <v>25.4130228792</v>
+        <v>134.6139363766</v>
       </c>
       <c r="J83">
-        <v>23.9233616458</v>
+        <v>147.9962126795</v>
       </c>
       <c r="K83">
-        <v>20.5572363508</v>
+        <v>167.5352937504</v>
       </c>
       <c r="L83">
-        <v>21.85989287321</v>
+        <v>194.65563035619</v>
       </c>
       <c r="M83">
-        <v>22.0061945598509</v>
+        <v>209.48414834546</v>
       </c>
       <c r="N83">
-        <v>23.4716648920859</v>
+        <v>221.53331477226</v>
       </c>
       <c r="O83">
-        <v>8.0040972578522</v>
+        <v>135.7815042838007</v>
       </c>
       <c r="P83">
-        <v>2.906242331618161</v>
+        <v>94.3683556627245</v>
       </c>
       <c r="Q83">
-        <v>0.0453164782284085</v>
+        <v>70.58513175367655</v>
       </c>
       <c r="R83">
-        <v>-1.805202224845626</v>
+        <v>61.95041745518545</v>
       </c>
       <c r="S83">
-        <v>-3.12084994089622</v>
+        <v>57.0351676034341</v>
       </c>
       <c r="T83">
-        <v>-3.507549308987473</v>
+        <v>52.32737614210357</v>
       </c>
       <c r="U83">
-        <v>-2.653942723459168</v>
+        <v>47.5294207231469</v>
       </c>
       <c r="V83">
-        <v>-1.640986365895647</v>
+        <v>42.99446129582498</v>
       </c>
       <c r="W83">
-        <v>-1.393899759111925</v>
+        <v>38.21922001229224</v>
       </c>
       <c r="X83">
-        <v>-1.710144543430045</v>
+        <v>33.33292309630156</v>
       </c>
       <c r="Y83">
-        <v>-1.842577505699234</v>
+        <v>27.56471076244554</v>
       </c>
       <c r="Z83">
-        <v>-2.05133623922913</v>
+        <v>19.78760590681228</v>
       </c>
       <c r="AA83">
-        <v>-2.063257477350279</v>
+        <v>13.40318925659928</v>
       </c>
     </row>
     <row r="84" spans="1:27">
@@ -7478,7 +7478,7 @@
         <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C84" t="s">
         <v>61</v>
@@ -7490,70 +7490,70 @@
         <v>69</v>
       </c>
       <c r="F84">
-        <v>34.557224208</v>
+        <v>11.976397889</v>
       </c>
       <c r="G84">
-        <v>163.5671125841</v>
+        <v>21.76024062437</v>
       </c>
       <c r="H84">
-        <v>340.7732727852</v>
+        <v>24.6177736181</v>
       </c>
       <c r="I84">
-        <v>492.3933979159</v>
+        <v>25.4130228792</v>
       </c>
       <c r="J84">
-        <v>636.596034527</v>
+        <v>23.9233616458</v>
       </c>
       <c r="K84">
-        <v>700.918416581</v>
+        <v>20.5572363508</v>
       </c>
       <c r="L84">
-        <v>756.839157981</v>
+        <v>21.85989287321</v>
       </c>
       <c r="M84">
-        <v>863.745887100642</v>
+        <v>22.0061945598509</v>
       </c>
       <c r="N84">
-        <v>961.986510506816</v>
+        <v>23.4716648920859</v>
       </c>
       <c r="O84">
-        <v>488.99605908982</v>
+        <v>8.0040972578522</v>
       </c>
       <c r="P84">
-        <v>271.78009105095</v>
+        <v>2.906242331618161</v>
       </c>
       <c r="Q84">
-        <v>191.054055191805</v>
+        <v>0.0453164782284085</v>
       </c>
       <c r="R84">
-        <v>172.240944623215</v>
+        <v>-1.805202224845626</v>
       </c>
       <c r="S84">
-        <v>159.6987133869044</v>
+        <v>-3.12084994089622</v>
       </c>
       <c r="T84">
-        <v>142.5593372325681</v>
+        <v>-3.507549308987473</v>
       </c>
       <c r="U84">
-        <v>116.354271983038</v>
+        <v>-2.653942723459168</v>
       </c>
       <c r="V84">
-        <v>91.24173230747684</v>
+        <v>-1.640986365895647</v>
       </c>
       <c r="W84">
-        <v>69.48322500407744</v>
+        <v>-1.393899759111925</v>
       </c>
       <c r="X84">
-        <v>86.72650529661328</v>
+        <v>-1.710144543430045</v>
       </c>
       <c r="Y84">
-        <v>70.23889340330332</v>
+        <v>-1.842577505699234</v>
       </c>
       <c r="Z84">
-        <v>57.42921862508466</v>
+        <v>-2.05133623922913</v>
       </c>
       <c r="AA84">
-        <v>48.26375081433664</v>
+        <v>-2.063257477350279</v>
       </c>
     </row>
     <row r="85" spans="1:27">
@@ -7561,7 +7561,7 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
         <v>61</v>
@@ -7573,70 +7573,70 @@
         <v>69</v>
       </c>
       <c r="F85">
-        <v>7.99434294</v>
+        <v>34.557224208</v>
       </c>
       <c r="G85">
-        <v>44.5699592992</v>
+        <v>163.5671125841</v>
       </c>
       <c r="H85">
-        <v>99.6257825818</v>
+        <v>340.7732727852</v>
       </c>
       <c r="I85">
-        <v>121.468212781</v>
+        <v>492.3933979159</v>
       </c>
       <c r="J85">
-        <v>139.793840632</v>
+        <v>636.596034527</v>
       </c>
       <c r="K85">
-        <v>167.163024052</v>
+        <v>700.918416581</v>
       </c>
       <c r="L85">
-        <v>172.9968705643</v>
+        <v>756.839157981</v>
       </c>
       <c r="M85">
-        <v>192.4195292929138</v>
+        <v>863.745887100642</v>
       </c>
       <c r="N85">
-        <v>207.882258939329</v>
+        <v>961.986510506816</v>
       </c>
       <c r="O85">
-        <v>99.39938463006</v>
+        <v>488.99605908982</v>
       </c>
       <c r="P85">
-        <v>55.653540448766</v>
+        <v>271.78009105095</v>
       </c>
       <c r="Q85">
-        <v>31.30483234110845</v>
+        <v>191.054055191805</v>
       </c>
       <c r="R85">
-        <v>25.45756654177295</v>
+        <v>172.240944623215</v>
       </c>
       <c r="S85">
-        <v>19.74359991324106</v>
+        <v>159.6987133869044</v>
       </c>
       <c r="T85">
-        <v>13.53496175466828</v>
+        <v>142.5593372325681</v>
       </c>
       <c r="U85">
-        <v>11.61738239711549</v>
+        <v>116.354271983038</v>
       </c>
       <c r="V85">
-        <v>17.02821119638817</v>
+        <v>91.24173230747684</v>
       </c>
       <c r="W85">
-        <v>13.08122564366091</v>
+        <v>69.48322500407744</v>
       </c>
       <c r="X85">
-        <v>9.594174135729654</v>
+        <v>86.72650529661328</v>
       </c>
       <c r="Y85">
-        <v>6.606540805231735</v>
+        <v>70.23889340330332</v>
       </c>
       <c r="Z85">
-        <v>3.645557611198165</v>
+        <v>57.42921862508466</v>
       </c>
       <c r="AA85">
-        <v>0.9545365842795496</v>
+        <v>48.26375081433664</v>
       </c>
     </row>
     <row r="86" spans="1:27">
@@ -7644,7 +7644,7 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C86" t="s">
         <v>61</v>
@@ -7656,70 +7656,70 @@
         <v>69</v>
       </c>
       <c r="F86">
-        <v>144.07195037</v>
+        <v>7.99434294</v>
       </c>
       <c r="G86">
-        <v>314.833747204</v>
+        <v>44.5699592992</v>
       </c>
       <c r="H86">
-        <v>352.1700565938</v>
+        <v>99.6257825818</v>
       </c>
       <c r="I86">
-        <v>327.1862158525</v>
+        <v>121.468212781</v>
       </c>
       <c r="J86">
-        <v>330.31564201089</v>
+        <v>139.793840632</v>
       </c>
       <c r="K86">
-        <v>284.64527130811</v>
+        <v>167.163024052</v>
       </c>
       <c r="L86">
-        <v>315.7080457570198</v>
+        <v>172.9968705643</v>
       </c>
       <c r="M86">
-        <v>306.6723026269224</v>
+        <v>192.4195292929138</v>
       </c>
       <c r="N86">
-        <v>294.9613927579666</v>
+        <v>207.882258939329</v>
       </c>
       <c r="O86">
-        <v>165.3400748084321</v>
+        <v>99.39938463006</v>
       </c>
       <c r="P86">
-        <v>97.77849453057588</v>
+        <v>55.653540448766</v>
       </c>
       <c r="Q86">
-        <v>55.66355057947226</v>
+        <v>31.30483234110845</v>
       </c>
       <c r="R86">
-        <v>30.42035732538928</v>
+        <v>25.45756654177295</v>
       </c>
       <c r="S86">
-        <v>17.57207612979361</v>
+        <v>19.74359991324106</v>
       </c>
       <c r="T86">
-        <v>11.00844392701663</v>
+        <v>13.53496175466828</v>
       </c>
       <c r="U86">
-        <v>9.311755826884928</v>
+        <v>11.61738239711549</v>
       </c>
       <c r="V86">
-        <v>9.355333271031045</v>
+        <v>17.02821119638817</v>
       </c>
       <c r="W86">
-        <v>10.92291794930008</v>
+        <v>13.08122564366091</v>
       </c>
       <c r="X86">
-        <v>12.9654760414277</v>
+        <v>9.594174135729654</v>
       </c>
       <c r="Y86">
-        <v>13.77474010489118</v>
+        <v>6.606540805231735</v>
       </c>
       <c r="Z86">
-        <v>12.86288275674709</v>
+        <v>3.645557611198165</v>
       </c>
       <c r="AA86">
-        <v>10.57810376735257</v>
+        <v>0.9545365842795496</v>
       </c>
     </row>
     <row r="87" spans="1:27">
@@ -7727,7 +7727,7 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C87" t="s">
         <v>61</v>
@@ -7739,70 +7739,70 @@
         <v>69</v>
       </c>
       <c r="F87">
-        <v>25.931869671</v>
+        <v>144.07195037</v>
       </c>
       <c r="G87">
-        <v>82.285989926</v>
+        <v>314.833747204</v>
       </c>
       <c r="H87">
-        <v>127.368707052</v>
+        <v>352.1700565938</v>
       </c>
       <c r="I87">
-        <v>134.812316285</v>
+        <v>327.1862158525</v>
       </c>
       <c r="J87">
-        <v>137.7236465</v>
+        <v>330.31564201089</v>
       </c>
       <c r="K87">
-        <v>113.71364008</v>
+        <v>284.64527130811</v>
       </c>
       <c r="L87">
-        <v>117.527243323</v>
+        <v>315.7080457570198</v>
       </c>
       <c r="M87">
-        <v>119.348551037236</v>
+        <v>306.6723026269224</v>
       </c>
       <c r="N87">
-        <v>125.108078934595</v>
+        <v>294.9613927579666</v>
       </c>
       <c r="O87">
-        <v>76.847959221876</v>
+        <v>165.3400748084321</v>
       </c>
       <c r="P87">
-        <v>46.1909259457501</v>
+        <v>97.77849453057588</v>
       </c>
       <c r="Q87">
-        <v>24.49211600200358</v>
+        <v>55.66355057947226</v>
       </c>
       <c r="R87">
-        <v>7.133675423962691</v>
+        <v>30.42035732538928</v>
       </c>
       <c r="S87">
-        <v>-7.186988482499226</v>
+        <v>17.57207612979361</v>
       </c>
       <c r="T87">
-        <v>-17.89015537944533</v>
+        <v>11.00844392701663</v>
       </c>
       <c r="U87">
-        <v>-28.13249423670137</v>
+        <v>9.311755826884928</v>
       </c>
       <c r="V87">
-        <v>-38.74072231144891</v>
+        <v>9.355333271031045</v>
       </c>
       <c r="W87">
-        <v>-51.46450996826594</v>
+        <v>10.92291794930008</v>
       </c>
       <c r="X87">
-        <v>-68.17179631166255</v>
+        <v>12.9654760414277</v>
       </c>
       <c r="Y87">
-        <v>-84.599841312564</v>
+        <v>13.77474010489118</v>
       </c>
       <c r="Z87">
-        <v>-97.3945746624206</v>
+        <v>12.86288275674709</v>
       </c>
       <c r="AA87">
-        <v>-108.5263258696281</v>
+        <v>10.57810376735257</v>
       </c>
     </row>
     <row r="88" spans="1:27">
@@ -7810,7 +7810,7 @@
         <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C88" t="s">
         <v>61</v>
@@ -7822,70 +7822,70 @@
         <v>69</v>
       </c>
       <c r="F88">
-        <v>93.8217636</v>
+        <v>25.931869671</v>
       </c>
       <c r="G88">
-        <v>201.359352363</v>
+        <v>82.285989926</v>
       </c>
       <c r="H88">
-        <v>388.508470137</v>
+        <v>127.368707052</v>
       </c>
       <c r="I88">
-        <v>501.038532346</v>
+        <v>134.812316285</v>
       </c>
       <c r="J88">
-        <v>588.125786353</v>
+        <v>137.7236465</v>
       </c>
       <c r="K88">
-        <v>607.3209548250001</v>
+        <v>113.71364008</v>
       </c>
       <c r="L88">
-        <v>619.5179006607</v>
+        <v>117.527243323</v>
       </c>
       <c r="M88">
-        <v>645.9277283192</v>
+        <v>119.348551037236</v>
       </c>
       <c r="N88">
-        <v>681.6840100013</v>
+        <v>125.108078934595</v>
       </c>
       <c r="O88">
-        <v>489.1579324297768</v>
+        <v>76.847959221876</v>
       </c>
       <c r="P88">
-        <v>337.2656939306884</v>
+        <v>46.1909259457501</v>
       </c>
       <c r="Q88">
-        <v>235.2637537830471</v>
+        <v>24.49211600200358</v>
       </c>
       <c r="R88">
-        <v>154.2736843558435</v>
+        <v>7.133675423962691</v>
       </c>
       <c r="S88">
-        <v>85.90809533535148</v>
+        <v>-7.186988482499226</v>
       </c>
       <c r="T88">
-        <v>37.28571549225971</v>
+        <v>-17.89015537944533</v>
       </c>
       <c r="U88">
-        <v>-0.3110933780161824</v>
+        <v>-28.13249423670137</v>
       </c>
       <c r="V88">
-        <v>-26.21979185450551</v>
+        <v>-38.74072231144891</v>
       </c>
       <c r="W88">
-        <v>-41.43571816060101</v>
+        <v>-51.46450996826594</v>
       </c>
       <c r="X88">
-        <v>-64.76006557495293</v>
+        <v>-68.17179631166255</v>
       </c>
       <c r="Y88">
-        <v>-95.01078795294856</v>
+        <v>-84.599841312564</v>
       </c>
       <c r="Z88">
-        <v>-120.4920067706615</v>
+        <v>-97.3945746624206</v>
       </c>
       <c r="AA88">
-        <v>-134.8827855899173</v>
+        <v>-108.5263258696281</v>
       </c>
     </row>
     <row r="89" spans="1:27">
@@ -7893,7 +7893,7 @@
         <v>27</v>
       </c>
       <c r="B89" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C89" t="s">
         <v>61</v>
@@ -7905,70 +7905,70 @@
         <v>69</v>
       </c>
       <c r="F89">
-        <v>3.7073918285</v>
+        <v>93.8217636</v>
       </c>
       <c r="G89">
-        <v>18.004178865</v>
+        <v>201.359352363</v>
       </c>
       <c r="H89">
-        <v>35.53882558</v>
+        <v>388.508470137</v>
       </c>
       <c r="I89">
-        <v>42.3510094222</v>
+        <v>501.038532346</v>
       </c>
       <c r="J89">
-        <v>48.648677713</v>
+        <v>588.125786353</v>
       </c>
       <c r="K89">
-        <v>62.947113303</v>
+        <v>607.3209548250001</v>
       </c>
       <c r="L89">
-        <v>69.309386406</v>
+        <v>619.5179006607</v>
       </c>
       <c r="M89">
-        <v>84.7170997713</v>
+        <v>645.9277283192</v>
       </c>
       <c r="N89">
-        <v>103.7394607089</v>
+        <v>681.6840100013</v>
       </c>
       <c r="O89">
-        <v>79.55034132616663</v>
+        <v>489.1579324297768</v>
       </c>
       <c r="P89">
-        <v>62.3693784664333</v>
+        <v>337.2656939306884</v>
       </c>
       <c r="Q89">
-        <v>55.82930654560868</v>
+        <v>235.2637537830471</v>
       </c>
       <c r="R89">
-        <v>59.33549923812058</v>
+        <v>154.2736843558435</v>
       </c>
       <c r="S89">
-        <v>61.01608165654263</v>
+        <v>85.90809533535148</v>
       </c>
       <c r="T89">
-        <v>65.45691571510717</v>
+        <v>37.28571549225971</v>
       </c>
       <c r="U89">
-        <v>67.19615155009836</v>
+        <v>-0.3110933780161824</v>
       </c>
       <c r="V89">
-        <v>62.88349897522617</v>
+        <v>-26.21979185450551</v>
       </c>
       <c r="W89">
-        <v>55.86037525242316</v>
+        <v>-41.43571816060101</v>
       </c>
       <c r="X89">
-        <v>47.47571031016815</v>
+        <v>-64.76006557495293</v>
       </c>
       <c r="Y89">
-        <v>38.5318812992957</v>
+        <v>-95.01078795294856</v>
       </c>
       <c r="Z89">
-        <v>30.45342046349376</v>
+        <v>-120.4920067706615</v>
       </c>
       <c r="AA89">
-        <v>22.91724018983757</v>
+        <v>-134.8827855899173</v>
       </c>
     </row>
     <row r="90" spans="1:27">
@@ -7976,7 +7976,7 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C90" t="s">
         <v>61</v>
@@ -7988,70 +7988,70 @@
         <v>69</v>
       </c>
       <c r="F90">
-        <v>299.24237394</v>
+        <v>3.7073918285</v>
       </c>
       <c r="G90">
-        <v>689.9881405</v>
+        <v>18.004178865</v>
       </c>
       <c r="H90">
-        <v>470.079781736</v>
+        <v>35.53882558</v>
       </c>
       <c r="I90">
-        <v>486.430444919</v>
+        <v>42.3510094222</v>
       </c>
       <c r="J90">
-        <v>489.98965414</v>
+        <v>48.648677713</v>
       </c>
       <c r="K90">
-        <v>546.263885011</v>
+        <v>62.947113303</v>
       </c>
       <c r="L90">
-        <v>588.7277551761</v>
+        <v>69.309386406</v>
       </c>
       <c r="M90">
-        <v>588.4122547203</v>
+        <v>84.7170997713</v>
       </c>
       <c r="N90">
-        <v>591.6226627709</v>
+        <v>103.7394607089</v>
       </c>
       <c r="O90">
-        <v>221.05940052086</v>
+        <v>79.55034132616663</v>
       </c>
       <c r="P90">
-        <v>118.0496459678307</v>
+        <v>62.3693784664333</v>
       </c>
       <c r="Q90">
-        <v>63.09758800163742</v>
+        <v>55.82930654560868</v>
       </c>
       <c r="R90">
-        <v>10.4007085223732</v>
+        <v>59.33549923812058</v>
       </c>
       <c r="S90">
-        <v>-31.28270350576203</v>
+        <v>61.01608165654263</v>
       </c>
       <c r="T90">
-        <v>-57.92751067387742</v>
+        <v>65.45691571510717</v>
       </c>
       <c r="U90">
-        <v>-71.46063805533269</v>
+        <v>67.19615155009836</v>
       </c>
       <c r="V90">
-        <v>-81.86958062487402</v>
+        <v>62.88349897522617</v>
       </c>
       <c r="W90">
-        <v>-98.71386174142852</v>
+        <v>55.86037525242316</v>
       </c>
       <c r="X90">
-        <v>-122.9068829896943</v>
+        <v>47.47571031016815</v>
       </c>
       <c r="Y90">
-        <v>-139.3538218372281</v>
+        <v>38.5318812992957</v>
       </c>
       <c r="Z90">
-        <v>-150.3907985642646</v>
+        <v>30.45342046349376</v>
       </c>
       <c r="AA90">
-        <v>-161.8089985009538</v>
+        <v>22.91724018983757</v>
       </c>
     </row>
     <row r="91" spans="1:27">
@@ -8059,7 +8059,7 @@
         <v>27</v>
       </c>
       <c r="B91" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C91" t="s">
         <v>61</v>
@@ -8071,70 +8071,70 @@
         <v>69</v>
       </c>
       <c r="F91">
-        <v>30.6799432</v>
+        <v>299.24237394</v>
       </c>
       <c r="G91">
-        <v>111.091547888352</v>
+        <v>689.9881405</v>
       </c>
       <c r="H91">
-        <v>136.320796525</v>
+        <v>470.079781736</v>
       </c>
       <c r="I91">
-        <v>143.7346250946</v>
+        <v>486.430444919</v>
       </c>
       <c r="J91">
-        <v>141.7703061473</v>
+        <v>489.98965414</v>
       </c>
       <c r="K91">
-        <v>128.87830533255</v>
+        <v>546.263885011</v>
       </c>
       <c r="L91">
-        <v>124.81825569464</v>
+        <v>588.7277551761</v>
       </c>
       <c r="M91">
-        <v>123.2956551051223</v>
+        <v>588.4122547203</v>
       </c>
       <c r="N91">
-        <v>122.6985872387188</v>
+        <v>591.6226627709</v>
       </c>
       <c r="O91">
-        <v>53.198100778235</v>
+        <v>221.05940052086</v>
       </c>
       <c r="P91">
-        <v>34.13689257039486</v>
+        <v>118.0496459678307</v>
       </c>
       <c r="Q91">
-        <v>26.75515706548108</v>
+        <v>63.09758800163742</v>
       </c>
       <c r="R91">
-        <v>24.8418181213399</v>
+        <v>10.4007085223732</v>
       </c>
       <c r="S91">
-        <v>22.57971314816973</v>
+        <v>-31.28270350576203</v>
       </c>
       <c r="T91">
-        <v>19.98122330826799</v>
+        <v>-57.92751067387742</v>
       </c>
       <c r="U91">
-        <v>16.99423996357886</v>
+        <v>-71.46063805533269</v>
       </c>
       <c r="V91">
-        <v>14.33148736304582</v>
+        <v>-81.86958062487402</v>
       </c>
       <c r="W91">
-        <v>11.51500259494315</v>
+        <v>-98.71386174142852</v>
       </c>
       <c r="X91">
-        <v>8.966024557977708</v>
+        <v>-122.9068829896943</v>
       </c>
       <c r="Y91">
-        <v>8.609674361448615</v>
+        <v>-139.3538218372281</v>
       </c>
       <c r="Z91">
-        <v>6.520494553013124</v>
+        <v>-150.3907985642646</v>
       </c>
       <c r="AA91">
-        <v>5.023093134307652</v>
+        <v>-161.8089985009538</v>
       </c>
     </row>
     <row r="92" spans="1:27">
@@ -8142,7 +8142,7 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C92" t="s">
         <v>61</v>
@@ -8154,70 +8154,70 @@
         <v>69</v>
       </c>
       <c r="F92">
-        <v>10.4999246633</v>
+        <v>30.6799432</v>
       </c>
       <c r="G92">
-        <v>30.526308404537</v>
+        <v>111.091547888352</v>
       </c>
       <c r="H92">
-        <v>48.447463061338</v>
+        <v>136.320796525</v>
       </c>
       <c r="I92">
-        <v>53.48845419328</v>
+        <v>143.7346250946</v>
       </c>
       <c r="J92">
-        <v>52.081331997129</v>
+        <v>141.7703061473</v>
       </c>
       <c r="K92">
-        <v>18.8934201023796</v>
+        <v>128.87830533255</v>
       </c>
       <c r="L92">
-        <v>21.5899657802328</v>
+        <v>124.81825569464</v>
       </c>
       <c r="M92">
-        <v>28.305324993938</v>
+        <v>123.2956551051223</v>
       </c>
       <c r="N92">
-        <v>37.7309884864162</v>
+        <v>122.6985872387188</v>
       </c>
       <c r="O92">
-        <v>20.3871822015429</v>
+        <v>53.198100778235</v>
       </c>
       <c r="P92">
-        <v>14.2321235675455</v>
+        <v>34.13689257039486</v>
       </c>
       <c r="Q92">
-        <v>10.43812405516996</v>
+        <v>26.75515706548108</v>
       </c>
       <c r="R92">
-        <v>7.387198381277328</v>
+        <v>24.8418181213399</v>
       </c>
       <c r="S92">
-        <v>4.004673089037043</v>
+        <v>22.57971314816973</v>
       </c>
       <c r="T92">
-        <v>0.6984613404522624</v>
+        <v>19.98122330826799</v>
       </c>
       <c r="U92">
-        <v>-2.702780629914919</v>
+        <v>16.99423996357886</v>
       </c>
       <c r="V92">
-        <v>-6.305562996868397</v>
+        <v>14.33148736304582</v>
       </c>
       <c r="W92">
-        <v>-9.506563744148568</v>
+        <v>11.51500259494315</v>
       </c>
       <c r="X92">
-        <v>-14.41168033905547</v>
+        <v>8.966024557977708</v>
       </c>
       <c r="Y92">
-        <v>-21.89364108149178</v>
+        <v>8.609674361448615</v>
       </c>
       <c r="Z92">
-        <v>-28.73623438937905</v>
+        <v>6.520494553013124</v>
       </c>
       <c r="AA92">
-        <v>-37.08049227745099</v>
+        <v>5.023093134307652</v>
       </c>
     </row>
     <row r="93" spans="1:27">
@@ -8225,7 +8225,7 @@
         <v>27</v>
       </c>
       <c r="B93" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C93" t="s">
         <v>61</v>
@@ -8237,70 +8237,70 @@
         <v>69</v>
       </c>
       <c r="F93">
-        <v>11.14068783</v>
+        <v>10.4999246633</v>
       </c>
       <c r="G93">
-        <v>24.094670319</v>
+        <v>30.526308404537</v>
       </c>
       <c r="H93">
-        <v>40.8691796131</v>
+        <v>48.447463061338</v>
       </c>
       <c r="I93">
-        <v>54.105418385</v>
+        <v>53.48845419328</v>
       </c>
       <c r="J93">
-        <v>61.425480548</v>
+        <v>52.081331997129</v>
       </c>
       <c r="K93">
-        <v>63.562396851</v>
+        <v>18.8934201023796</v>
       </c>
       <c r="L93">
-        <v>67.67987878785</v>
+        <v>21.5899657802328</v>
       </c>
       <c r="M93">
-        <v>69.28031488633999</v>
+        <v>28.305324993938</v>
       </c>
       <c r="N93">
-        <v>71.97786793941999</v>
+        <v>37.7309884864162</v>
       </c>
       <c r="O93">
-        <v>31.0126997726025</v>
+        <v>20.3871822015429</v>
       </c>
       <c r="P93">
-        <v>11.5901459219118</v>
+        <v>14.2321235675455</v>
       </c>
       <c r="Q93">
-        <v>-4.57330054923735</v>
+        <v>10.43812405516996</v>
       </c>
       <c r="R93">
-        <v>-19.7475301794545</v>
+        <v>7.387198381277328</v>
       </c>
       <c r="S93">
-        <v>-33.80818491615519</v>
+        <v>4.004673089037043</v>
       </c>
       <c r="T93">
-        <v>-45.25941250677859</v>
+        <v>0.6984613404522624</v>
       </c>
       <c r="U93">
-        <v>-57.9293703333792</v>
+        <v>-2.702780629914919</v>
       </c>
       <c r="V93">
-        <v>-72.1718027102698</v>
+        <v>-6.305562996868397</v>
       </c>
       <c r="W93">
-        <v>-88.51431772137333</v>
+        <v>-9.506563744148568</v>
       </c>
       <c r="X93">
-        <v>-111.539023448266</v>
+        <v>-14.41168033905547</v>
       </c>
       <c r="Y93">
-        <v>-137.0754457639094</v>
+        <v>-21.89364108149178</v>
       </c>
       <c r="Z93">
-        <v>-163.7003415666787</v>
+        <v>-28.73623438937905</v>
       </c>
       <c r="AA93">
-        <v>-190.2673069267766</v>
+        <v>-37.08049227745099</v>
       </c>
     </row>
     <row r="94" spans="1:27">
@@ -8308,7 +8308,7 @@
         <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C94" t="s">
         <v>61</v>
@@ -8320,70 +8320,70 @@
         <v>69</v>
       </c>
       <c r="F94">
-        <v>3.1148930041</v>
+        <v>11.14068783</v>
       </c>
       <c r="G94">
-        <v>7.62235648322</v>
+        <v>24.094670319</v>
       </c>
       <c r="H94">
-        <v>19.00970764024</v>
+        <v>40.8691796131</v>
       </c>
       <c r="I94">
-        <v>25.2807926606</v>
+        <v>54.105418385</v>
       </c>
       <c r="J94">
-        <v>34.86366746</v>
+        <v>61.425480548</v>
       </c>
       <c r="K94">
-        <v>46.036315605</v>
+        <v>63.562396851</v>
       </c>
       <c r="L94">
-        <v>50.34600700032</v>
+        <v>67.67987878785</v>
       </c>
       <c r="M94">
-        <v>61.30501390622</v>
+        <v>69.28031488633999</v>
       </c>
       <c r="N94">
-        <v>73.51887703328001</v>
+        <v>71.97786793941999</v>
       </c>
       <c r="O94">
-        <v>47.58898015631059</v>
+        <v>31.0126997726025</v>
       </c>
       <c r="P94">
-        <v>37.12948094582137</v>
+        <v>11.5901459219118</v>
       </c>
       <c r="Q94">
-        <v>30.10716165665923</v>
+        <v>-4.57330054923735</v>
       </c>
       <c r="R94">
-        <v>28.19239768043192</v>
+        <v>-19.7475301794545</v>
       </c>
       <c r="S94">
-        <v>27.76608619793173</v>
+        <v>-33.80818491615519</v>
       </c>
       <c r="T94">
-        <v>27.01833101246332</v>
+        <v>-45.25941250677859</v>
       </c>
       <c r="U94">
-        <v>25.25662918107847</v>
+        <v>-57.9293703333792</v>
       </c>
       <c r="V94">
-        <v>22.91328020455089</v>
+        <v>-72.1718027102698</v>
       </c>
       <c r="W94">
-        <v>21.94023279152456</v>
+        <v>-88.51431772137333</v>
       </c>
       <c r="X94">
-        <v>18.29405714453439</v>
+        <v>-111.539023448266</v>
       </c>
       <c r="Y94">
-        <v>14.27820564335437</v>
+        <v>-137.0754457639094</v>
       </c>
       <c r="Z94">
-        <v>10.63788876761847</v>
+        <v>-163.7003415666787</v>
       </c>
       <c r="AA94">
-        <v>7.519061029555161</v>
+        <v>-190.2673069267766</v>
       </c>
     </row>
     <row r="95" spans="1:27">
@@ -8391,7 +8391,7 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C95" t="s">
         <v>61</v>
@@ -8403,70 +8403,70 @@
         <v>69</v>
       </c>
       <c r="F95">
-        <v>10.67685026</v>
+        <v>3.1148930041</v>
       </c>
       <c r="G95">
-        <v>76.444830001452</v>
+        <v>7.62235648322</v>
       </c>
       <c r="H95">
-        <v>144.7140606732</v>
+        <v>19.00970764024</v>
       </c>
       <c r="I95">
-        <v>169.81910517803</v>
+        <v>25.2807926606</v>
       </c>
       <c r="J95">
-        <v>182.233588030905</v>
+        <v>34.86366746</v>
       </c>
       <c r="K95">
-        <v>175.684081942998</v>
+        <v>46.036315605</v>
       </c>
       <c r="L95">
-        <v>177.4392963020035</v>
+        <v>50.34600700032</v>
       </c>
       <c r="M95">
-        <v>174.7776867406871</v>
+        <v>61.30501390622</v>
       </c>
       <c r="N95">
-        <v>171.0847761804603</v>
+        <v>73.51887703328001</v>
       </c>
       <c r="O95">
-        <v>119.433330030011</v>
+        <v>47.58898015631059</v>
       </c>
       <c r="P95">
-        <v>87.55819695017188</v>
+        <v>37.12948094582137</v>
       </c>
       <c r="Q95">
-        <v>69.87164141676296</v>
+        <v>30.10716165665923</v>
       </c>
       <c r="R95">
-        <v>59.2295397426653</v>
+        <v>28.19239768043192</v>
       </c>
       <c r="S95">
-        <v>50.43836858618496</v>
+        <v>27.76608619793173</v>
       </c>
       <c r="T95">
-        <v>42.9533016117083</v>
+        <v>27.01833101246332</v>
       </c>
       <c r="U95">
-        <v>35.70936828952965</v>
+        <v>25.25662918107847</v>
       </c>
       <c r="V95">
-        <v>30.38877642911908</v>
+        <v>22.91328020455089</v>
       </c>
       <c r="W95">
-        <v>26.33642613817894</v>
+        <v>21.94023279152456</v>
       </c>
       <c r="X95">
-        <v>22.87811682134046</v>
+        <v>18.29405714453439</v>
       </c>
       <c r="Y95">
-        <v>20.02094164729559</v>
+        <v>14.27820564335437</v>
       </c>
       <c r="Z95">
-        <v>17.74225544600758</v>
+        <v>10.63788876761847</v>
       </c>
       <c r="AA95">
-        <v>15.8732688469519</v>
+        <v>7.519061029555161</v>
       </c>
     </row>
     <row r="96" spans="1:27">
@@ -8474,7 +8474,7 @@
         <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C96" t="s">
         <v>61</v>
@@ -8486,70 +8486,70 @@
         <v>69</v>
       </c>
       <c r="F96">
-        <v>36.76990316</v>
+        <v>10.67685026</v>
       </c>
       <c r="G96">
-        <v>120.822000304375</v>
+        <v>76.444830001452</v>
       </c>
       <c r="H96">
-        <v>233.0029986110314</v>
+        <v>144.7140606732</v>
       </c>
       <c r="I96">
-        <v>286.3061332203409</v>
+        <v>169.81910517803</v>
       </c>
       <c r="J96">
-        <v>328.1676309439272</v>
+        <v>182.233588030905</v>
       </c>
       <c r="K96">
-        <v>384.7846333041183</v>
+        <v>175.684081942998</v>
       </c>
       <c r="L96">
-        <v>409.1349515082217</v>
+        <v>177.4392963020035</v>
       </c>
       <c r="M96">
-        <v>444.998469243266</v>
+        <v>174.7776867406871</v>
       </c>
       <c r="N96">
-        <v>476.494657841313</v>
+        <v>171.0847761804603</v>
       </c>
       <c r="O96">
-        <v>233.9390054773612</v>
+        <v>119.433330030011</v>
       </c>
       <c r="P96">
-        <v>125.5760832127253</v>
+        <v>87.55819695017188</v>
       </c>
       <c r="Q96">
-        <v>48.58843980759231</v>
+        <v>69.87164141676296</v>
       </c>
       <c r="R96">
-        <v>-10.985753066195</v>
+        <v>59.2295397426653</v>
       </c>
       <c r="S96">
-        <v>-54.45420499396563</v>
+        <v>50.43836858618496</v>
       </c>
       <c r="T96">
-        <v>-83.69602777485095</v>
+        <v>42.9533016117083</v>
       </c>
       <c r="U96">
-        <v>-104.4499353183856</v>
+        <v>35.70936828952965</v>
       </c>
       <c r="V96">
-        <v>-113.7620539511867</v>
+        <v>30.38877642911908</v>
       </c>
       <c r="W96">
-        <v>-115.2500558791728</v>
+        <v>26.33642613817894</v>
       </c>
       <c r="X96">
-        <v>-116.7273793244488</v>
+        <v>22.87811682134046</v>
       </c>
       <c r="Y96">
-        <v>-118.3018463842557</v>
+        <v>20.02094164729559</v>
       </c>
       <c r="Z96">
-        <v>-122.0129157750319</v>
+        <v>17.74225544600758</v>
       </c>
       <c r="AA96">
-        <v>-121.319970970934</v>
+        <v>15.8732688469519</v>
       </c>
     </row>
     <row r="97" spans="1:27">
@@ -8557,7 +8557,7 @@
         <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C97" t="s">
         <v>61</v>
@@ -8569,70 +8569,70 @@
         <v>69</v>
       </c>
       <c r="F97">
-        <v>6.7345662939</v>
+        <v>36.76990316</v>
       </c>
       <c r="G97">
-        <v>35.3351190809</v>
+        <v>120.822000304375</v>
       </c>
       <c r="H97">
-        <v>78.66162216849</v>
+        <v>233.0029986110314</v>
       </c>
       <c r="I97">
-        <v>77.92614730137001</v>
+        <v>286.3061332203409</v>
       </c>
       <c r="J97">
-        <v>80.559486531576</v>
+        <v>328.1676309439272</v>
       </c>
       <c r="K97">
-        <v>81.177959502977</v>
+        <v>384.7846333041183</v>
       </c>
       <c r="L97">
-        <v>77.127423409904</v>
+        <v>409.1349515082217</v>
       </c>
       <c r="M97">
-        <v>75.35397825878937</v>
+        <v>444.998469243266</v>
       </c>
       <c r="N97">
-        <v>71.92005158032907</v>
+        <v>476.494657841313</v>
       </c>
       <c r="O97">
-        <v>49.7268908528239</v>
+        <v>233.9390054773612</v>
       </c>
       <c r="P97">
-        <v>32.13876062846828</v>
+        <v>125.5760832127253</v>
       </c>
       <c r="Q97">
-        <v>23.57468646237333</v>
+        <v>48.58843980759231</v>
       </c>
       <c r="R97">
-        <v>18.98797937410516</v>
+        <v>-10.985753066195</v>
       </c>
       <c r="S97">
-        <v>14.75799623722541</v>
+        <v>-54.45420499396563</v>
       </c>
       <c r="T97">
-        <v>11.170583941565</v>
+        <v>-83.69602777485095</v>
       </c>
       <c r="U97">
-        <v>7.992970153967071</v>
+        <v>-104.4499353183856</v>
       </c>
       <c r="V97">
-        <v>5.555553944609983</v>
+        <v>-113.7620539511867</v>
       </c>
       <c r="W97">
-        <v>3.405485176147516</v>
+        <v>-115.2500558791728</v>
       </c>
       <c r="X97">
-        <v>0.692989882837999</v>
+        <v>-116.7273793244488</v>
       </c>
       <c r="Y97">
-        <v>-1.905554059350958</v>
+        <v>-118.3018463842557</v>
       </c>
       <c r="Z97">
-        <v>-3.696349115467541</v>
+        <v>-122.0129157750319</v>
       </c>
       <c r="AA97">
-        <v>-4.767550614521398</v>
+        <v>-121.319970970934</v>
       </c>
     </row>
     <row r="98" spans="1:27">
@@ -8640,7 +8640,7 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C98" t="s">
         <v>61</v>
@@ -8652,70 +8652,70 @@
         <v>69</v>
       </c>
       <c r="F98">
-        <v>516.9936186</v>
+        <v>6.7345662939</v>
       </c>
       <c r="G98">
-        <v>1400.6891308</v>
+        <v>35.3351190809</v>
       </c>
       <c r="H98">
-        <v>1638.91332928</v>
+        <v>78.66162216849</v>
       </c>
       <c r="I98">
-        <v>1529.410123</v>
+        <v>77.92614730137001</v>
       </c>
       <c r="J98">
-        <v>1438.06798541</v>
+        <v>80.559486531576</v>
       </c>
       <c r="K98">
-        <v>1332.99193917</v>
+        <v>81.177959502977</v>
       </c>
       <c r="L98">
-        <v>1292.0998880832</v>
+        <v>77.127423409904</v>
       </c>
       <c r="M98">
-        <v>1265.5225853502</v>
+        <v>75.35397825878937</v>
       </c>
       <c r="N98">
-        <v>1226.6668507922</v>
+        <v>71.92005158032907</v>
       </c>
       <c r="O98">
-        <v>722.5466785196001</v>
+        <v>49.7268908528239</v>
       </c>
       <c r="P98">
-        <v>430.0603145843</v>
+        <v>32.13876062846828</v>
       </c>
       <c r="Q98">
-        <v>197.5936252463459</v>
+        <v>23.57468646237333</v>
       </c>
       <c r="R98">
-        <v>30.6325646079124</v>
+        <v>18.98797937410516</v>
       </c>
       <c r="S98">
-        <v>-114.8277093649022</v>
+        <v>14.75799623722541</v>
       </c>
       <c r="T98">
-        <v>-223.2442680569352</v>
+        <v>11.170583941565</v>
       </c>
       <c r="U98">
-        <v>-333.28120980281</v>
+        <v>7.992970153967071</v>
       </c>
       <c r="V98">
-        <v>-429.0130690527428</v>
+        <v>5.555553944609983</v>
       </c>
       <c r="W98">
-        <v>-528.0705096888206</v>
+        <v>3.405485176147516</v>
       </c>
       <c r="X98">
-        <v>-651.2764043280414</v>
+        <v>0.692989882837999</v>
       </c>
       <c r="Y98">
-        <v>-766.5994770976006</v>
+        <v>-1.905554059350958</v>
       </c>
       <c r="Z98">
-        <v>-844.3037622498205</v>
+        <v>-3.696349115467541</v>
       </c>
       <c r="AA98">
-        <v>-926.8221247838544</v>
+        <v>-4.767550614521398</v>
       </c>
     </row>
     <row r="99" spans="1:27">
@@ -8723,7 +8723,7 @@
         <v>27</v>
       </c>
       <c r="B99" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C99" t="s">
         <v>61</v>
@@ -8735,70 +8735,70 @@
         <v>69</v>
       </c>
       <c r="F99">
-        <v>91.95284384</v>
+        <v>516.9936186</v>
       </c>
       <c r="G99">
-        <v>210.80527056</v>
+        <v>1400.6891308</v>
       </c>
       <c r="H99">
-        <v>100.781637089</v>
+        <v>1638.91332928</v>
       </c>
       <c r="I99">
-        <v>87.12979062078</v>
+        <v>1529.410123</v>
       </c>
       <c r="J99">
-        <v>62.31136040854</v>
+        <v>1438.06798541</v>
       </c>
       <c r="K99">
-        <v>52.30090783331</v>
+        <v>1332.99193917</v>
       </c>
       <c r="L99">
-        <v>50.38967054566</v>
+        <v>1292.0998880832</v>
       </c>
       <c r="M99">
-        <v>54.28903742533</v>
+        <v>1265.5225853502</v>
       </c>
       <c r="N99">
-        <v>58.06529480089</v>
+        <v>1226.6668507922</v>
       </c>
       <c r="O99">
-        <v>28.095540736981</v>
+        <v>722.5466785196001</v>
       </c>
       <c r="P99">
-        <v>17.247189228069</v>
+        <v>430.0603145843</v>
       </c>
       <c r="Q99">
-        <v>11.05981576962534</v>
+        <v>197.5936252463459</v>
       </c>
       <c r="R99">
-        <v>7.75222049673956</v>
+        <v>30.6325646079124</v>
       </c>
       <c r="S99">
-        <v>5.313555273422687</v>
+        <v>-114.8277093649022</v>
       </c>
       <c r="T99">
-        <v>3.887262791733732</v>
+        <v>-223.2442680569352</v>
       </c>
       <c r="U99">
-        <v>3.611046206949093</v>
+        <v>-333.28120980281</v>
       </c>
       <c r="V99">
-        <v>3.773915802552625</v>
+        <v>-429.0130690527428</v>
       </c>
       <c r="W99">
-        <v>3.721605635769954</v>
+        <v>-528.0705096888206</v>
       </c>
       <c r="X99">
-        <v>3.20413311143767</v>
+        <v>-651.2764043280414</v>
       </c>
       <c r="Y99">
-        <v>2.387762702658748</v>
+        <v>-766.5994770976006</v>
       </c>
       <c r="Z99">
-        <v>1.38228276689191</v>
+        <v>-844.3037622498205</v>
       </c>
       <c r="AA99">
-        <v>0.3580857297832861</v>
+        <v>-926.8221247838544</v>
       </c>
     </row>
     <row r="100" spans="1:27">
@@ -8806,7 +8806,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C100" t="s">
         <v>61</v>
@@ -8818,69 +8818,152 @@
         <v>69</v>
       </c>
       <c r="F100">
+        <v>91.95284384</v>
+      </c>
+      <c r="G100">
+        <v>210.80527056</v>
+      </c>
+      <c r="H100">
+        <v>100.781637089</v>
+      </c>
+      <c r="I100">
+        <v>87.12979062078</v>
+      </c>
+      <c r="J100">
+        <v>62.31136040854</v>
+      </c>
+      <c r="K100">
+        <v>52.30090783331</v>
+      </c>
+      <c r="L100">
+        <v>50.38967054566</v>
+      </c>
+      <c r="M100">
+        <v>54.28903742533</v>
+      </c>
+      <c r="N100">
+        <v>58.06529480089</v>
+      </c>
+      <c r="O100">
+        <v>28.095540736981</v>
+      </c>
+      <c r="P100">
+        <v>17.247189228069</v>
+      </c>
+      <c r="Q100">
+        <v>11.05981576962534</v>
+      </c>
+      <c r="R100">
+        <v>7.75222049673956</v>
+      </c>
+      <c r="S100">
+        <v>5.313555273422687</v>
+      </c>
+      <c r="T100">
+        <v>3.887262791733732</v>
+      </c>
+      <c r="U100">
+        <v>3.611046206949093</v>
+      </c>
+      <c r="V100">
+        <v>3.773915802552625</v>
+      </c>
+      <c r="W100">
+        <v>3.721605635769954</v>
+      </c>
+      <c r="X100">
+        <v>3.20413311143767</v>
+      </c>
+      <c r="Y100">
+        <v>2.387762702658748</v>
+      </c>
+      <c r="Z100">
+        <v>1.38228276689191</v>
+      </c>
+      <c r="AA100">
+        <v>0.3580857297832861</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27">
+      <c r="A101" t="s">
+        <v>27</v>
+      </c>
+      <c r="B101" t="s">
+        <v>60</v>
+      </c>
+      <c r="C101" t="s">
+        <v>61</v>
+      </c>
+      <c r="D101" t="s">
+        <v>65</v>
+      </c>
+      <c r="E101" t="s">
+        <v>69</v>
+      </c>
+      <c r="F101">
         <v>2380.523956178104</v>
       </c>
-      <c r="G100">
+      <c r="G101">
         <v>6201.846850010113</v>
       </c>
-      <c r="H100">
+      <c r="H101">
         <v>8196.469731564328</v>
       </c>
-      <c r="I100">
+      <c r="I101">
         <v>9310.694019157982</v>
       </c>
-      <c r="J100">
+      <c r="J101">
         <v>9934.615954610279</v>
       </c>
-      <c r="K100">
+      <c r="K101">
         <v>10272.83692404719</v>
       </c>
-      <c r="L100">
+      <c r="L101">
         <v>10947.33920047185</v>
       </c>
-      <c r="M100">
+      <c r="M101">
         <v>11216.91448693623</v>
       </c>
-      <c r="N100">
+      <c r="N101">
         <v>11443.53452819194</v>
       </c>
-      <c r="O100">
+      <c r="O101">
         <v>5779.364027751162</v>
       </c>
-      <c r="P100">
+      <c r="P101">
         <v>3409.949954611135</v>
       </c>
-      <c r="Q100">
+      <c r="Q101">
         <v>1959.689939098703</v>
       </c>
-      <c r="R100">
+      <c r="R101">
         <v>1021.566198474898</v>
       </c>
-      <c r="S100">
+      <c r="S101">
         <v>300.2387368179965</v>
       </c>
-      <c r="T100">
+      <c r="T101">
         <v>-239.8452457330159</v>
       </c>
-      <c r="U100">
+      <c r="U101">
         <v>-754.4570125152899</v>
       </c>
-      <c r="V100">
+      <c r="V101">
         <v>-1147.548096357275</v>
       </c>
-      <c r="W100">
+      <c r="W101">
         <v>-1516.995926095977</v>
       </c>
-      <c r="X100">
+      <c r="X101">
         <v>-1915.934696355146</v>
       </c>
-      <c r="Y100">
+      <c r="Y101">
         <v>-2339.757359426527</v>
       </c>
-      <c r="Z100">
+      <c r="Z101">
         <v>-2678.051951125386</v>
       </c>
-      <c r="AA100">
+      <c r="AA101">
         <v>-3080.517565934394</v>
       </c>
     </row>
